--- a/artfynd/A 18557-2025 artfynd.xlsx
+++ b/artfynd/A 18557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY550"/>
+  <dimension ref="A1:AY551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5064,10 +5064,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125036186</v>
+        <v>125046711</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,37 +5080,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444489</v>
+        <v>444558</v>
       </c>
       <c r="R44" t="n">
-        <v>6846220</v>
+        <v>6846340</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5154,22 +5154,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125035599</v>
+        <v>125046604</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5182,37 +5182,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444609</v>
+        <v>444838</v>
       </c>
       <c r="R45" t="n">
-        <v>6846136</v>
+        <v>6846288</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5256,22 +5256,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125046711</v>
+        <v>125036186</v>
       </c>
       <c r="B46" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5284,37 +5284,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444558</v>
+        <v>444489</v>
       </c>
       <c r="R46" t="n">
-        <v>6846340</v>
+        <v>6846220</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5358,22 +5358,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125046604</v>
+        <v>125035599</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5386,37 +5386,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444838</v>
+        <v>444609</v>
       </c>
       <c r="R47" t="n">
-        <v>6846288</v>
+        <v>6846136</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5460,12 +5460,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125038101</v>
+        <v>125047007</v>
       </c>
       <c r="B144" t="n">
         <v>78810</v>
@@ -15320,17 +15320,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>444754</v>
+        <v>444499</v>
       </c>
       <c r="R144" t="n">
-        <v>6846466</v>
+        <v>6846245</v>
       </c>
       <c r="S144" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15374,19 +15374,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125047007</v>
+        <v>125047037</v>
       </c>
       <c r="B145" t="n">
         <v>78810</v>
@@ -15426,10 +15426,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>444499</v>
+        <v>444636</v>
       </c>
       <c r="R145" t="n">
-        <v>6846245</v>
+        <v>6846147</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15488,7 +15488,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125047037</v>
+        <v>125046966</v>
       </c>
       <c r="B146" t="n">
         <v>78810</v>
@@ -15528,10 +15528,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>444636</v>
+        <v>444600</v>
       </c>
       <c r="R146" t="n">
-        <v>6846147</v>
+        <v>6846520</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15590,7 +15590,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125046966</v>
+        <v>125047064</v>
       </c>
       <c r="B147" t="n">
         <v>78810</v>
@@ -15630,10 +15630,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>444600</v>
+        <v>444890</v>
       </c>
       <c r="R147" t="n">
-        <v>6846520</v>
+        <v>6846336</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15692,7 +15692,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125047064</v>
+        <v>125047068</v>
       </c>
       <c r="B148" t="n">
         <v>78810</v>
@@ -15732,10 +15732,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>444890</v>
+        <v>444956</v>
       </c>
       <c r="R148" t="n">
-        <v>6846336</v>
+        <v>6846307</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15794,7 +15794,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125047068</v>
+        <v>125046981</v>
       </c>
       <c r="B149" t="n">
         <v>78810</v>
@@ -15834,10 +15834,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>444956</v>
+        <v>444537</v>
       </c>
       <c r="R149" t="n">
-        <v>6846307</v>
+        <v>6846522</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15896,7 +15896,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125046981</v>
+        <v>125047004</v>
       </c>
       <c r="B150" t="n">
         <v>78810</v>
@@ -15936,10 +15936,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>444537</v>
+        <v>444496</v>
       </c>
       <c r="R150" t="n">
-        <v>6846522</v>
+        <v>6846293</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15998,7 +15998,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125047004</v>
+        <v>125038101</v>
       </c>
       <c r="B151" t="n">
         <v>78810</v>
@@ -16034,17 +16034,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>444496</v>
+        <v>444754</v>
       </c>
       <c r="R151" t="n">
-        <v>6846293</v>
+        <v>6846466</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16088,12 +16088,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -23871,7 +23871,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>125033819</v>
+        <v>125047066</v>
       </c>
       <c r="B228" t="n">
         <v>78810</v>
@@ -23907,17 +23907,17 @@
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>444990</v>
+        <v>444930</v>
       </c>
       <c r="R228" t="n">
-        <v>6846293</v>
+        <v>6846308</v>
       </c>
       <c r="S228" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -23961,19 +23961,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>125039623</v>
+        <v>125046987</v>
       </c>
       <c r="B229" t="n">
         <v>78810</v>
@@ -24009,14 +24009,14 @@
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>445082</v>
+        <v>444532</v>
       </c>
       <c r="R229" t="n">
-        <v>6846475</v>
+        <v>6846448</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24063,22 +24063,22 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>125047066</v>
+        <v>125046714</v>
       </c>
       <c r="B230" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24091,21 +24091,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24115,10 +24115,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>444930</v>
+        <v>444747</v>
       </c>
       <c r="R230" t="n">
-        <v>6846308</v>
+        <v>6846227</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24177,10 +24177,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>125046987</v>
+        <v>125046603</v>
       </c>
       <c r="B231" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24193,21 +24193,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24217,10 +24217,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>444532</v>
+        <v>444736</v>
       </c>
       <c r="R231" t="n">
-        <v>6846448</v>
+        <v>6846178</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24279,10 +24279,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>125046714</v>
+        <v>125046948</v>
       </c>
       <c r="B232" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24295,21 +24295,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24319,10 +24319,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>444747</v>
+        <v>445066</v>
       </c>
       <c r="R232" t="n">
-        <v>6846227</v>
+        <v>6846537</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24381,10 +24381,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>125046603</v>
+        <v>125046729</v>
       </c>
       <c r="B233" t="n">
-        <v>79428</v>
+        <v>78905</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24397,21 +24397,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24421,10 +24421,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>444736</v>
+        <v>444533</v>
       </c>
       <c r="R233" t="n">
-        <v>6846178</v>
+        <v>6846485</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24483,7 +24483,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>125046948</v>
+        <v>125047050</v>
       </c>
       <c r="B234" t="n">
         <v>78810</v>
@@ -24523,10 +24523,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445066</v>
+        <v>444726</v>
       </c>
       <c r="R234" t="n">
-        <v>6846537</v>
+        <v>6846130</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24585,10 +24585,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>125046729</v>
+        <v>125046961</v>
       </c>
       <c r="B235" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24601,21 +24601,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>444533</v>
+        <v>444747</v>
       </c>
       <c r="R235" t="n">
-        <v>6846485</v>
+        <v>6846466</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24687,10 +24687,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>125047050</v>
+        <v>125046672</v>
       </c>
       <c r="B236" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24703,21 +24703,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24727,10 +24727,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>444726</v>
+        <v>444514</v>
       </c>
       <c r="R236" t="n">
-        <v>6846130</v>
+        <v>6846296</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24789,10 +24789,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>125046961</v>
+        <v>125046671</v>
       </c>
       <c r="B237" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24805,21 +24805,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>444747</v>
+        <v>444533</v>
       </c>
       <c r="R237" t="n">
-        <v>6846466</v>
+        <v>6846410</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24891,10 +24891,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>125046672</v>
+        <v>125046963</v>
       </c>
       <c r="B238" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -24907,21 +24907,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24931,10 +24931,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>444514</v>
+        <v>444710</v>
       </c>
       <c r="R238" t="n">
-        <v>6846296</v>
+        <v>6846480</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24993,10 +24993,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>125046671</v>
+        <v>125033819</v>
       </c>
       <c r="B239" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25009,37 +25009,37 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>444533</v>
+        <v>444990</v>
       </c>
       <c r="R239" t="n">
-        <v>6846410</v>
+        <v>6846293</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -25083,19 +25083,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>125046963</v>
+        <v>125039623</v>
       </c>
       <c r="B240" t="n">
         <v>78810</v>
@@ -25131,14 +25131,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>444710</v>
+        <v>445082</v>
       </c>
       <c r="R240" t="n">
-        <v>6846480</v>
+        <v>6846475</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25185,12 +25185,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
@@ -29926,7 +29926,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>125033575</v>
+        <v>125046894</v>
       </c>
       <c r="B287" t="n">
         <v>78810</v>
@@ -29962,14 +29962,14 @@
       <c r="I287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>445136</v>
+        <v>445621</v>
       </c>
       <c r="R287" t="n">
-        <v>6846374</v>
+        <v>6846493</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -30016,19 +30016,19 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>125046894</v>
+        <v>125046897</v>
       </c>
       <c r="B288" t="n">
         <v>78810</v>
@@ -30068,10 +30068,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>445621</v>
+        <v>445575</v>
       </c>
       <c r="R288" t="n">
-        <v>6846493</v>
+        <v>6846503</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -30130,7 +30130,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>125046897</v>
+        <v>125047133</v>
       </c>
       <c r="B289" t="n">
         <v>78810</v>
@@ -30170,10 +30170,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>445575</v>
+        <v>445672</v>
       </c>
       <c r="R289" t="n">
-        <v>6846503</v>
+        <v>6846269</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30232,7 +30232,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>125047133</v>
+        <v>125047095</v>
       </c>
       <c r="B290" t="n">
         <v>78810</v>
@@ -30272,10 +30272,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>445672</v>
+        <v>445182</v>
       </c>
       <c r="R290" t="n">
-        <v>6846269</v>
+        <v>6846438</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30334,7 +30334,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>125047095</v>
+        <v>125046910</v>
       </c>
       <c r="B291" t="n">
         <v>78810</v>
@@ -30374,10 +30374,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>445182</v>
+        <v>445493</v>
       </c>
       <c r="R291" t="n">
-        <v>6846438</v>
+        <v>6846458</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30436,7 +30436,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>125046910</v>
+        <v>125047088</v>
       </c>
       <c r="B292" t="n">
         <v>78810</v>
@@ -30476,10 +30476,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>445493</v>
+        <v>445132</v>
       </c>
       <c r="R292" t="n">
-        <v>6846458</v>
+        <v>6846422</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30538,7 +30538,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>125047088</v>
+        <v>125046846</v>
       </c>
       <c r="B293" t="n">
         <v>78810</v>
@@ -30578,10 +30578,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>445132</v>
+        <v>445508</v>
       </c>
       <c r="R293" t="n">
-        <v>6846422</v>
+        <v>6846149</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -30640,10 +30640,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>125046846</v>
+        <v>125046693</v>
       </c>
       <c r="B294" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30656,21 +30656,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -30680,10 +30680,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>445508</v>
+        <v>445542</v>
       </c>
       <c r="R294" t="n">
-        <v>6846149</v>
+        <v>6846225</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30742,10 +30742,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>125046693</v>
+        <v>125046765</v>
       </c>
       <c r="B295" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -30758,34 +30758,39 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P295" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>445542</v>
+        <v>445635</v>
       </c>
       <c r="R295" t="n">
-        <v>6846225</v>
+        <v>6846282</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30818,6 +30823,11 @@
       <c r="AA295" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>Äldre ringack (gran)</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -30844,10 +30854,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>125046765</v>
+        <v>125033575</v>
       </c>
       <c r="B296" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -30860,39 +30870,34 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>445635</v>
+        <v>445136</v>
       </c>
       <c r="R296" t="n">
-        <v>6846282</v>
+        <v>6846374</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30927,11 +30932,6 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>Äldre ringack (gran)</t>
-        </is>
-      </c>
       <c r="AD296" t="b">
         <v>0</v>
       </c>
@@ -30944,12 +30944,12 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125043335</v>
+        <v>125046898</v>
       </c>
       <c r="B328" t="n">
         <v>78810</v>
@@ -34154,17 +34154,17 @@
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>445762</v>
+        <v>445556</v>
       </c>
       <c r="R328" t="n">
-        <v>6846422</v>
+        <v>6846502</v>
       </c>
       <c r="S328" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -34208,19 +34208,19 @@
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>125046898</v>
+        <v>125047104</v>
       </c>
       <c r="B329" t="n">
         <v>78810</v>
@@ -34260,10 +34260,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>445556</v>
+        <v>445274</v>
       </c>
       <c r="R329" t="n">
-        <v>6846502</v>
+        <v>6846518</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -34322,7 +34322,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125047104</v>
+        <v>125046930</v>
       </c>
       <c r="B330" t="n">
         <v>78810</v>
@@ -34362,10 +34362,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>445274</v>
+        <v>445392</v>
       </c>
       <c r="R330" t="n">
-        <v>6846518</v>
+        <v>6846479</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -34424,7 +34424,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125046930</v>
+        <v>125047124</v>
       </c>
       <c r="B331" t="n">
         <v>78810</v>
@@ -34464,10 +34464,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>445392</v>
+        <v>445517</v>
       </c>
       <c r="R331" t="n">
-        <v>6846479</v>
+        <v>6846232</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -34526,7 +34526,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125047124</v>
+        <v>125047094</v>
       </c>
       <c r="B332" t="n">
         <v>78810</v>
@@ -34566,10 +34566,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>445517</v>
+        <v>445172</v>
       </c>
       <c r="R332" t="n">
-        <v>6846232</v>
+        <v>6846437</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -34628,7 +34628,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125047094</v>
+        <v>125046886</v>
       </c>
       <c r="B333" t="n">
         <v>78810</v>
@@ -34668,10 +34668,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>445172</v>
+        <v>445710</v>
       </c>
       <c r="R333" t="n">
-        <v>6846437</v>
+        <v>6846565</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -34730,7 +34730,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>125046886</v>
+        <v>125047102</v>
       </c>
       <c r="B334" t="n">
         <v>78810</v>
@@ -34770,10 +34770,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>445710</v>
+        <v>445259</v>
       </c>
       <c r="R334" t="n">
-        <v>6846565</v>
+        <v>6846504</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -34832,7 +34832,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125047102</v>
+        <v>125047106</v>
       </c>
       <c r="B335" t="n">
         <v>78810</v>
@@ -34872,10 +34872,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>445259</v>
+        <v>445294</v>
       </c>
       <c r="R335" t="n">
-        <v>6846504</v>
+        <v>6846511</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -34934,7 +34934,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125047106</v>
+        <v>125046942</v>
       </c>
       <c r="B336" t="n">
         <v>78810</v>
@@ -34974,10 +34974,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>445294</v>
+        <v>445174</v>
       </c>
       <c r="R336" t="n">
-        <v>6846511</v>
+        <v>6846523</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -35036,7 +35036,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125046942</v>
+        <v>125047125</v>
       </c>
       <c r="B337" t="n">
         <v>78810</v>
@@ -35076,10 +35076,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>445174</v>
+        <v>445547</v>
       </c>
       <c r="R337" t="n">
-        <v>6846523</v>
+        <v>6846233</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -35138,7 +35138,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125047125</v>
+        <v>125043335</v>
       </c>
       <c r="B338" t="n">
         <v>78810</v>
@@ -35174,17 +35174,17 @@
       <c r="I338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>445547</v>
+        <v>445762</v>
       </c>
       <c r="R338" t="n">
-        <v>6846233</v>
+        <v>6846422</v>
       </c>
       <c r="S338" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -35228,22 +35228,22 @@
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125042370</v>
+        <v>125042127</v>
       </c>
       <c r="B339" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -35256,21 +35256,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -35280,10 +35280,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>445558</v>
+        <v>445538</v>
       </c>
       <c r="R339" t="n">
-        <v>6846476</v>
+        <v>6846416</v>
       </c>
       <c r="S339" t="n">
         <v>20</v>
@@ -35342,10 +35342,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125042127</v>
+        <v>125042370</v>
       </c>
       <c r="B340" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -35358,21 +35358,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -35382,10 +35382,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>445538</v>
+        <v>445558</v>
       </c>
       <c r="R340" t="n">
-        <v>6846416</v>
+        <v>6846476</v>
       </c>
       <c r="S340" t="n">
         <v>20</v>
@@ -42507,7 +42507,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>125040082</v>
+        <v>125043358</v>
       </c>
       <c r="B410" t="n">
         <v>78842</v>
@@ -42543,14 +42543,14 @@
       <c r="I410" t="inlineStr"/>
       <c r="P410" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q410" t="n">
-        <v>445167</v>
+        <v>445763</v>
       </c>
       <c r="R410" t="n">
-        <v>6846498</v>
+        <v>6846407</v>
       </c>
       <c r="S410" t="n">
         <v>20</v>
@@ -42609,10 +42609,10 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>125043358</v>
+        <v>125044508</v>
       </c>
       <c r="B411" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
@@ -42625,21 +42625,21 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I411" t="inlineStr"/>
@@ -42649,10 +42649,10 @@
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>445763</v>
+        <v>445608</v>
       </c>
       <c r="R411" t="n">
-        <v>6846407</v>
+        <v>6846170</v>
       </c>
       <c r="S411" t="n">
         <v>20</v>
@@ -42711,10 +42711,10 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>125046890</v>
+        <v>125040082</v>
       </c>
       <c r="B412" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -42727,37 +42727,37 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I412" t="inlineStr"/>
       <c r="P412" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>445655</v>
+        <v>445167</v>
       </c>
       <c r="R412" t="n">
-        <v>6846538</v>
+        <v>6846498</v>
       </c>
       <c r="S412" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -42801,19 +42801,19 @@
       <c r="AT412" t="inlineStr"/>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>125046888</v>
+        <v>125046890</v>
       </c>
       <c r="B413" t="n">
         <v>78810</v>
@@ -42853,10 +42853,10 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>445691</v>
+        <v>445655</v>
       </c>
       <c r="R413" t="n">
-        <v>6846537</v>
+        <v>6846538</v>
       </c>
       <c r="S413" t="n">
         <v>10</v>
@@ -42915,10 +42915,10 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>125046791</v>
+        <v>125046888</v>
       </c>
       <c r="B414" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -42931,21 +42931,21 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I414" t="inlineStr"/>
@@ -42955,10 +42955,10 @@
         </is>
       </c>
       <c r="Q414" t="n">
-        <v>445291</v>
+        <v>445691</v>
       </c>
       <c r="R414" t="n">
-        <v>6846523</v>
+        <v>6846537</v>
       </c>
       <c r="S414" t="n">
         <v>10</v>
@@ -43017,10 +43017,10 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>125046795</v>
+        <v>125046791</v>
       </c>
       <c r="B415" t="n">
-        <v>80763</v>
+        <v>78547</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -43033,21 +43033,21 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I415" t="inlineStr"/>
@@ -43057,10 +43057,10 @@
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>445335</v>
+        <v>445291</v>
       </c>
       <c r="R415" t="n">
-        <v>6846442</v>
+        <v>6846523</v>
       </c>
       <c r="S415" t="n">
         <v>10</v>
@@ -43119,10 +43119,10 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>125046766</v>
+        <v>125046795</v>
       </c>
       <c r="B416" t="n">
-        <v>96979</v>
+        <v>80763</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -43131,25 +43131,25 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I416" t="inlineStr"/>
@@ -43159,10 +43159,10 @@
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>445478</v>
+        <v>445335</v>
       </c>
       <c r="R416" t="n">
-        <v>6846122</v>
+        <v>6846442</v>
       </c>
       <c r="S416" t="n">
         <v>10</v>
@@ -43221,10 +43221,10 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>125046924</v>
+        <v>125046766</v>
       </c>
       <c r="B417" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -43233,25 +43233,25 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I417" t="inlineStr"/>
@@ -43261,10 +43261,10 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>445502</v>
+        <v>445478</v>
       </c>
       <c r="R417" t="n">
-        <v>6846541</v>
+        <v>6846122</v>
       </c>
       <c r="S417" t="n">
         <v>10</v>
@@ -43323,7 +43323,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>125046944</v>
+        <v>125046924</v>
       </c>
       <c r="B418" t="n">
         <v>78810</v>
@@ -43363,10 +43363,10 @@
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>445137</v>
+        <v>445502</v>
       </c>
       <c r="R418" t="n">
-        <v>6846572</v>
+        <v>6846541</v>
       </c>
       <c r="S418" t="n">
         <v>10</v>
@@ -43425,7 +43425,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>125046908</v>
+        <v>125046944</v>
       </c>
       <c r="B419" t="n">
         <v>78810</v>
@@ -43465,10 +43465,10 @@
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>445514</v>
+        <v>445137</v>
       </c>
       <c r="R419" t="n">
-        <v>6846439</v>
+        <v>6846572</v>
       </c>
       <c r="S419" t="n">
         <v>10</v>
@@ -43527,7 +43527,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>125046873</v>
+        <v>125046908</v>
       </c>
       <c r="B420" t="n">
         <v>78810</v>
@@ -43567,10 +43567,10 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>445796</v>
+        <v>445514</v>
       </c>
       <c r="R420" t="n">
-        <v>6846481</v>
+        <v>6846439</v>
       </c>
       <c r="S420" t="n">
         <v>10</v>
@@ -43629,10 +43629,10 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>125046662</v>
+        <v>125046873</v>
       </c>
       <c r="B421" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -43645,21 +43645,21 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I421" t="inlineStr"/>
@@ -43669,10 +43669,10 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>445499</v>
+        <v>445796</v>
       </c>
       <c r="R421" t="n">
-        <v>6846505</v>
+        <v>6846481</v>
       </c>
       <c r="S421" t="n">
         <v>10</v>
@@ -43731,7 +43731,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>125046618</v>
+        <v>125046662</v>
       </c>
       <c r="B422" t="n">
         <v>78842</v>
@@ -43771,10 +43771,10 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>445478</v>
+        <v>445499</v>
       </c>
       <c r="R422" t="n">
-        <v>6846122</v>
+        <v>6846505</v>
       </c>
       <c r="S422" t="n">
         <v>10</v>
@@ -43833,7 +43833,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>125046632</v>
+        <v>125046618</v>
       </c>
       <c r="B423" t="n">
         <v>78842</v>
@@ -43873,10 +43873,10 @@
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>445747</v>
+        <v>445478</v>
       </c>
       <c r="R423" t="n">
-        <v>6846595</v>
+        <v>6846122</v>
       </c>
       <c r="S423" t="n">
         <v>10</v>
@@ -43935,10 +43935,10 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>125044508</v>
+        <v>125046632</v>
       </c>
       <c r="B424" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -43951,37 +43951,37 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
       <c r="P424" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>445608</v>
+        <v>445747</v>
       </c>
       <c r="R424" t="n">
-        <v>6846170</v>
+        <v>6846595</v>
       </c>
       <c r="S424" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -44025,22 +44025,22 @@
       <c r="AT424" t="inlineStr"/>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>125033647</v>
+        <v>125046848</v>
       </c>
       <c r="B425" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -44053,37 +44053,37 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I425" t="inlineStr"/>
       <c r="P425" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>445123</v>
+        <v>445555</v>
       </c>
       <c r="R425" t="n">
-        <v>6846347</v>
+        <v>6846181</v>
       </c>
       <c r="S425" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -44127,22 +44127,22 @@
       <c r="AT425" t="inlineStr"/>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>125046848</v>
+        <v>125046647</v>
       </c>
       <c r="B426" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -44155,21 +44155,21 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
@@ -44179,10 +44179,10 @@
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>445555</v>
+        <v>445561</v>
       </c>
       <c r="R426" t="n">
-        <v>6846181</v>
+        <v>6846419</v>
       </c>
       <c r="S426" t="n">
         <v>10</v>
@@ -44241,7 +44241,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>125046647</v>
+        <v>125046636</v>
       </c>
       <c r="B427" t="n">
         <v>78842</v>
@@ -44281,10 +44281,10 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>445561</v>
+        <v>445630</v>
       </c>
       <c r="R427" t="n">
-        <v>6846419</v>
+        <v>6846498</v>
       </c>
       <c r="S427" t="n">
         <v>10</v>
@@ -44343,10 +44343,10 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>125046636</v>
+        <v>125046905</v>
       </c>
       <c r="B428" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -44359,21 +44359,21 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I428" t="inlineStr"/>
@@ -44383,10 +44383,10 @@
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>445630</v>
+        <v>445540</v>
       </c>
       <c r="R428" t="n">
-        <v>6846498</v>
+        <v>6846396</v>
       </c>
       <c r="S428" t="n">
         <v>10</v>
@@ -44445,7 +44445,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>125046905</v>
+        <v>125046880</v>
       </c>
       <c r="B429" t="n">
         <v>78810</v>
@@ -44485,10 +44485,10 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>445540</v>
+        <v>445762</v>
       </c>
       <c r="R429" t="n">
-        <v>6846396</v>
+        <v>6846576</v>
       </c>
       <c r="S429" t="n">
         <v>10</v>
@@ -44547,7 +44547,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>125046880</v>
+        <v>125046844</v>
       </c>
       <c r="B430" t="n">
         <v>78810</v>
@@ -44587,10 +44587,10 @@
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>445762</v>
+        <v>445468</v>
       </c>
       <c r="R430" t="n">
-        <v>6846576</v>
+        <v>6846114</v>
       </c>
       <c r="S430" t="n">
         <v>10</v>
@@ -44649,7 +44649,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>125046844</v>
+        <v>125046862</v>
       </c>
       <c r="B431" t="n">
         <v>78810</v>
@@ -44689,10 +44689,10 @@
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>445468</v>
+        <v>445729</v>
       </c>
       <c r="R431" t="n">
-        <v>6846114</v>
+        <v>6846371</v>
       </c>
       <c r="S431" t="n">
         <v>10</v>
@@ -44751,10 +44751,10 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>125046862</v>
+        <v>125046700</v>
       </c>
       <c r="B432" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -44767,21 +44767,21 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I432" t="inlineStr"/>
@@ -44791,10 +44791,10 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>445729</v>
+        <v>445180</v>
       </c>
       <c r="R432" t="n">
-        <v>6846371</v>
+        <v>6846446</v>
       </c>
       <c r="S432" t="n">
         <v>10</v>
@@ -44853,10 +44853,10 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>125046700</v>
+        <v>125046906</v>
       </c>
       <c r="B433" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -44869,21 +44869,21 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I433" t="inlineStr"/>
@@ -44893,10 +44893,10 @@
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>445180</v>
+        <v>445543</v>
       </c>
       <c r="R433" t="n">
-        <v>6846446</v>
+        <v>6846371</v>
       </c>
       <c r="S433" t="n">
         <v>10</v>
@@ -44955,10 +44955,10 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>125046906</v>
+        <v>125046803</v>
       </c>
       <c r="B434" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -44971,21 +44971,21 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I434" t="inlineStr"/>
@@ -44995,10 +44995,10 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>445543</v>
+        <v>445455</v>
       </c>
       <c r="R434" t="n">
-        <v>6846371</v>
+        <v>6846258</v>
       </c>
       <c r="S434" t="n">
         <v>10</v>
@@ -45057,10 +45057,10 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>125046803</v>
+        <v>125047080</v>
       </c>
       <c r="B435" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -45073,21 +45073,21 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I435" t="inlineStr"/>
@@ -45097,10 +45097,10 @@
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>445455</v>
+        <v>445110</v>
       </c>
       <c r="R435" t="n">
-        <v>6846258</v>
+        <v>6846348</v>
       </c>
       <c r="S435" t="n">
         <v>10</v>
@@ -45159,7 +45159,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>125047080</v>
+        <v>125047115</v>
       </c>
       <c r="B436" t="n">
         <v>78810</v>
@@ -45199,10 +45199,10 @@
         </is>
       </c>
       <c r="Q436" t="n">
-        <v>445110</v>
+        <v>445409</v>
       </c>
       <c r="R436" t="n">
-        <v>6846348</v>
+        <v>6846412</v>
       </c>
       <c r="S436" t="n">
         <v>10</v>
@@ -45261,10 +45261,10 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>125047115</v>
+        <v>125046624</v>
       </c>
       <c r="B437" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -45277,21 +45277,21 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I437" t="inlineStr"/>
@@ -45301,10 +45301,10 @@
         </is>
       </c>
       <c r="Q437" t="n">
-        <v>445409</v>
+        <v>445700</v>
       </c>
       <c r="R437" t="n">
-        <v>6846412</v>
+        <v>6846331</v>
       </c>
       <c r="S437" t="n">
         <v>10</v>
@@ -45363,7 +45363,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>125046624</v>
+        <v>125046628</v>
       </c>
       <c r="B438" t="n">
         <v>78842</v>
@@ -45403,10 +45403,10 @@
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>445700</v>
+        <v>445792</v>
       </c>
       <c r="R438" t="n">
-        <v>6846331</v>
+        <v>6846472</v>
       </c>
       <c r="S438" t="n">
         <v>10</v>
@@ -45465,10 +45465,10 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>125046628</v>
+        <v>125046895</v>
       </c>
       <c r="B439" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -45481,21 +45481,21 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I439" t="inlineStr"/>
@@ -45505,10 +45505,10 @@
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>445792</v>
+        <v>445603</v>
       </c>
       <c r="R439" t="n">
-        <v>6846472</v>
+        <v>6846478</v>
       </c>
       <c r="S439" t="n">
         <v>10</v>
@@ -45567,7 +45567,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>125046895</v>
+        <v>125046841</v>
       </c>
       <c r="B440" t="n">
         <v>78810</v>
@@ -45607,10 +45607,10 @@
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>445603</v>
+        <v>445451</v>
       </c>
       <c r="R440" t="n">
-        <v>6846478</v>
+        <v>6846042</v>
       </c>
       <c r="S440" t="n">
         <v>10</v>
@@ -45669,10 +45669,10 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>125046841</v>
+        <v>125047151</v>
       </c>
       <c r="B441" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -45685,34 +45685,39 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I441" t="inlineStr"/>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P441" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>445451</v>
+        <v>445414</v>
       </c>
       <c r="R441" t="n">
-        <v>6846042</v>
+        <v>6846069</v>
       </c>
       <c r="S441" t="n">
         <v>10</v>
@@ -45771,10 +45776,10 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>125047151</v>
+        <v>125046614</v>
       </c>
       <c r="B442" t="n">
-        <v>57513</v>
+        <v>78842</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -45787,39 +45792,34 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I442" t="inlineStr"/>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P442" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>445414</v>
+        <v>445418</v>
       </c>
       <c r="R442" t="n">
-        <v>6846069</v>
+        <v>6846058</v>
       </c>
       <c r="S442" t="n">
         <v>10</v>
@@ -45878,10 +45878,10 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>125046614</v>
+        <v>125033647</v>
       </c>
       <c r="B443" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -45894,37 +45894,37 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I443" t="inlineStr"/>
       <c r="P443" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q443" t="n">
-        <v>445418</v>
+        <v>445123</v>
       </c>
       <c r="R443" t="n">
-        <v>6846058</v>
+        <v>6846347</v>
       </c>
       <c r="S443" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
@@ -45968,12 +45968,12 @@
       <c r="AT443" t="inlineStr"/>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
@@ -54874,10 +54874,10 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>125043897</v>
+        <v>125046784</v>
       </c>
       <c r="B531" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
@@ -54890,37 +54890,37 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I531" t="inlineStr"/>
       <c r="P531" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q531" t="n">
-        <v>445742</v>
+        <v>445501</v>
       </c>
       <c r="R531" t="n">
-        <v>6846386</v>
+        <v>6846560</v>
       </c>
       <c r="S531" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
@@ -54964,22 +54964,22 @@
       <c r="AT531" t="inlineStr"/>
       <c r="AW531" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX531" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>125043041</v>
+        <v>125046687</v>
       </c>
       <c r="B532" t="n">
-        <v>91184</v>
+        <v>78842</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -54992,37 +54992,37 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>1588</v>
+        <v>185</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I532" t="inlineStr"/>
       <c r="P532" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q532" t="n">
-        <v>445711</v>
+        <v>445390</v>
       </c>
       <c r="R532" t="n">
-        <v>6846458</v>
+        <v>6846346</v>
       </c>
       <c r="S532" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -55066,19 +55066,19 @@
       <c r="AT532" t="inlineStr"/>
       <c r="AW532" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX532" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>125042918</v>
+        <v>125047077</v>
       </c>
       <c r="B533" t="n">
         <v>78810</v>
@@ -55114,14 +55114,14 @@
       <c r="I533" t="inlineStr"/>
       <c r="P533" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q533" t="n">
-        <v>445731</v>
+        <v>445108</v>
       </c>
       <c r="R533" t="n">
-        <v>6846458</v>
+        <v>6846332</v>
       </c>
       <c r="S533" t="n">
         <v>10</v>
@@ -55168,22 +55168,22 @@
       <c r="AT533" t="inlineStr"/>
       <c r="AW533" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX533" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>125042795</v>
+        <v>125046885</v>
       </c>
       <c r="B534" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -55192,41 +55192,41 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E534" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I534" t="inlineStr"/>
       <c r="P534" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q534" t="n">
-        <v>445688</v>
+        <v>445732</v>
       </c>
       <c r="R534" t="n">
-        <v>6846464</v>
+        <v>6846592</v>
       </c>
       <c r="S534" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T534" t="inlineStr">
         <is>
@@ -55270,19 +55270,19 @@
       <c r="AT534" t="inlineStr"/>
       <c r="AW534" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX534" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>125042197</v>
+        <v>125046692</v>
       </c>
       <c r="B535" t="n">
         <v>78842</v>
@@ -55318,17 +55318,17 @@
       <c r="I535" t="inlineStr"/>
       <c r="P535" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q535" t="n">
-        <v>445544</v>
+        <v>445427</v>
       </c>
       <c r="R535" t="n">
-        <v>6846442</v>
+        <v>6846297</v>
       </c>
       <c r="S535" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T535" t="inlineStr">
         <is>
@@ -55372,22 +55372,22 @@
       <c r="AT535" t="inlineStr"/>
       <c r="AW535" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX535" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>125046784</v>
+        <v>125047113</v>
       </c>
       <c r="B536" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
@@ -55400,21 +55400,21 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I536" t="inlineStr"/>
@@ -55424,10 +55424,10 @@
         </is>
       </c>
       <c r="Q536" t="n">
-        <v>445501</v>
+        <v>445420</v>
       </c>
       <c r="R536" t="n">
-        <v>6846560</v>
+        <v>6846444</v>
       </c>
       <c r="S536" t="n">
         <v>10</v>
@@ -55486,10 +55486,10 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>125046687</v>
+        <v>125047161</v>
       </c>
       <c r="B537" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
@@ -55502,34 +55502,39 @@
         </is>
       </c>
       <c r="E537" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I537" t="inlineStr"/>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P537" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q537" t="n">
-        <v>445390</v>
+        <v>445120</v>
       </c>
       <c r="R537" t="n">
-        <v>6846346</v>
+        <v>6846397</v>
       </c>
       <c r="S537" t="n">
         <v>10</v>
@@ -55588,7 +55593,7 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>125047077</v>
+        <v>125046847</v>
       </c>
       <c r="B538" t="n">
         <v>78810</v>
@@ -55628,10 +55633,10 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>445108</v>
+        <v>445518</v>
       </c>
       <c r="R538" t="n">
-        <v>6846332</v>
+        <v>6846152</v>
       </c>
       <c r="S538" t="n">
         <v>10</v>
@@ -55690,10 +55695,10 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>125046885</v>
+        <v>125046630</v>
       </c>
       <c r="B539" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -55706,21 +55711,21 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I539" t="inlineStr"/>
@@ -55730,10 +55735,10 @@
         </is>
       </c>
       <c r="Q539" t="n">
-        <v>445732</v>
+        <v>445773</v>
       </c>
       <c r="R539" t="n">
-        <v>6846592</v>
+        <v>6846524</v>
       </c>
       <c r="S539" t="n">
         <v>10</v>
@@ -55792,7 +55797,7 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>125046692</v>
+        <v>125046625</v>
       </c>
       <c r="B540" t="n">
         <v>78842</v>
@@ -55832,10 +55837,10 @@
         </is>
       </c>
       <c r="Q540" t="n">
-        <v>445427</v>
+        <v>445730</v>
       </c>
       <c r="R540" t="n">
-        <v>6846297</v>
+        <v>6846366</v>
       </c>
       <c r="S540" t="n">
         <v>10</v>
@@ -55894,10 +55899,10 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>125047113</v>
+        <v>125046649</v>
       </c>
       <c r="B541" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -55910,21 +55915,21 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I541" t="inlineStr"/>
@@ -55934,10 +55939,10 @@
         </is>
       </c>
       <c r="Q541" t="n">
-        <v>445420</v>
+        <v>445544</v>
       </c>
       <c r="R541" t="n">
-        <v>6846444</v>
+        <v>6846404</v>
       </c>
       <c r="S541" t="n">
         <v>10</v>
@@ -55996,10 +56001,10 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>125047161</v>
+        <v>125046907</v>
       </c>
       <c r="B542" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -56012,39 +56017,34 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr"/>
-      <c r="M542" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P542" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q542" t="n">
-        <v>445120</v>
+        <v>445512</v>
       </c>
       <c r="R542" t="n">
-        <v>6846397</v>
+        <v>6846409</v>
       </c>
       <c r="S542" t="n">
         <v>10</v>
@@ -56103,10 +56103,10 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>125046847</v>
+        <v>125046587</v>
       </c>
       <c r="B543" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -56119,21 +56119,21 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I543" t="inlineStr"/>
@@ -56143,10 +56143,10 @@
         </is>
       </c>
       <c r="Q543" t="n">
-        <v>445518</v>
+        <v>445305</v>
       </c>
       <c r="R543" t="n">
-        <v>6846152</v>
+        <v>6846480</v>
       </c>
       <c r="S543" t="n">
         <v>10</v>
@@ -56205,10 +56205,10 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>125046630</v>
+        <v>125046891</v>
       </c>
       <c r="B544" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -56221,21 +56221,21 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I544" t="inlineStr"/>
@@ -56245,7 +56245,7 @@
         </is>
       </c>
       <c r="Q544" t="n">
-        <v>445773</v>
+        <v>445648</v>
       </c>
       <c r="R544" t="n">
         <v>6846524</v>
@@ -56307,10 +56307,10 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>125046625</v>
+        <v>125046904</v>
       </c>
       <c r="B545" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -56323,21 +56323,21 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I545" t="inlineStr"/>
@@ -56347,10 +56347,10 @@
         </is>
       </c>
       <c r="Q545" t="n">
-        <v>445730</v>
+        <v>445552</v>
       </c>
       <c r="R545" t="n">
-        <v>6846366</v>
+        <v>6846413</v>
       </c>
       <c r="S545" t="n">
         <v>10</v>
@@ -56409,10 +56409,10 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>125046649</v>
+        <v>125043041</v>
       </c>
       <c r="B546" t="n">
-        <v>78842</v>
+        <v>91184</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -56425,37 +56425,37 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>185</v>
+        <v>1588</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
       <c r="P546" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q546" t="n">
-        <v>445544</v>
+        <v>445711</v>
       </c>
       <c r="R546" t="n">
-        <v>6846404</v>
+        <v>6846458</v>
       </c>
       <c r="S546" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -56499,19 +56499,19 @@
       <c r="AT546" t="inlineStr"/>
       <c r="AW546" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX546" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>125046907</v>
+        <v>125042918</v>
       </c>
       <c r="B547" t="n">
         <v>78810</v>
@@ -56547,14 +56547,14 @@
       <c r="I547" t="inlineStr"/>
       <c r="P547" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q547" t="n">
-        <v>445512</v>
+        <v>445731</v>
       </c>
       <c r="R547" t="n">
-        <v>6846409</v>
+        <v>6846458</v>
       </c>
       <c r="S547" t="n">
         <v>10</v>
@@ -56601,22 +56601,22 @@
       <c r="AT547" t="inlineStr"/>
       <c r="AW547" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX547" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>125046587</v>
+        <v>125042795</v>
       </c>
       <c r="B548" t="n">
-        <v>79428</v>
+        <v>90977</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -56625,41 +56625,41 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I548" t="inlineStr"/>
       <c r="P548" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q548" t="n">
-        <v>445305</v>
+        <v>445688</v>
       </c>
       <c r="R548" t="n">
-        <v>6846480</v>
+        <v>6846464</v>
       </c>
       <c r="S548" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -56703,22 +56703,22 @@
       <c r="AT548" t="inlineStr"/>
       <c r="AW548" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX548" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>125046891</v>
+        <v>125042197</v>
       </c>
       <c r="B549" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -56731,37 +56731,37 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I549" t="inlineStr"/>
       <c r="P549" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q549" t="n">
-        <v>445648</v>
+        <v>445544</v>
       </c>
       <c r="R549" t="n">
-        <v>6846524</v>
+        <v>6846442</v>
       </c>
       <c r="S549" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -56805,22 +56805,22 @@
       <c r="AT549" t="inlineStr"/>
       <c r="AW549" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX549" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>125046904</v>
+        <v>125043897</v>
       </c>
       <c r="B550" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -56833,37 +56833,37 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
       <c r="P550" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q550" t="n">
-        <v>445552</v>
+        <v>445742</v>
       </c>
       <c r="R550" t="n">
-        <v>6846413</v>
+        <v>6846386</v>
       </c>
       <c r="S550" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -56907,15 +56907,118 @@
       <c r="AT550" t="inlineStr"/>
       <c r="AW550" t="inlineStr">
         <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX550" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>125047177</v>
+      </c>
+      <c r="B551" t="n">
+        <v>91369</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>Stor Åndberg, Hjd</t>
+        </is>
+      </c>
+      <c r="Q551" t="n">
+        <v>445551</v>
+      </c>
+      <c r="R551" t="n">
+        <v>6846478</v>
+      </c>
+      <c r="S551" t="n">
+        <v>10</v>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD551" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE551" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF551" t="inlineStr"/>
+      <c r="AG551" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT551" t="inlineStr"/>
+      <c r="AW551" t="inlineStr">
+        <is>
           <t>Philipp Weiss</t>
         </is>
       </c>
-      <c r="AX550" t="inlineStr">
+      <c r="AX551" t="inlineStr">
         <is>
           <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
-      <c r="AY550" t="inlineStr"/>
+      <c r="AY551" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18557-2025 artfynd.xlsx
+++ b/artfynd/A 18557-2025 artfynd.xlsx
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125046715</v>
+        <v>125036045</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,37 +1704,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444737</v>
+        <v>444513</v>
       </c>
       <c r="R11" t="n">
-        <v>6846216</v>
+        <v>6846156</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,22 +1778,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125046707</v>
+        <v>125046948</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444962</v>
+        <v>445066</v>
       </c>
       <c r="R12" t="n">
-        <v>6846424</v>
+        <v>6846537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125047040</v>
+        <v>125046599</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444637</v>
+        <v>444520</v>
       </c>
       <c r="R13" t="n">
-        <v>6846198</v>
+        <v>6846480</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125047060</v>
+        <v>125046604</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,21 +2010,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444847</v>
+        <v>444838</v>
       </c>
       <c r="R14" t="n">
-        <v>6846296</v>
+        <v>6846288</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125036045</v>
+        <v>125046715</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,37 +2112,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444513</v>
+        <v>444737</v>
       </c>
       <c r="R15" t="n">
-        <v>6846156</v>
+        <v>6846216</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,19 +2186,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125046948</v>
+        <v>125047040</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445066</v>
+        <v>444637</v>
       </c>
       <c r="R16" t="n">
-        <v>6846537</v>
+        <v>6846198</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125046599</v>
+        <v>125047060</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444520</v>
+        <v>444847</v>
       </c>
       <c r="R17" t="n">
-        <v>6846480</v>
+        <v>6846296</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125046604</v>
+        <v>125046728</v>
       </c>
       <c r="B18" t="n">
-        <v>79428</v>
+        <v>78905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444838</v>
+        <v>444671</v>
       </c>
       <c r="R18" t="n">
-        <v>6846288</v>
+        <v>6846500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125046728</v>
+        <v>125046707</v>
       </c>
       <c r="B19" t="n">
-        <v>78905</v>
+        <v>79399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444671</v>
+        <v>444962</v>
       </c>
       <c r="R19" t="n">
-        <v>6846500</v>
+        <v>6846424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125047068</v>
+        <v>125046763</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,34 +2728,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444956</v>
+        <v>444582</v>
       </c>
       <c r="R21" t="n">
-        <v>6846307</v>
+        <v>6846569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,6 +2793,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringack (tall)</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2824,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125047013</v>
+        <v>125047068</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2854,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444487</v>
+        <v>444956</v>
       </c>
       <c r="R22" t="n">
-        <v>6846211</v>
+        <v>6846307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,7 +2926,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125046998</v>
+        <v>125047013</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2956,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444547</v>
+        <v>444487</v>
       </c>
       <c r="R23" t="n">
-        <v>6846345</v>
+        <v>6846211</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3028,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125047049</v>
+        <v>125046998</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3058,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444730</v>
+        <v>444547</v>
       </c>
       <c r="R24" t="n">
-        <v>6846168</v>
+        <v>6846345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3130,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125033797</v>
+        <v>125047049</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3156,17 +3166,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445008</v>
+        <v>444730</v>
       </c>
       <c r="R25" t="n">
-        <v>6846306</v>
+        <v>6846168</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3210,19 +3220,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125035654</v>
+        <v>125033797</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3262,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444640</v>
+        <v>445008</v>
       </c>
       <c r="R26" t="n">
-        <v>6846141</v>
+        <v>6846306</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3324,7 +3334,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039886</v>
+        <v>125035654</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3360,14 +3370,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445091</v>
+        <v>444640</v>
       </c>
       <c r="R27" t="n">
-        <v>6846446</v>
+        <v>6846141</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3426,7 +3436,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125047017</v>
+        <v>125039886</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3462,17 +3472,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444488</v>
+        <v>445091</v>
       </c>
       <c r="R28" t="n">
-        <v>6846179</v>
+        <v>6846446</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3516,22 +3526,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125038002</v>
+        <v>125047017</v>
       </c>
       <c r="B29" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,37 +3554,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444706</v>
+        <v>444488</v>
       </c>
       <c r="R29" t="n">
-        <v>6846458</v>
+        <v>6846179</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3618,22 +3628,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125046797</v>
+        <v>125038002</v>
       </c>
       <c r="B30" t="n">
-        <v>80763</v>
+        <v>78905</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,37 +3656,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>967</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444830</v>
+        <v>444706</v>
       </c>
       <c r="R30" t="n">
-        <v>6846275</v>
+        <v>6846458</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3720,22 +3730,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125047048</v>
+        <v>125046797</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,21 +3758,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3772,10 +3782,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444728</v>
+        <v>444830</v>
       </c>
       <c r="R31" t="n">
-        <v>6846177</v>
+        <v>6846275</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125046763</v>
+        <v>125047048</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,39 +3860,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444582</v>
+        <v>444728</v>
       </c>
       <c r="R32" t="n">
-        <v>6846569</v>
+        <v>6846177</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3915,11 +3920,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringack (tall)</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -6812,7 +6812,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125046976</v>
+        <v>125047042</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444542</v>
+        <v>444654</v>
       </c>
       <c r="R61" t="n">
-        <v>6846558</v>
+        <v>6846208</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125047042</v>
+        <v>125046595</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444654</v>
+        <v>444605</v>
       </c>
       <c r="R62" t="n">
-        <v>6846208</v>
+        <v>6846502</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125046595</v>
+        <v>125038292</v>
       </c>
       <c r="B63" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7032,37 +7032,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444605</v>
+        <v>444761</v>
       </c>
       <c r="R63" t="n">
-        <v>6846502</v>
+        <v>6846496</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7106,22 +7106,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125038292</v>
+        <v>125046671</v>
       </c>
       <c r="B64" t="n">
-        <v>77738</v>
+        <v>78842</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7134,37 +7134,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444761</v>
+        <v>444533</v>
       </c>
       <c r="R64" t="n">
-        <v>6846496</v>
+        <v>6846410</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7208,22 +7208,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125047007</v>
+        <v>125046673</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7236,21 +7236,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444499</v>
+        <v>444495</v>
       </c>
       <c r="R65" t="n">
-        <v>6846245</v>
+        <v>6846210</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7322,10 +7322,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125034509</v>
+        <v>125038823</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7338,34 +7338,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444763</v>
+        <v>444858</v>
       </c>
       <c r="R66" t="n">
-        <v>6846122</v>
+        <v>6846569</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7424,10 +7424,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125035805</v>
+        <v>125046720</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7440,37 +7440,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444541</v>
+        <v>445092</v>
       </c>
       <c r="R67" t="n">
-        <v>6846159</v>
+        <v>6846328</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,19 +7514,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125047074</v>
+        <v>125046976</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445047</v>
+        <v>444542</v>
       </c>
       <c r="R68" t="n">
-        <v>6846330</v>
+        <v>6846558</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125046963</v>
+        <v>125047007</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444710</v>
+        <v>444499</v>
       </c>
       <c r="R69" t="n">
-        <v>6846480</v>
+        <v>6846245</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125046965</v>
+        <v>125034509</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7766,17 +7766,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444601</v>
+        <v>444763</v>
       </c>
       <c r="R70" t="n">
-        <v>6846489</v>
+        <v>6846122</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7820,19 +7820,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125046981</v>
+        <v>125035805</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7868,17 +7868,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444537</v>
+        <v>444541</v>
       </c>
       <c r="R71" t="n">
-        <v>6846522</v>
+        <v>6846159</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7922,22 +7922,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125046671</v>
+        <v>125047074</v>
       </c>
       <c r="B72" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7950,21 +7950,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444533</v>
+        <v>445047</v>
       </c>
       <c r="R72" t="n">
-        <v>6846410</v>
+        <v>6846330</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125046673</v>
+        <v>125046963</v>
       </c>
       <c r="B73" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8052,21 +8052,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444495</v>
+        <v>444710</v>
       </c>
       <c r="R73" t="n">
-        <v>6846210</v>
+        <v>6846480</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125038823</v>
+        <v>125046965</v>
       </c>
       <c r="B74" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8154,37 +8154,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444858</v>
+        <v>444601</v>
       </c>
       <c r="R74" t="n">
-        <v>6846569</v>
+        <v>6846489</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8228,22 +8228,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125046720</v>
+        <v>125046981</v>
       </c>
       <c r="B75" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445092</v>
+        <v>444537</v>
       </c>
       <c r="R75" t="n">
-        <v>6846328</v>
+        <v>6846522</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9265,10 +9265,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125047157</v>
+        <v>125046959</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9281,39 +9281,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444505</v>
+        <v>444778</v>
       </c>
       <c r="R85" t="n">
-        <v>6846397</v>
+        <v>6846468</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9372,10 +9367,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125046711</v>
+        <v>125046814</v>
       </c>
       <c r="B86" t="n">
-        <v>79399</v>
+        <v>91030</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9388,21 +9383,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9412,10 +9407,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444558</v>
+        <v>444486</v>
       </c>
       <c r="R86" t="n">
-        <v>6846340</v>
+        <v>6846184</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9474,10 +9469,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125046706</v>
+        <v>125046993</v>
       </c>
       <c r="B87" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9490,21 +9485,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9514,10 +9509,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445022</v>
+        <v>444504</v>
       </c>
       <c r="R87" t="n">
-        <v>6846542</v>
+        <v>6846395</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9576,7 +9571,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125046959</v>
+        <v>125047084</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9616,10 +9611,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444778</v>
+        <v>445085</v>
       </c>
       <c r="R88" t="n">
-        <v>6846468</v>
+        <v>6846391</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9678,10 +9673,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125046814</v>
+        <v>125047070</v>
       </c>
       <c r="B89" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9694,21 +9689,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9718,10 +9713,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444486</v>
+        <v>445000</v>
       </c>
       <c r="R89" t="n">
-        <v>6846184</v>
+        <v>6846312</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9780,7 +9775,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125046993</v>
+        <v>125039020</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9816,17 +9811,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444504</v>
+        <v>444897</v>
       </c>
       <c r="R90" t="n">
-        <v>6846395</v>
+        <v>6846564</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9870,22 +9865,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125047084</v>
+        <v>125047157</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9898,34 +9893,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445085</v>
+        <v>444505</v>
       </c>
       <c r="R91" t="n">
-        <v>6846391</v>
+        <v>6846397</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10290,10 +10290,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125047070</v>
+        <v>125046711</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445000</v>
+        <v>444558</v>
       </c>
       <c r="R95" t="n">
-        <v>6846312</v>
+        <v>6846340</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125039020</v>
+        <v>125046706</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10408,37 +10408,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444897</v>
+        <v>445022</v>
       </c>
       <c r="R96" t="n">
-        <v>6846564</v>
+        <v>6846542</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10482,12 +10482,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -13962,7 +13962,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125047063</v>
+        <v>125047033</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14002,10 +14002,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444866</v>
+        <v>444600</v>
       </c>
       <c r="R131" t="n">
-        <v>6846312</v>
+        <v>6846124</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14064,7 +14064,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125035586</v>
+        <v>125047047</v>
       </c>
       <c r="B132" t="n">
         <v>78810</v>
@@ -14100,14 +14100,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444620</v>
+        <v>444740</v>
       </c>
       <c r="R132" t="n">
-        <v>6846127</v>
+        <v>6846228</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14154,19 +14154,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125047005</v>
+        <v>125047063</v>
       </c>
       <c r="B133" t="n">
         <v>78810</v>
@@ -14206,10 +14206,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444494</v>
+        <v>444866</v>
       </c>
       <c r="R133" t="n">
-        <v>6846271</v>
+        <v>6846312</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14268,7 +14268,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125046966</v>
+        <v>125035586</v>
       </c>
       <c r="B134" t="n">
         <v>78810</v>
@@ -14304,14 +14304,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444600</v>
+        <v>444620</v>
       </c>
       <c r="R134" t="n">
-        <v>6846520</v>
+        <v>6846127</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14358,19 +14358,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125037824</v>
+        <v>125047005</v>
       </c>
       <c r="B135" t="n">
         <v>78810</v>
@@ -14406,17 +14406,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444709</v>
+        <v>444494</v>
       </c>
       <c r="R135" t="n">
-        <v>6846425</v>
+        <v>6846271</v>
       </c>
       <c r="S135" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14460,19 +14460,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125047033</v>
+        <v>125046966</v>
       </c>
       <c r="B136" t="n">
         <v>78810</v>
@@ -14515,7 +14515,7 @@
         <v>444600</v>
       </c>
       <c r="R136" t="n">
-        <v>6846124</v>
+        <v>6846520</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14574,7 +14574,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125047047</v>
+        <v>125037824</v>
       </c>
       <c r="B137" t="n">
         <v>78810</v>
@@ -14610,17 +14610,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444740</v>
+        <v>444709</v>
       </c>
       <c r="R137" t="n">
-        <v>6846228</v>
+        <v>6846425</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14664,12 +14664,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -15089,10 +15089,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125046960</v>
+        <v>125037692</v>
       </c>
       <c r="B142" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15105,37 +15105,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>444758</v>
+        <v>444696</v>
       </c>
       <c r="R142" t="n">
-        <v>6846475</v>
+        <v>6846398</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15179,19 +15179,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125047001</v>
+        <v>125047000</v>
       </c>
       <c r="B143" t="n">
         <v>78810</v>
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>444501</v>
+        <v>444508</v>
       </c>
       <c r="R143" t="n">
-        <v>6846315</v>
+        <v>6846328</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15293,7 +15293,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125047062</v>
+        <v>125035959</v>
       </c>
       <c r="B144" t="n">
         <v>78810</v>
@@ -15329,17 +15329,17 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>444855</v>
+        <v>444515</v>
       </c>
       <c r="R144" t="n">
-        <v>6846310</v>
+        <v>6846143</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15383,22 +15383,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125037307</v>
+        <v>125046960</v>
       </c>
       <c r="B145" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15411,34 +15411,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>444521</v>
+        <v>444758</v>
       </c>
       <c r="R145" t="n">
-        <v>6846203</v>
+        <v>6846475</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15473,11 +15473,6 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -15490,22 +15485,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125037692</v>
+        <v>125047001</v>
       </c>
       <c r="B146" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15518,37 +15513,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>444696</v>
+        <v>444501</v>
       </c>
       <c r="R146" t="n">
-        <v>6846398</v>
+        <v>6846315</v>
       </c>
       <c r="S146" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15592,19 +15587,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125047000</v>
+        <v>125047062</v>
       </c>
       <c r="B147" t="n">
         <v>78810</v>
@@ -15644,10 +15639,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>444508</v>
+        <v>444855</v>
       </c>
       <c r="R147" t="n">
-        <v>6846328</v>
+        <v>6846310</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15706,10 +15701,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125035959</v>
+        <v>125037307</v>
       </c>
       <c r="B148" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15722,21 +15717,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15746,13 +15741,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>444515</v>
+        <v>444521</v>
       </c>
       <c r="R148" t="n">
-        <v>6846143</v>
+        <v>6846203</v>
       </c>
       <c r="S148" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15782,6 +15777,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16114,10 +16114,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125038296</v>
+        <v>125047169</v>
       </c>
       <c r="B152" t="n">
-        <v>79399</v>
+        <v>78194</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16130,37 +16130,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>444761</v>
+        <v>444930</v>
       </c>
       <c r="R152" t="n">
-        <v>6846496</v>
+        <v>6846320</v>
       </c>
       <c r="S152" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16204,22 +16204,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125047169</v>
+        <v>125037687</v>
       </c>
       <c r="B153" t="n">
-        <v>78194</v>
+        <v>77738</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16232,34 +16232,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>444930</v>
+        <v>444696</v>
       </c>
       <c r="R153" t="n">
-        <v>6846320</v>
+        <v>6846398</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16306,22 +16306,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125037687</v>
+        <v>125046954</v>
       </c>
       <c r="B154" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16334,34 +16334,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>444696</v>
+        <v>444910</v>
       </c>
       <c r="R154" t="n">
-        <v>6846398</v>
+        <v>6846390</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16408,19 +16408,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125046954</v>
+        <v>125047026</v>
       </c>
       <c r="B155" t="n">
         <v>78810</v>
@@ -16460,10 +16460,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>444910</v>
+        <v>444519</v>
       </c>
       <c r="R155" t="n">
-        <v>6846390</v>
+        <v>6846154</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16522,7 +16522,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125047026</v>
+        <v>125047022</v>
       </c>
       <c r="B156" t="n">
         <v>78810</v>
@@ -16562,10 +16562,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>444519</v>
+        <v>444485</v>
       </c>
       <c r="R156" t="n">
-        <v>6846154</v>
+        <v>6846146</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16624,10 +16624,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125047022</v>
+        <v>125038296</v>
       </c>
       <c r="B157" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16640,37 +16640,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>444485</v>
+        <v>444761</v>
       </c>
       <c r="R157" t="n">
-        <v>6846146</v>
+        <v>6846496</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16714,12 +16714,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19174,10 +19174,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125035022</v>
+        <v>125046672</v>
       </c>
       <c r="B182" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19190,37 +19190,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>444651</v>
+        <v>444514</v>
       </c>
       <c r="R182" t="n">
-        <v>6846168</v>
+        <v>6846296</v>
       </c>
       <c r="S182" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19264,22 +19264,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125047064</v>
+        <v>125046796</v>
       </c>
       <c r="B183" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19292,21 +19292,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19316,10 +19316,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>444890</v>
+        <v>444542</v>
       </c>
       <c r="R183" t="n">
-        <v>6846336</v>
+        <v>6846517</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19378,7 +19378,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125046974</v>
+        <v>125047050</v>
       </c>
       <c r="B184" t="n">
         <v>78810</v>
@@ -19418,10 +19418,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>444553</v>
+        <v>444726</v>
       </c>
       <c r="R184" t="n">
-        <v>6846568</v>
+        <v>6846130</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19480,7 +19480,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125046997</v>
+        <v>125047009</v>
       </c>
       <c r="B185" t="n">
         <v>78810</v>
@@ -19520,10 +19520,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>444540</v>
+        <v>444501</v>
       </c>
       <c r="R185" t="n">
-        <v>6846347</v>
+        <v>6846240</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19582,10 +19582,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125047170</v>
+        <v>125035022</v>
       </c>
       <c r="B186" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19598,37 +19598,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>444963</v>
+        <v>444651</v>
       </c>
       <c r="R186" t="n">
-        <v>6846302</v>
+        <v>6846168</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19672,19 +19672,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125046968</v>
+        <v>125047064</v>
       </c>
       <c r="B187" t="n">
         <v>78810</v>
@@ -19724,10 +19724,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>444579</v>
+        <v>444890</v>
       </c>
       <c r="R187" t="n">
-        <v>6846583</v>
+        <v>6846336</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19786,7 +19786,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125046987</v>
+        <v>125046974</v>
       </c>
       <c r="B188" t="n">
         <v>78810</v>
@@ -19826,10 +19826,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>444532</v>
+        <v>444553</v>
       </c>
       <c r="R188" t="n">
-        <v>6846448</v>
+        <v>6846568</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19888,7 +19888,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125034871</v>
+        <v>125046997</v>
       </c>
       <c r="B189" t="n">
         <v>78810</v>
@@ -19924,17 +19924,17 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>444678</v>
+        <v>444540</v>
       </c>
       <c r="R189" t="n">
-        <v>6846146</v>
+        <v>6846347</v>
       </c>
       <c r="S189" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19978,22 +19978,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125047082</v>
+        <v>125047170</v>
       </c>
       <c r="B190" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20006,21 +20006,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20030,10 +20030,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>445098</v>
+        <v>444963</v>
       </c>
       <c r="R190" t="n">
-        <v>6846358</v>
+        <v>6846302</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20092,7 +20092,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125047051</v>
+        <v>125046968</v>
       </c>
       <c r="B191" t="n">
         <v>78810</v>
@@ -20132,10 +20132,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>444754</v>
+        <v>444579</v>
       </c>
       <c r="R191" t="n">
-        <v>6846114</v>
+        <v>6846583</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20194,7 +20194,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125038101</v>
+        <v>125046987</v>
       </c>
       <c r="B192" t="n">
         <v>78810</v>
@@ -20230,17 +20230,17 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>444754</v>
+        <v>444532</v>
       </c>
       <c r="R192" t="n">
-        <v>6846466</v>
+        <v>6846448</v>
       </c>
       <c r="S192" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20284,22 +20284,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125046786</v>
+        <v>125034871</v>
       </c>
       <c r="B193" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20312,37 +20312,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>445022</v>
+        <v>444678</v>
       </c>
       <c r="R193" t="n">
-        <v>6846543</v>
+        <v>6846146</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20386,19 +20386,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125047050</v>
+        <v>125047082</v>
       </c>
       <c r="B194" t="n">
         <v>78810</v>
@@ -20438,10 +20438,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>444726</v>
+        <v>445098</v>
       </c>
       <c r="R194" t="n">
-        <v>6846130</v>
+        <v>6846358</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20500,7 +20500,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125047009</v>
+        <v>125047051</v>
       </c>
       <c r="B195" t="n">
         <v>78810</v>
@@ -20540,10 +20540,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>444501</v>
+        <v>444754</v>
       </c>
       <c r="R195" t="n">
-        <v>6846240</v>
+        <v>6846114</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20602,10 +20602,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125046607</v>
+        <v>125038101</v>
       </c>
       <c r="B196" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20618,37 +20618,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445086</v>
+        <v>444754</v>
       </c>
       <c r="R196" t="n">
-        <v>6846378</v>
+        <v>6846466</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20692,22 +20692,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125046672</v>
+        <v>125046607</v>
       </c>
       <c r="B197" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20720,21 +20720,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>444514</v>
+        <v>445086</v>
       </c>
       <c r="R197" t="n">
-        <v>6846296</v>
+        <v>6846378</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20806,10 +20806,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125046796</v>
+        <v>125046737</v>
       </c>
       <c r="B198" t="n">
-        <v>80763</v>
+        <v>56722</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20818,38 +20818,43 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>444542</v>
+        <v>444759</v>
       </c>
       <c r="R198" t="n">
-        <v>6846517</v>
+        <v>6846476</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20908,10 +20913,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125046737</v>
+        <v>125046786</v>
       </c>
       <c r="B199" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20920,43 +20925,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>444759</v>
+        <v>445022</v>
       </c>
       <c r="R199" t="n">
-        <v>6846476</v>
+        <v>6846543</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -25423,10 +25423,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>125046783</v>
+        <v>125047106</v>
       </c>
       <c r="B243" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25439,21 +25439,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25463,10 +25463,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445681</v>
+        <v>445294</v>
       </c>
       <c r="R243" t="n">
-        <v>6846547</v>
+        <v>6846511</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25525,7 +25525,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>125046891</v>
+        <v>125047132</v>
       </c>
       <c r="B244" t="n">
         <v>78810</v>
@@ -25565,10 +25565,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445648</v>
+        <v>445663</v>
       </c>
       <c r="R244" t="n">
-        <v>6846524</v>
+        <v>6846264</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25627,7 +25627,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>125047079</v>
+        <v>125046912</v>
       </c>
       <c r="B245" t="n">
         <v>78810</v>
@@ -25667,10 +25667,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445117</v>
+        <v>445388</v>
       </c>
       <c r="R245" t="n">
-        <v>6846339</v>
+        <v>6846473</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25729,10 +25729,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>125047133</v>
+        <v>125046783</v>
       </c>
       <c r="B246" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25745,21 +25745,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25769,10 +25769,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445672</v>
+        <v>445681</v>
       </c>
       <c r="R246" t="n">
-        <v>6846269</v>
+        <v>6846547</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25831,10 +25831,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>125046812</v>
+        <v>125046891</v>
       </c>
       <c r="B247" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25847,21 +25847,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25871,10 +25871,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445677</v>
+        <v>445648</v>
       </c>
       <c r="R247" t="n">
-        <v>6846563</v>
+        <v>6846524</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25933,7 +25933,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>125047106</v>
+        <v>125047079</v>
       </c>
       <c r="B248" t="n">
         <v>78810</v>
@@ -25973,10 +25973,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445294</v>
+        <v>445117</v>
       </c>
       <c r="R248" t="n">
-        <v>6846511</v>
+        <v>6846339</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26035,7 +26035,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>125047132</v>
+        <v>125047133</v>
       </c>
       <c r="B249" t="n">
         <v>78810</v>
@@ -26075,10 +26075,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445663</v>
+        <v>445672</v>
       </c>
       <c r="R249" t="n">
-        <v>6846264</v>
+        <v>6846269</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26137,10 +26137,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>125046912</v>
+        <v>125046812</v>
       </c>
       <c r="B250" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26153,21 +26153,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26177,10 +26177,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>445388</v>
+        <v>445677</v>
       </c>
       <c r="R250" t="n">
-        <v>6846473</v>
+        <v>6846563</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26545,10 +26545,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>125046611</v>
+        <v>125042176</v>
       </c>
       <c r="B254" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26561,37 +26561,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>445200</v>
+        <v>445540</v>
       </c>
       <c r="R254" t="n">
-        <v>6846496</v>
+        <v>6846431</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -26635,19 +26635,19 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>125042176</v>
+        <v>125046908</v>
       </c>
       <c r="B255" t="n">
         <v>78810</v>
@@ -26683,17 +26683,17 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>445540</v>
+        <v>445514</v>
       </c>
       <c r="R255" t="n">
-        <v>6846431</v>
+        <v>6846439</v>
       </c>
       <c r="S255" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -26737,19 +26737,19 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>125046908</v>
+        <v>125046902</v>
       </c>
       <c r="B256" t="n">
         <v>78810</v>
@@ -26789,10 +26789,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>445514</v>
+        <v>445559</v>
       </c>
       <c r="R256" t="n">
-        <v>6846439</v>
+        <v>6846433</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26851,7 +26851,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>125046902</v>
+        <v>125033498</v>
       </c>
       <c r="B257" t="n">
         <v>78810</v>
@@ -26887,14 +26887,14 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>445559</v>
+        <v>445171</v>
       </c>
       <c r="R257" t="n">
-        <v>6846433</v>
+        <v>6846401</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26941,22 +26941,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>125033498</v>
+        <v>125046611</v>
       </c>
       <c r="B258" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -26969,34 +26969,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>445171</v>
+        <v>445200</v>
       </c>
       <c r="R258" t="n">
-        <v>6846401</v>
+        <v>6846496</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27043,12 +27043,12 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
@@ -31043,7 +31043,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>125047113</v>
+        <v>125046935</v>
       </c>
       <c r="B298" t="n">
         <v>78810</v>
@@ -31083,10 +31083,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>445420</v>
+        <v>445335</v>
       </c>
       <c r="R298" t="n">
-        <v>6846444</v>
+        <v>6846449</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -31145,7 +31145,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>125046935</v>
+        <v>125046916</v>
       </c>
       <c r="B299" t="n">
         <v>78810</v>
@@ -31185,10 +31185,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>445335</v>
+        <v>445474</v>
       </c>
       <c r="R299" t="n">
-        <v>6846449</v>
+        <v>6846496</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -31247,7 +31247,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>125046916</v>
+        <v>125046862</v>
       </c>
       <c r="B300" t="n">
         <v>78810</v>
@@ -31287,10 +31287,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>445474</v>
+        <v>445729</v>
       </c>
       <c r="R300" t="n">
-        <v>6846496</v>
+        <v>6846371</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -31349,10 +31349,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>125046862</v>
+        <v>125046623</v>
       </c>
       <c r="B301" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -31365,21 +31365,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -31389,10 +31389,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>445729</v>
+        <v>445684</v>
       </c>
       <c r="R301" t="n">
-        <v>6846371</v>
+        <v>6846335</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -31451,10 +31451,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>125046854</v>
+        <v>125042970</v>
       </c>
       <c r="B302" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -31467,37 +31467,37 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>445654</v>
+        <v>445734</v>
       </c>
       <c r="R302" t="n">
-        <v>6846310</v>
+        <v>6846477</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -31541,22 +31541,22 @@
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>125046855</v>
+        <v>125046664</v>
       </c>
       <c r="B303" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -31569,21 +31569,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -31593,10 +31593,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>445668</v>
+        <v>445463</v>
       </c>
       <c r="R303" t="n">
-        <v>6846323</v>
+        <v>6846541</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -31655,10 +31655,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>125047077</v>
+        <v>125046648</v>
       </c>
       <c r="B304" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -31671,21 +31671,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -31695,10 +31695,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>445108</v>
+        <v>445554</v>
       </c>
       <c r="R304" t="n">
-        <v>6846332</v>
+        <v>6846413</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -31757,10 +31757,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>125046623</v>
+        <v>125047113</v>
       </c>
       <c r="B305" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -31773,21 +31773,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -31797,10 +31797,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>445684</v>
+        <v>445420</v>
       </c>
       <c r="R305" t="n">
-        <v>6846335</v>
+        <v>6846444</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -31859,10 +31859,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>125042970</v>
+        <v>125046854</v>
       </c>
       <c r="B306" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -31875,37 +31875,37 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>445734</v>
+        <v>445654</v>
       </c>
       <c r="R306" t="n">
-        <v>6846477</v>
+        <v>6846310</v>
       </c>
       <c r="S306" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -31949,22 +31949,22 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>125046664</v>
+        <v>125046855</v>
       </c>
       <c r="B307" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -31977,21 +31977,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>445463</v>
+        <v>445668</v>
       </c>
       <c r="R307" t="n">
-        <v>6846541</v>
+        <v>6846323</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -32063,10 +32063,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>125046648</v>
+        <v>125047077</v>
       </c>
       <c r="B308" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -32079,21 +32079,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -32103,10 +32103,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>445554</v>
+        <v>445108</v>
       </c>
       <c r="R308" t="n">
-        <v>6846413</v>
+        <v>6846332</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -33899,10 +33899,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125047152</v>
+        <v>125046844</v>
       </c>
       <c r="B326" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -33915,39 +33915,34 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P326" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>445630</v>
+        <v>445468</v>
       </c>
       <c r="R326" t="n">
-        <v>6846272</v>
+        <v>6846114</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -34006,10 +34001,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125046637</v>
+        <v>125047101</v>
       </c>
       <c r="B327" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -34022,21 +34017,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -34046,10 +34041,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>445621</v>
+        <v>445247</v>
       </c>
       <c r="R327" t="n">
-        <v>6846493</v>
+        <v>6846503</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -34108,10 +34103,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>125046692</v>
+        <v>125046898</v>
       </c>
       <c r="B328" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -34124,21 +34119,21 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -34148,10 +34143,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>445427</v>
+        <v>445556</v>
       </c>
       <c r="R328" t="n">
-        <v>6846297</v>
+        <v>6846502</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -34210,7 +34205,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>125046844</v>
+        <v>125046939</v>
       </c>
       <c r="B329" t="n">
         <v>78810</v>
@@ -34250,10 +34245,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>445468</v>
+        <v>445245</v>
       </c>
       <c r="R329" t="n">
-        <v>6846114</v>
+        <v>6846523</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -34312,10 +34307,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>125047101</v>
+        <v>125042795</v>
       </c>
       <c r="B330" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -34324,41 +34319,41 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>445247</v>
+        <v>445688</v>
       </c>
       <c r="R330" t="n">
-        <v>6846503</v>
+        <v>6846464</v>
       </c>
       <c r="S330" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -34402,19 +34397,19 @@
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>125046898</v>
+        <v>125046856</v>
       </c>
       <c r="B331" t="n">
         <v>78810</v>
@@ -34454,10 +34449,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>445556</v>
+        <v>445684</v>
       </c>
       <c r="R331" t="n">
-        <v>6846502</v>
+        <v>6846335</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -34516,7 +34511,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>125046939</v>
+        <v>125046905</v>
       </c>
       <c r="B332" t="n">
         <v>78810</v>
@@ -34556,10 +34551,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>445245</v>
+        <v>445540</v>
       </c>
       <c r="R332" t="n">
-        <v>6846523</v>
+        <v>6846396</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -34618,10 +34613,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>125042795</v>
+        <v>125046590</v>
       </c>
       <c r="B333" t="n">
-        <v>90977</v>
+        <v>79428</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -34630,41 +34625,41 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>445688</v>
+        <v>445294</v>
       </c>
       <c r="R333" t="n">
-        <v>6846464</v>
+        <v>6846485</v>
       </c>
       <c r="S333" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -34708,19 +34703,19 @@
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>125046856</v>
+        <v>125043307</v>
       </c>
       <c r="B334" t="n">
         <v>78810</v>
@@ -34756,17 +34751,17 @@
       <c r="I334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>445684</v>
+        <v>445779</v>
       </c>
       <c r="R334" t="n">
-        <v>6846335</v>
+        <v>6846435</v>
       </c>
       <c r="S334" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -34810,19 +34805,19 @@
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125046905</v>
+        <v>125046853</v>
       </c>
       <c r="B335" t="n">
         <v>78810</v>
@@ -34862,10 +34857,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>445540</v>
+        <v>445640</v>
       </c>
       <c r="R335" t="n">
-        <v>6846396</v>
+        <v>6846313</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -34924,10 +34919,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125046590</v>
+        <v>125044882</v>
       </c>
       <c r="B336" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -34940,37 +34935,37 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>445294</v>
+        <v>445503</v>
       </c>
       <c r="R336" t="n">
-        <v>6846485</v>
+        <v>6846055</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -35014,22 +35009,22 @@
       <c r="AT336" t="inlineStr"/>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125046610</v>
+        <v>125046889</v>
       </c>
       <c r="B337" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -35042,21 +35037,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -35066,10 +35061,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>445149</v>
+        <v>445693</v>
       </c>
       <c r="R337" t="n">
-        <v>6846429</v>
+        <v>6846539</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -35128,10 +35123,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125043307</v>
+        <v>125046610</v>
       </c>
       <c r="B338" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -35144,37 +35139,37 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>445779</v>
+        <v>445149</v>
       </c>
       <c r="R338" t="n">
-        <v>6846435</v>
+        <v>6846429</v>
       </c>
       <c r="S338" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -35218,22 +35213,22 @@
       <c r="AT338" t="inlineStr"/>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125046853</v>
+        <v>125046637</v>
       </c>
       <c r="B339" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -35246,21 +35241,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -35270,10 +35265,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>445640</v>
+        <v>445621</v>
       </c>
       <c r="R339" t="n">
-        <v>6846313</v>
+        <v>6846493</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -35332,10 +35327,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125044882</v>
+        <v>125046692</v>
       </c>
       <c r="B340" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -35348,37 +35343,37 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>445503</v>
+        <v>445427</v>
       </c>
       <c r="R340" t="n">
-        <v>6846055</v>
+        <v>6846297</v>
       </c>
       <c r="S340" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -35422,22 +35417,22 @@
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125046889</v>
+        <v>125047152</v>
       </c>
       <c r="B341" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -35450,34 +35445,39 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P341" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>445693</v>
+        <v>445630</v>
       </c>
       <c r="R341" t="n">
-        <v>6846539</v>
+        <v>6846272</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -41579,10 +41579,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>125033462</v>
+        <v>125047107</v>
       </c>
       <c r="B401" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -41595,34 +41595,34 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
       <c r="P401" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>445182</v>
+        <v>445358</v>
       </c>
       <c r="R401" t="n">
-        <v>6846445</v>
+        <v>6846488</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -41669,22 +41669,22 @@
       <c r="AT401" t="inlineStr"/>
       <c r="AW401" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>125046761</v>
+        <v>125046863</v>
       </c>
       <c r="B402" t="n">
-        <v>78896</v>
+        <v>78810</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -41693,25 +41693,25 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I402" t="inlineStr"/>
@@ -41721,10 +41721,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>445101</v>
+        <v>445707</v>
       </c>
       <c r="R402" t="n">
-        <v>6846542</v>
+        <v>6846395</v>
       </c>
       <c r="S402" t="n">
         <v>10</v>
@@ -41783,10 +41783,10 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>125046857</v>
+        <v>125033462</v>
       </c>
       <c r="B403" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -41799,34 +41799,34 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I403" t="inlineStr"/>
       <c r="P403" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>445697</v>
+        <v>445182</v>
       </c>
       <c r="R403" t="n">
-        <v>6846323</v>
+        <v>6846445</v>
       </c>
       <c r="S403" t="n">
         <v>10</v>
@@ -41873,22 +41873,22 @@
       <c r="AT403" t="inlineStr"/>
       <c r="AW403" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>125046929</v>
+        <v>125046761</v>
       </c>
       <c r="B404" t="n">
-        <v>78810</v>
+        <v>78896</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -41897,25 +41897,25 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I404" t="inlineStr"/>
@@ -41925,10 +41925,10 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>445400</v>
+        <v>445101</v>
       </c>
       <c r="R404" t="n">
-        <v>6846484</v>
+        <v>6846542</v>
       </c>
       <c r="S404" t="n">
         <v>10</v>
@@ -41987,7 +41987,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>125033575</v>
+        <v>125046857</v>
       </c>
       <c r="B405" t="n">
         <v>78810</v>
@@ -42023,14 +42023,14 @@
       <c r="I405" t="inlineStr"/>
       <c r="P405" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>445136</v>
+        <v>445697</v>
       </c>
       <c r="R405" t="n">
-        <v>6846374</v>
+        <v>6846323</v>
       </c>
       <c r="S405" t="n">
         <v>10</v>
@@ -42077,19 +42077,19 @@
       <c r="AT405" t="inlineStr"/>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>125042370</v>
+        <v>125046929</v>
       </c>
       <c r="B406" t="n">
         <v>78810</v>
@@ -42125,17 +42125,17 @@
       <c r="I406" t="inlineStr"/>
       <c r="P406" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>445558</v>
+        <v>445400</v>
       </c>
       <c r="R406" t="n">
-        <v>6846476</v>
+        <v>6846484</v>
       </c>
       <c r="S406" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -42179,19 +42179,19 @@
       <c r="AT406" t="inlineStr"/>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>125042481</v>
+        <v>125033575</v>
       </c>
       <c r="B407" t="n">
         <v>78810</v>
@@ -42227,17 +42227,17 @@
       <c r="I407" t="inlineStr"/>
       <c r="P407" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>445595</v>
+        <v>445136</v>
       </c>
       <c r="R407" t="n">
-        <v>6846474</v>
+        <v>6846374</v>
       </c>
       <c r="S407" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>125047128</v>
+        <v>125042370</v>
       </c>
       <c r="B408" t="n">
         <v>78810</v>
@@ -42329,17 +42329,17 @@
       <c r="I408" t="inlineStr"/>
       <c r="P408" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>445625</v>
+        <v>445558</v>
       </c>
       <c r="R408" t="n">
-        <v>6846250</v>
+        <v>6846476</v>
       </c>
       <c r="S408" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -42383,19 +42383,19 @@
       <c r="AT408" t="inlineStr"/>
       <c r="AW408" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX408" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>125033638</v>
+        <v>125042481</v>
       </c>
       <c r="B409" t="n">
         <v>78810</v>
@@ -42431,14 +42431,14 @@
       <c r="I409" t="inlineStr"/>
       <c r="P409" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>445149</v>
+        <v>445595</v>
       </c>
       <c r="R409" t="n">
-        <v>6846386</v>
+        <v>6846474</v>
       </c>
       <c r="S409" t="n">
         <v>20</v>
@@ -42497,7 +42497,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>125047107</v>
+        <v>125047128</v>
       </c>
       <c r="B410" t="n">
         <v>78810</v>
@@ -42537,10 +42537,10 @@
         </is>
       </c>
       <c r="Q410" t="n">
-        <v>445358</v>
+        <v>445625</v>
       </c>
       <c r="R410" t="n">
-        <v>6846488</v>
+        <v>6846250</v>
       </c>
       <c r="S410" t="n">
         <v>10</v>
@@ -42599,7 +42599,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>125046863</v>
+        <v>125033638</v>
       </c>
       <c r="B411" t="n">
         <v>78810</v>
@@ -42635,17 +42635,17 @@
       <c r="I411" t="inlineStr"/>
       <c r="P411" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>445707</v>
+        <v>445149</v>
       </c>
       <c r="R411" t="n">
-        <v>6846395</v>
+        <v>6846386</v>
       </c>
       <c r="S411" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -42689,12 +42689,12 @@
       <c r="AT411" t="inlineStr"/>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
@@ -43017,10 +43017,10 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>125046810</v>
+        <v>125043041</v>
       </c>
       <c r="B415" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -43033,37 +43033,37 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I415" t="inlineStr"/>
       <c r="P415" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>445646</v>
+        <v>445711</v>
       </c>
       <c r="R415" t="n">
-        <v>6846261</v>
+        <v>6846458</v>
       </c>
       <c r="S415" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -43107,22 +43107,22 @@
       <c r="AT415" t="inlineStr"/>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>125046815</v>
+        <v>125046941</v>
       </c>
       <c r="B416" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -43135,21 +43135,21 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I416" t="inlineStr"/>
@@ -43159,10 +43159,10 @@
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>445196</v>
+        <v>445187</v>
       </c>
       <c r="R416" t="n">
-        <v>6846474</v>
+        <v>6846515</v>
       </c>
       <c r="S416" t="n">
         <v>10</v>
@@ -43221,7 +43221,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>125047127</v>
+        <v>125046865</v>
       </c>
       <c r="B417" t="n">
         <v>78810</v>
@@ -43261,10 +43261,10 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>445599</v>
+        <v>445731</v>
       </c>
       <c r="R417" t="n">
-        <v>6846247</v>
+        <v>6846384</v>
       </c>
       <c r="S417" t="n">
         <v>10</v>
@@ -43323,10 +43323,10 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>125043041</v>
+        <v>125047086</v>
       </c>
       <c r="B418" t="n">
-        <v>91184</v>
+        <v>78810</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -43339,37 +43339,37 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I418" t="inlineStr"/>
       <c r="P418" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>445711</v>
+        <v>445120</v>
       </c>
       <c r="R418" t="n">
-        <v>6846458</v>
+        <v>6846396</v>
       </c>
       <c r="S418" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -43413,19 +43413,19 @@
       <c r="AT418" t="inlineStr"/>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>125046941</v>
+        <v>125046933</v>
       </c>
       <c r="B419" t="n">
         <v>78810</v>
@@ -43465,10 +43465,10 @@
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>445187</v>
+        <v>445367</v>
       </c>
       <c r="R419" t="n">
-        <v>6846515</v>
+        <v>6846461</v>
       </c>
       <c r="S419" t="n">
         <v>10</v>
@@ -43527,10 +43527,10 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>125046865</v>
+        <v>125042127</v>
       </c>
       <c r="B420" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -43543,37 +43543,37 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I420" t="inlineStr"/>
       <c r="P420" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>445731</v>
+        <v>445538</v>
       </c>
       <c r="R420" t="n">
-        <v>6846384</v>
+        <v>6846416</v>
       </c>
       <c r="S420" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -43617,22 +43617,22 @@
       <c r="AT420" t="inlineStr"/>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>125047086</v>
+        <v>125046693</v>
       </c>
       <c r="B421" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -43645,21 +43645,21 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I421" t="inlineStr"/>
@@ -43669,10 +43669,10 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>445120</v>
+        <v>445542</v>
       </c>
       <c r="R421" t="n">
-        <v>6846396</v>
+        <v>6846225</v>
       </c>
       <c r="S421" t="n">
         <v>10</v>
@@ -43731,10 +43731,10 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>125046933</v>
+        <v>125046727</v>
       </c>
       <c r="B422" t="n">
-        <v>78810</v>
+        <v>78905</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -43747,21 +43747,21 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I422" t="inlineStr"/>
@@ -43771,10 +43771,10 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>445367</v>
+        <v>445106</v>
       </c>
       <c r="R422" t="n">
-        <v>6846461</v>
+        <v>6846414</v>
       </c>
       <c r="S422" t="n">
         <v>10</v>
@@ -43833,10 +43833,10 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>125042127</v>
+        <v>125047172</v>
       </c>
       <c r="B423" t="n">
-        <v>78842</v>
+        <v>5176</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -43845,41 +43845,46 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P423" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>445538</v>
+        <v>445593</v>
       </c>
       <c r="R423" t="n">
-        <v>6846416</v>
+        <v>6846250</v>
       </c>
       <c r="S423" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -43923,22 +43928,22 @@
       <c r="AT423" t="inlineStr"/>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>125046693</v>
+        <v>125046810</v>
       </c>
       <c r="B424" t="n">
-        <v>78842</v>
+        <v>91030</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -43951,21 +43956,21 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
@@ -43975,10 +43980,10 @@
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>445542</v>
+        <v>445646</v>
       </c>
       <c r="R424" t="n">
-        <v>6846225</v>
+        <v>6846261</v>
       </c>
       <c r="S424" t="n">
         <v>10</v>
@@ -44037,10 +44042,10 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>125046727</v>
+        <v>125046815</v>
       </c>
       <c r="B425" t="n">
-        <v>78905</v>
+        <v>91030</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -44053,21 +44058,21 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>967</v>
+        <v>5432</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I425" t="inlineStr"/>
@@ -44077,10 +44082,10 @@
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>445106</v>
+        <v>445196</v>
       </c>
       <c r="R425" t="n">
-        <v>6846414</v>
+        <v>6846474</v>
       </c>
       <c r="S425" t="n">
         <v>10</v>
@@ -44139,10 +44144,10 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>125047172</v>
+        <v>125047127</v>
       </c>
       <c r="B426" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -44151,43 +44156,38 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
-      <c r="M426" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P426" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>445593</v>
+        <v>445599</v>
       </c>
       <c r="R426" t="n">
-        <v>6846250</v>
+        <v>6846247</v>
       </c>
       <c r="S426" t="n">
         <v>10</v>
@@ -44246,10 +44246,10 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>125047160</v>
+        <v>125046682</v>
       </c>
       <c r="B427" t="n">
-        <v>57513</v>
+        <v>78842</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -44262,39 +44262,34 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
-      <c r="M427" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P427" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>445108</v>
+        <v>445276</v>
       </c>
       <c r="R427" t="n">
-        <v>6846332</v>
+        <v>6846526</v>
       </c>
       <c r="S427" t="n">
         <v>10</v>
@@ -44353,10 +44348,10 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>125033485</v>
+        <v>125046811</v>
       </c>
       <c r="B428" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -44369,34 +44364,34 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I428" t="inlineStr"/>
       <c r="P428" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>445169</v>
+        <v>445791</v>
       </c>
       <c r="R428" t="n">
-        <v>6846417</v>
+        <v>6846476</v>
       </c>
       <c r="S428" t="n">
         <v>10</v>
@@ -44443,19 +44438,19 @@
       <c r="AT428" t="inlineStr"/>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>125046849</v>
+        <v>125046922</v>
       </c>
       <c r="B429" t="n">
         <v>78810</v>
@@ -44495,10 +44490,10 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>445591</v>
+        <v>445516</v>
       </c>
       <c r="R429" t="n">
-        <v>6846218</v>
+        <v>6846555</v>
       </c>
       <c r="S429" t="n">
         <v>10</v>
@@ -44557,10 +44552,10 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>125043335</v>
+        <v>125046618</v>
       </c>
       <c r="B430" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -44573,37 +44568,37 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I430" t="inlineStr"/>
       <c r="P430" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>445762</v>
+        <v>445478</v>
       </c>
       <c r="R430" t="n">
-        <v>6846422</v>
+        <v>6846122</v>
       </c>
       <c r="S430" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T430" t="inlineStr">
         <is>
@@ -44647,19 +44642,19 @@
       <c r="AT430" t="inlineStr"/>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>125046859</v>
+        <v>125033485</v>
       </c>
       <c r="B431" t="n">
         <v>78810</v>
@@ -44695,14 +44690,14 @@
       <c r="I431" t="inlineStr"/>
       <c r="P431" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>445700</v>
+        <v>445169</v>
       </c>
       <c r="R431" t="n">
-        <v>6846331</v>
+        <v>6846417</v>
       </c>
       <c r="S431" t="n">
         <v>10</v>
@@ -44749,19 +44744,19 @@
       <c r="AT431" t="inlineStr"/>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>125047092</v>
+        <v>125046849</v>
       </c>
       <c r="B432" t="n">
         <v>78810</v>
@@ -44801,10 +44796,10 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>445141</v>
+        <v>445591</v>
       </c>
       <c r="R432" t="n">
-        <v>6846434</v>
+        <v>6846218</v>
       </c>
       <c r="S432" t="n">
         <v>10</v>
@@ -44863,10 +44858,10 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>125046700</v>
+        <v>125043335</v>
       </c>
       <c r="B433" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -44879,37 +44874,37 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I433" t="inlineStr"/>
       <c r="P433" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>445180</v>
+        <v>445762</v>
       </c>
       <c r="R433" t="n">
-        <v>6846446</v>
+        <v>6846422</v>
       </c>
       <c r="S433" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -44953,19 +44948,19 @@
       <c r="AT433" t="inlineStr"/>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>125046843</v>
+        <v>125046859</v>
       </c>
       <c r="B434" t="n">
         <v>78810</v>
@@ -45005,10 +45000,10 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>445436</v>
+        <v>445700</v>
       </c>
       <c r="R434" t="n">
-        <v>6846091</v>
+        <v>6846331</v>
       </c>
       <c r="S434" t="n">
         <v>10</v>
@@ -45067,7 +45062,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>125046910</v>
+        <v>125047092</v>
       </c>
       <c r="B435" t="n">
         <v>78810</v>
@@ -45107,10 +45102,10 @@
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>445493</v>
+        <v>445141</v>
       </c>
       <c r="R435" t="n">
-        <v>6846458</v>
+        <v>6846434</v>
       </c>
       <c r="S435" t="n">
         <v>10</v>
@@ -45169,10 +45164,10 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>125046811</v>
+        <v>125046700</v>
       </c>
       <c r="B436" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -45185,21 +45180,21 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I436" t="inlineStr"/>
@@ -45209,10 +45204,10 @@
         </is>
       </c>
       <c r="Q436" t="n">
-        <v>445791</v>
+        <v>445180</v>
       </c>
       <c r="R436" t="n">
-        <v>6846476</v>
+        <v>6846446</v>
       </c>
       <c r="S436" t="n">
         <v>10</v>
@@ -45271,7 +45266,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>125046922</v>
+        <v>125046843</v>
       </c>
       <c r="B437" t="n">
         <v>78810</v>
@@ -45311,10 +45306,10 @@
         </is>
       </c>
       <c r="Q437" t="n">
-        <v>445516</v>
+        <v>445436</v>
       </c>
       <c r="R437" t="n">
-        <v>6846555</v>
+        <v>6846091</v>
       </c>
       <c r="S437" t="n">
         <v>10</v>
@@ -45373,10 +45368,10 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>125046682</v>
+        <v>125046910</v>
       </c>
       <c r="B438" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -45389,21 +45384,21 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I438" t="inlineStr"/>
@@ -45413,10 +45408,10 @@
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>445276</v>
+        <v>445493</v>
       </c>
       <c r="R438" t="n">
-        <v>6846526</v>
+        <v>6846458</v>
       </c>
       <c r="S438" t="n">
         <v>10</v>
@@ -45475,7 +45470,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>125046618</v>
+        <v>125046624</v>
       </c>
       <c r="B439" t="n">
         <v>78842</v>
@@ -45515,10 +45510,10 @@
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>445478</v>
+        <v>445700</v>
       </c>
       <c r="R439" t="n">
-        <v>6846122</v>
+        <v>6846331</v>
       </c>
       <c r="S439" t="n">
         <v>10</v>
@@ -45577,7 +45572,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>125046624</v>
+        <v>125046640</v>
       </c>
       <c r="B440" t="n">
         <v>78842</v>
@@ -45617,10 +45612,10 @@
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>445700</v>
+        <v>445575</v>
       </c>
       <c r="R440" t="n">
-        <v>6846331</v>
+        <v>6846503</v>
       </c>
       <c r="S440" t="n">
         <v>10</v>
@@ -45679,7 +45674,7 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>125046640</v>
+        <v>125046630</v>
       </c>
       <c r="B441" t="n">
         <v>78842</v>
@@ -45719,10 +45714,10 @@
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>445575</v>
+        <v>445773</v>
       </c>
       <c r="R441" t="n">
-        <v>6846503</v>
+        <v>6846524</v>
       </c>
       <c r="S441" t="n">
         <v>10</v>
@@ -45781,10 +45776,10 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>125046630</v>
+        <v>125047160</v>
       </c>
       <c r="B442" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -45797,34 +45792,39 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I442" t="inlineStr"/>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P442" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>445773</v>
+        <v>445108</v>
       </c>
       <c r="R442" t="n">
-        <v>6846524</v>
+        <v>6846332</v>
       </c>
       <c r="S442" t="n">
         <v>10</v>
@@ -48637,10 +48637,10 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>125047156</v>
+        <v>125042661</v>
       </c>
       <c r="B470" t="n">
-        <v>57513</v>
+        <v>78842</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -48653,39 +48653,34 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I470" t="inlineStr"/>
-      <c r="M470" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P470" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q470" t="n">
-        <v>445481</v>
+        <v>445648</v>
       </c>
       <c r="R470" t="n">
-        <v>6846499</v>
+        <v>6846428</v>
       </c>
       <c r="S470" t="n">
         <v>10</v>
@@ -48732,22 +48727,22 @@
       <c r="AT470" t="inlineStr"/>
       <c r="AW470" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX470" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>125047080</v>
+        <v>125046686</v>
       </c>
       <c r="B471" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -48760,21 +48755,21 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I471" t="inlineStr"/>
@@ -48784,10 +48779,10 @@
         </is>
       </c>
       <c r="Q471" t="n">
-        <v>445110</v>
+        <v>445410</v>
       </c>
       <c r="R471" t="n">
-        <v>6846348</v>
+        <v>6846399</v>
       </c>
       <c r="S471" t="n">
         <v>10</v>
@@ -48846,10 +48841,10 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>125046871</v>
+        <v>125046683</v>
       </c>
       <c r="B472" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -48862,21 +48857,21 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I472" t="inlineStr"/>
@@ -48886,10 +48881,10 @@
         </is>
       </c>
       <c r="Q472" t="n">
-        <v>445782</v>
+        <v>445378</v>
       </c>
       <c r="R472" t="n">
-        <v>6846455</v>
+        <v>6846474</v>
       </c>
       <c r="S472" t="n">
         <v>10</v>
@@ -48948,10 +48943,10 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>125047097</v>
+        <v>125046647</v>
       </c>
       <c r="B473" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -48964,21 +48959,21 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I473" t="inlineStr"/>
@@ -48988,10 +48983,10 @@
         </is>
       </c>
       <c r="Q473" t="n">
-        <v>445192</v>
+        <v>445561</v>
       </c>
       <c r="R473" t="n">
-        <v>6846484</v>
+        <v>6846419</v>
       </c>
       <c r="S473" t="n">
         <v>10</v>
@@ -49050,10 +49045,10 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>125046789</v>
+        <v>125046663</v>
       </c>
       <c r="B474" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
@@ -49066,21 +49061,21 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I474" t="inlineStr"/>
@@ -49090,10 +49085,10 @@
         </is>
       </c>
       <c r="Q474" t="n">
-        <v>445105</v>
+        <v>445512</v>
       </c>
       <c r="R474" t="n">
-        <v>6846415</v>
+        <v>6846523</v>
       </c>
       <c r="S474" t="n">
         <v>10</v>
@@ -49152,10 +49147,10 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>125047104</v>
+        <v>125046629</v>
       </c>
       <c r="B475" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
@@ -49168,21 +49163,21 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I475" t="inlineStr"/>
@@ -49192,10 +49187,10 @@
         </is>
       </c>
       <c r="Q475" t="n">
-        <v>445274</v>
+        <v>445792</v>
       </c>
       <c r="R475" t="n">
-        <v>6846518</v>
+        <v>6846513</v>
       </c>
       <c r="S475" t="n">
         <v>10</v>
@@ -49254,10 +49249,10 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>125046864</v>
+        <v>125046665</v>
       </c>
       <c r="B476" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
@@ -49270,21 +49265,21 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I476" t="inlineStr"/>
@@ -49294,10 +49289,10 @@
         </is>
       </c>
       <c r="Q476" t="n">
-        <v>445717</v>
+        <v>445375</v>
       </c>
       <c r="R476" t="n">
-        <v>6846391</v>
+        <v>6846474</v>
       </c>
       <c r="S476" t="n">
         <v>10</v>
@@ -49356,10 +49351,10 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>125046698</v>
+        <v>125047156</v>
       </c>
       <c r="B477" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
@@ -49368,38 +49363,43 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I477" t="inlineStr"/>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P477" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q477" t="n">
-        <v>445716</v>
+        <v>445481</v>
       </c>
       <c r="R477" t="n">
-        <v>6846584</v>
+        <v>6846499</v>
       </c>
       <c r="S477" t="n">
         <v>10</v>
@@ -49458,7 +49458,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>125046897</v>
+        <v>125047104</v>
       </c>
       <c r="B478" t="n">
         <v>78810</v>
@@ -49498,10 +49498,10 @@
         </is>
       </c>
       <c r="Q478" t="n">
-        <v>445575</v>
+        <v>445274</v>
       </c>
       <c r="R478" t="n">
-        <v>6846503</v>
+        <v>6846518</v>
       </c>
       <c r="S478" t="n">
         <v>10</v>
@@ -49560,7 +49560,7 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>125046906</v>
+        <v>125046864</v>
       </c>
       <c r="B479" t="n">
         <v>78810</v>
@@ -49600,10 +49600,10 @@
         </is>
       </c>
       <c r="Q479" t="n">
-        <v>445543</v>
+        <v>445717</v>
       </c>
       <c r="R479" t="n">
-        <v>6846371</v>
+        <v>6846391</v>
       </c>
       <c r="S479" t="n">
         <v>10</v>
@@ -49662,10 +49662,10 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>125047093</v>
+        <v>125046698</v>
       </c>
       <c r="B480" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
@@ -49674,25 +49674,25 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I480" t="inlineStr"/>
@@ -49702,10 +49702,10 @@
         </is>
       </c>
       <c r="Q480" t="n">
-        <v>445167</v>
+        <v>445716</v>
       </c>
       <c r="R480" t="n">
-        <v>6846434</v>
+        <v>6846584</v>
       </c>
       <c r="S480" t="n">
         <v>10</v>
@@ -49764,10 +49764,10 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>125046605</v>
+        <v>125046897</v>
       </c>
       <c r="B481" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -49780,21 +49780,21 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I481" t="inlineStr"/>
@@ -49804,10 +49804,10 @@
         </is>
       </c>
       <c r="Q481" t="n">
-        <v>445117</v>
+        <v>445575</v>
       </c>
       <c r="R481" t="n">
-        <v>6846341</v>
+        <v>6846503</v>
       </c>
       <c r="S481" t="n">
         <v>10</v>
@@ -49866,10 +49866,10 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>125042661</v>
+        <v>125046906</v>
       </c>
       <c r="B482" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -49882,34 +49882,34 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
       <c r="P482" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q482" t="n">
-        <v>445648</v>
+        <v>445543</v>
       </c>
       <c r="R482" t="n">
-        <v>6846428</v>
+        <v>6846371</v>
       </c>
       <c r="S482" t="n">
         <v>10</v>
@@ -49956,22 +49956,22 @@
       <c r="AT482" t="inlineStr"/>
       <c r="AW482" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX482" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>125046686</v>
+        <v>125047093</v>
       </c>
       <c r="B483" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -49984,21 +49984,21 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I483" t="inlineStr"/>
@@ -50008,10 +50008,10 @@
         </is>
       </c>
       <c r="Q483" t="n">
-        <v>445410</v>
+        <v>445167</v>
       </c>
       <c r="R483" t="n">
-        <v>6846399</v>
+        <v>6846434</v>
       </c>
       <c r="S483" t="n">
         <v>10</v>
@@ -50070,10 +50070,10 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>125046683</v>
+        <v>125047080</v>
       </c>
       <c r="B484" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -50086,21 +50086,21 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I484" t="inlineStr"/>
@@ -50110,10 +50110,10 @@
         </is>
       </c>
       <c r="Q484" t="n">
-        <v>445378</v>
+        <v>445110</v>
       </c>
       <c r="R484" t="n">
-        <v>6846474</v>
+        <v>6846348</v>
       </c>
       <c r="S484" t="n">
         <v>10</v>
@@ -50172,10 +50172,10 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>125046647</v>
+        <v>125046871</v>
       </c>
       <c r="B485" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -50188,21 +50188,21 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I485" t="inlineStr"/>
@@ -50212,10 +50212,10 @@
         </is>
       </c>
       <c r="Q485" t="n">
-        <v>445561</v>
+        <v>445782</v>
       </c>
       <c r="R485" t="n">
-        <v>6846419</v>
+        <v>6846455</v>
       </c>
       <c r="S485" t="n">
         <v>10</v>
@@ -50274,10 +50274,10 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>125046663</v>
+        <v>125047097</v>
       </c>
       <c r="B486" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -50290,21 +50290,21 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I486" t="inlineStr"/>
@@ -50314,10 +50314,10 @@
         </is>
       </c>
       <c r="Q486" t="n">
-        <v>445512</v>
+        <v>445192</v>
       </c>
       <c r="R486" t="n">
-        <v>6846523</v>
+        <v>6846484</v>
       </c>
       <c r="S486" t="n">
         <v>10</v>
@@ -50376,10 +50376,10 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>125046629</v>
+        <v>125046605</v>
       </c>
       <c r="B487" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -50392,21 +50392,21 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I487" t="inlineStr"/>
@@ -50416,10 +50416,10 @@
         </is>
       </c>
       <c r="Q487" t="n">
-        <v>445792</v>
+        <v>445117</v>
       </c>
       <c r="R487" t="n">
-        <v>6846513</v>
+        <v>6846341</v>
       </c>
       <c r="S487" t="n">
         <v>10</v>
@@ -50478,10 +50478,10 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>125046665</v>
+        <v>125046789</v>
       </c>
       <c r="B488" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -50494,21 +50494,21 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I488" t="inlineStr"/>
@@ -50518,10 +50518,10 @@
         </is>
       </c>
       <c r="Q488" t="n">
-        <v>445375</v>
+        <v>445105</v>
       </c>
       <c r="R488" t="n">
-        <v>6846474</v>
+        <v>6846415</v>
       </c>
       <c r="S488" t="n">
         <v>10</v>
@@ -52008,7 +52008,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>125040082</v>
+        <v>125046641</v>
       </c>
       <c r="B503" t="n">
         <v>78842</v>
@@ -52044,17 +52044,17 @@
       <c r="I503" t="inlineStr"/>
       <c r="P503" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q503" t="n">
-        <v>445167</v>
+        <v>445551</v>
       </c>
       <c r="R503" t="n">
-        <v>6846498</v>
+        <v>6846487</v>
       </c>
       <c r="S503" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T503" t="inlineStr">
         <is>
@@ -52098,19 +52098,19 @@
       <c r="AT503" t="inlineStr"/>
       <c r="AW503" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX503" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>125046641</v>
+        <v>125046668</v>
       </c>
       <c r="B504" t="n">
         <v>78842</v>
@@ -52150,10 +52150,10 @@
         </is>
       </c>
       <c r="Q504" t="n">
-        <v>445551</v>
+        <v>445340</v>
       </c>
       <c r="R504" t="n">
-        <v>6846487</v>
+        <v>6846449</v>
       </c>
       <c r="S504" t="n">
         <v>10</v>
@@ -52212,7 +52212,7 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>125046668</v>
+        <v>125044685</v>
       </c>
       <c r="B505" t="n">
         <v>78842</v>
@@ -52248,17 +52248,17 @@
       <c r="I505" t="inlineStr"/>
       <c r="P505" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q505" t="n">
-        <v>445340</v>
+        <v>445563</v>
       </c>
       <c r="R505" t="n">
-        <v>6846449</v>
+        <v>6846098</v>
       </c>
       <c r="S505" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T505" t="inlineStr">
         <is>
@@ -52302,22 +52302,22 @@
       <c r="AT505" t="inlineStr"/>
       <c r="AW505" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX505" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>125044685</v>
+        <v>125046791</v>
       </c>
       <c r="B506" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -52330,37 +52330,37 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I506" t="inlineStr"/>
       <c r="P506" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q506" t="n">
-        <v>445563</v>
+        <v>445291</v>
       </c>
       <c r="R506" t="n">
-        <v>6846098</v>
+        <v>6846523</v>
       </c>
       <c r="S506" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T506" t="inlineStr">
         <is>
@@ -52404,19 +52404,19 @@
       <c r="AT506" t="inlineStr"/>
       <c r="AW506" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX506" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>125043358</v>
+        <v>125040082</v>
       </c>
       <c r="B507" t="n">
         <v>78842</v>
@@ -52452,14 +52452,14 @@
       <c r="I507" t="inlineStr"/>
       <c r="P507" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q507" t="n">
-        <v>445763</v>
+        <v>445167</v>
       </c>
       <c r="R507" t="n">
-        <v>6846407</v>
+        <v>6846498</v>
       </c>
       <c r="S507" t="n">
         <v>20</v>
@@ -52518,10 +52518,10 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>125046791</v>
+        <v>125043358</v>
       </c>
       <c r="B508" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -52534,37 +52534,37 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I508" t="inlineStr"/>
       <c r="P508" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q508" t="n">
-        <v>445291</v>
+        <v>445763</v>
       </c>
       <c r="R508" t="n">
-        <v>6846523</v>
+        <v>6846407</v>
       </c>
       <c r="S508" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T508" t="inlineStr">
         <is>
@@ -52608,12 +52608,12 @@
       <c r="AT508" t="inlineStr"/>
       <c r="AW508" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX508" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY508" t="inlineStr"/>

--- a/artfynd/A 18557-2025 artfynd.xlsx
+++ b/artfynd/A 18557-2025 artfynd.xlsx
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125047034</v>
+        <v>125046674</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444612</v>
+        <v>444501</v>
       </c>
       <c r="R24" t="n">
-        <v>6846142</v>
+        <v>6846240</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125039726</v>
+        <v>125033984</v>
       </c>
       <c r="B25" t="n">
         <v>79428</v>
@@ -3152,17 +3152,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445081</v>
+        <v>444904</v>
       </c>
       <c r="R25" t="n">
-        <v>6846466</v>
+        <v>6846287</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125046674</v>
+        <v>125035937</v>
       </c>
       <c r="B26" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,37 +3234,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444501</v>
+        <v>444514</v>
       </c>
       <c r="R26" t="n">
-        <v>6846240</v>
+        <v>6846145</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3308,22 +3308,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125033984</v>
+        <v>125035022</v>
       </c>
       <c r="B27" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,13 +3360,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444904</v>
+        <v>444651</v>
       </c>
       <c r="R27" t="n">
-        <v>6846287</v>
+        <v>6846168</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125035937</v>
+        <v>125047064</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3458,17 +3458,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444514</v>
+        <v>444890</v>
       </c>
       <c r="R28" t="n">
-        <v>6846145</v>
+        <v>6846336</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3512,19 +3512,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125035022</v>
+        <v>125047053</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3560,17 +3560,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444651</v>
+        <v>444797</v>
       </c>
       <c r="R29" t="n">
-        <v>6846168</v>
+        <v>6846194</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,19 +3614,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125047064</v>
+        <v>125047054</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444890</v>
+        <v>444812</v>
       </c>
       <c r="R30" t="n">
-        <v>6846336</v>
+        <v>6846244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125047053</v>
+        <v>125047004</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444797</v>
+        <v>444496</v>
       </c>
       <c r="R31" t="n">
-        <v>6846194</v>
+        <v>6846293</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125047054</v>
+        <v>125046954</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444812</v>
+        <v>444910</v>
       </c>
       <c r="R32" t="n">
-        <v>6846244</v>
+        <v>6846390</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125047004</v>
+        <v>125046717</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3948,21 +3948,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444496</v>
+        <v>444902</v>
       </c>
       <c r="R33" t="n">
-        <v>6846293</v>
+        <v>6846334</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125046954</v>
+        <v>125047034</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444910</v>
+        <v>444612</v>
       </c>
       <c r="R34" t="n">
-        <v>6846390</v>
+        <v>6846142</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4136,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125046717</v>
+        <v>125039726</v>
       </c>
       <c r="B35" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4152,37 +4152,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444902</v>
+        <v>445081</v>
       </c>
       <c r="R35" t="n">
-        <v>6846334</v>
+        <v>6846466</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4226,22 +4226,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125046814</v>
+        <v>125038407</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>78905</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,37 +4254,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>967</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444486</v>
+        <v>444720</v>
       </c>
       <c r="R36" t="n">
-        <v>6846184</v>
+        <v>6846606</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125046947</v>
+        <v>125046797</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445089</v>
+        <v>444830</v>
       </c>
       <c r="R37" t="n">
-        <v>6846537</v>
+        <v>6846275</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4442,7 +4442,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125047052</v>
+        <v>125046960</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444778</v>
+        <v>444758</v>
       </c>
       <c r="R38" t="n">
-        <v>6846129</v>
+        <v>6846475</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125046995</v>
+        <v>125046983</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444528</v>
+        <v>444525</v>
       </c>
       <c r="R39" t="n">
-        <v>6846366</v>
+        <v>6846510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125046956</v>
+        <v>125047027</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444822</v>
+        <v>444529</v>
       </c>
       <c r="R40" t="n">
-        <v>6846368</v>
+        <v>6846143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4748,10 +4748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125046960</v>
+        <v>125046712</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4764,21 +4764,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444758</v>
+        <v>444508</v>
       </c>
       <c r="R41" t="n">
-        <v>6846475</v>
+        <v>6846303</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4850,10 +4850,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125046983</v>
+        <v>125034328</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4866,37 +4866,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444525</v>
+        <v>444814</v>
       </c>
       <c r="R42" t="n">
-        <v>6846510</v>
+        <v>6846168</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4940,22 +4940,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125047027</v>
+        <v>125046814</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4968,21 +4968,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444529</v>
+        <v>444486</v>
       </c>
       <c r="R43" t="n">
-        <v>6846143</v>
+        <v>6846184</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5054,10 +5054,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125046712</v>
+        <v>125046947</v>
       </c>
       <c r="B44" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5070,21 +5070,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444508</v>
+        <v>445089</v>
       </c>
       <c r="R44" t="n">
-        <v>6846303</v>
+        <v>6846537</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125034328</v>
+        <v>125047052</v>
       </c>
       <c r="B45" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5172,37 +5172,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444814</v>
+        <v>444778</v>
       </c>
       <c r="R45" t="n">
-        <v>6846168</v>
+        <v>6846129</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5246,22 +5246,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125038407</v>
+        <v>125046995</v>
       </c>
       <c r="B46" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5274,37 +5274,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444720</v>
+        <v>444528</v>
       </c>
       <c r="R46" t="n">
-        <v>6846606</v>
+        <v>6846366</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5348,22 +5348,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125046797</v>
+        <v>125046956</v>
       </c>
       <c r="B47" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5376,21 +5376,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5400,10 +5400,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444830</v>
+        <v>444822</v>
       </c>
       <c r="R47" t="n">
-        <v>6846275</v>
+        <v>6846368</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6696,10 +6696,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125046980</v>
+        <v>125046716</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6712,21 +6712,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444528</v>
+        <v>444784</v>
       </c>
       <c r="R60" t="n">
-        <v>6846547</v>
+        <v>6846153</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6798,10 +6798,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125047003</v>
+        <v>125046706</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6814,21 +6814,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444514</v>
+        <v>445022</v>
       </c>
       <c r="R61" t="n">
-        <v>6846274</v>
+        <v>6846542</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6900,7 +6900,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125047039</v>
+        <v>125046980</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444637</v>
+        <v>444528</v>
       </c>
       <c r="R62" t="n">
-        <v>6846186</v>
+        <v>6846547</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7002,7 +7002,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125047023</v>
+        <v>125047003</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7042,10 +7042,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444494</v>
+        <v>444514</v>
       </c>
       <c r="R63" t="n">
-        <v>6846160</v>
+        <v>6846274</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7104,7 +7104,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125046969</v>
+        <v>125047039</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444560</v>
+        <v>444637</v>
       </c>
       <c r="R64" t="n">
-        <v>6846584</v>
+        <v>6846186</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125034238</v>
+        <v>125047023</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7242,17 +7242,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444807</v>
+        <v>444494</v>
       </c>
       <c r="R65" t="n">
-        <v>6846285</v>
+        <v>6846160</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7296,19 +7296,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125035654</v>
+        <v>125046969</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7344,17 +7344,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444640</v>
+        <v>444560</v>
       </c>
       <c r="R66" t="n">
-        <v>6846141</v>
+        <v>6846584</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7398,19 +7398,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125046961</v>
+        <v>125034238</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7446,17 +7446,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444747</v>
+        <v>444807</v>
       </c>
       <c r="R67" t="n">
-        <v>6846466</v>
+        <v>6846285</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7500,19 +7500,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125047084</v>
+        <v>125035654</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7548,17 +7548,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445085</v>
+        <v>444640</v>
       </c>
       <c r="R68" t="n">
-        <v>6846391</v>
+        <v>6846141</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7602,19 +7602,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125047065</v>
+        <v>125046961</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7654,10 +7654,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444898</v>
+        <v>444747</v>
       </c>
       <c r="R69" t="n">
-        <v>6846327</v>
+        <v>6846466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7716,7 +7716,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125047001</v>
+        <v>125047084</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7756,10 +7756,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444501</v>
+        <v>445085</v>
       </c>
       <c r="R70" t="n">
-        <v>6846315</v>
+        <v>6846391</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7818,7 +7818,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125038101</v>
+        <v>125047065</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7854,17 +7854,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444754</v>
+        <v>444898</v>
       </c>
       <c r="R71" t="n">
-        <v>6846466</v>
+        <v>6846327</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7908,19 +7908,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125046955</v>
+        <v>125047001</v>
       </c>
       <c r="B72" t="n">
         <v>78810</v>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444885</v>
+        <v>444501</v>
       </c>
       <c r="R72" t="n">
-        <v>6846368</v>
+        <v>6846315</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125047157</v>
+        <v>125038101</v>
       </c>
       <c r="B73" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8038,42 +8038,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444505</v>
+        <v>444754</v>
       </c>
       <c r="R73" t="n">
-        <v>6846397</v>
+        <v>6846466</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8117,22 +8112,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125046767</v>
+        <v>125046955</v>
       </c>
       <c r="B74" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8141,25 +8136,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8169,10 +8164,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444519</v>
+        <v>444885</v>
       </c>
       <c r="R74" t="n">
-        <v>6846154</v>
+        <v>6846368</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8231,10 +8226,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125046716</v>
+        <v>125047157</v>
       </c>
       <c r="B75" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8247,34 +8242,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444784</v>
+        <v>444505</v>
       </c>
       <c r="R75" t="n">
-        <v>6846153</v>
+        <v>6846397</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125046706</v>
+        <v>125046767</v>
       </c>
       <c r="B76" t="n">
-        <v>79399</v>
+        <v>96979</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8345,25 +8345,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445022</v>
+        <v>444519</v>
       </c>
       <c r="R76" t="n">
-        <v>6846542</v>
+        <v>6846154</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9659,10 +9659,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125047025</v>
+        <v>125046715</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9675,21 +9675,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444502</v>
+        <v>444737</v>
       </c>
       <c r="R89" t="n">
-        <v>6846158</v>
+        <v>6846216</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9761,10 +9761,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125039886</v>
+        <v>125046728</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>78905</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9777,37 +9777,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445091</v>
+        <v>444671</v>
       </c>
       <c r="R90" t="n">
-        <v>6846446</v>
+        <v>6846500</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9851,19 +9851,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125037824</v>
+        <v>125047025</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -9899,17 +9899,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444709</v>
+        <v>444502</v>
       </c>
       <c r="R91" t="n">
-        <v>6846425</v>
+        <v>6846158</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9953,22 +9953,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125046715</v>
+        <v>125039886</v>
       </c>
       <c r="B92" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9981,37 +9981,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444737</v>
+        <v>445091</v>
       </c>
       <c r="R92" t="n">
-        <v>6846216</v>
+        <v>6846446</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10055,22 +10055,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125046728</v>
+        <v>125037824</v>
       </c>
       <c r="B93" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10083,37 +10083,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444671</v>
+        <v>444709</v>
       </c>
       <c r="R93" t="n">
-        <v>6846500</v>
+        <v>6846425</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10157,12 +10157,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11903,10 +11903,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125046601</v>
+        <v>125034086</v>
       </c>
       <c r="B111" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11919,37 +11919,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444528</v>
+        <v>444847</v>
       </c>
       <c r="R111" t="n">
-        <v>6846157</v>
+        <v>6846241</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11993,19 +11993,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125034086</v>
+        <v>125047058</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -12041,17 +12041,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444847</v>
+        <v>444837</v>
       </c>
       <c r="R112" t="n">
-        <v>6846241</v>
+        <v>6846289</v>
       </c>
       <c r="S112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12095,19 +12095,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125047058</v>
+        <v>125046951</v>
       </c>
       <c r="B113" t="n">
         <v>78810</v>
@@ -12147,10 +12147,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444837</v>
+        <v>445021</v>
       </c>
       <c r="R113" t="n">
-        <v>6846289</v>
+        <v>6846540</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12209,7 +12209,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125046951</v>
+        <v>125047051</v>
       </c>
       <c r="B114" t="n">
         <v>78810</v>
@@ -12249,10 +12249,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445021</v>
+        <v>444754</v>
       </c>
       <c r="R114" t="n">
-        <v>6846540</v>
+        <v>6846114</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12311,7 +12311,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125047051</v>
+        <v>125039579</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -12347,14 +12347,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>444754</v>
+        <v>445087</v>
       </c>
       <c r="R115" t="n">
-        <v>6846114</v>
+        <v>6846503</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12401,22 +12401,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125039579</v>
+        <v>125046720</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12429,34 +12429,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445087</v>
+        <v>445092</v>
       </c>
       <c r="R116" t="n">
-        <v>6846503</v>
+        <v>6846328</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12503,22 +12503,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125047158</v>
+        <v>125034812</v>
       </c>
       <c r="B117" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12531,42 +12531,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444486</v>
+        <v>444712</v>
       </c>
       <c r="R117" t="n">
-        <v>6846185</v>
+        <v>6846142</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12610,22 +12605,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125046720</v>
+        <v>125046800</v>
       </c>
       <c r="B118" t="n">
-        <v>79399</v>
+        <v>78889</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12638,21 +12633,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12662,10 +12657,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445092</v>
+        <v>444499</v>
       </c>
       <c r="R118" t="n">
-        <v>6846328</v>
+        <v>6846245</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12724,10 +12719,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125034812</v>
+        <v>125046601</v>
       </c>
       <c r="B119" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12740,37 +12735,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>444712</v>
+        <v>444528</v>
       </c>
       <c r="R119" t="n">
-        <v>6846142</v>
+        <v>6846157</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12814,22 +12809,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125046800</v>
+        <v>125047158</v>
       </c>
       <c r="B120" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12842,34 +12837,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>444499</v>
+        <v>444486</v>
       </c>
       <c r="R120" t="n">
-        <v>6846245</v>
+        <v>6846185</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15478,10 +15478,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125047014</v>
+        <v>125038002</v>
       </c>
       <c r="B146" t="n">
-        <v>78810</v>
+        <v>78905</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15494,37 +15494,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>444494</v>
+        <v>444706</v>
       </c>
       <c r="R146" t="n">
-        <v>6846208</v>
+        <v>6846458</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15568,19 +15568,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125047017</v>
+        <v>125047014</v>
       </c>
       <c r="B147" t="n">
         <v>78810</v>
@@ -15620,10 +15620,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>444488</v>
+        <v>444494</v>
       </c>
       <c r="R147" t="n">
-        <v>6846179</v>
+        <v>6846208</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15682,10 +15682,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125046602</v>
+        <v>125047017</v>
       </c>
       <c r="B148" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15698,21 +15698,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15722,10 +15722,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>444748</v>
+        <v>444488</v>
       </c>
       <c r="R148" t="n">
-        <v>6846223</v>
+        <v>6846179</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15784,10 +15784,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125046710</v>
+        <v>125046602</v>
       </c>
       <c r="B149" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15800,21 +15800,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15824,10 +15824,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>444544</v>
+        <v>444748</v>
       </c>
       <c r="R149" t="n">
-        <v>6846359</v>
+        <v>6846223</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15886,10 +15886,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125046737</v>
+        <v>125046975</v>
       </c>
       <c r="B150" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15898,43 +15898,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>444759</v>
+        <v>444544</v>
       </c>
       <c r="R150" t="n">
-        <v>6846476</v>
+        <v>6846567</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15993,10 +15988,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125038002</v>
+        <v>125046999</v>
       </c>
       <c r="B151" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16009,37 +16004,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>444706</v>
+        <v>444520</v>
       </c>
       <c r="R151" t="n">
-        <v>6846458</v>
+        <v>6846337</v>
       </c>
       <c r="S151" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16083,19 +16078,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125046975</v>
+        <v>125038887</v>
       </c>
       <c r="B152" t="n">
         <v>78810</v>
@@ -16131,14 +16126,14 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>444544</v>
+        <v>444847</v>
       </c>
       <c r="R152" t="n">
-        <v>6846567</v>
+        <v>6846563</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16185,19 +16180,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125046999</v>
+        <v>125035307</v>
       </c>
       <c r="B153" t="n">
         <v>78810</v>
@@ -16233,17 +16228,17 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>444520</v>
+        <v>444643</v>
       </c>
       <c r="R153" t="n">
-        <v>6846337</v>
+        <v>6846139</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16287,19 +16282,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125038887</v>
+        <v>125047056</v>
       </c>
       <c r="B154" t="n">
         <v>78810</v>
@@ -16335,14 +16330,14 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>444847</v>
+        <v>444829</v>
       </c>
       <c r="R154" t="n">
-        <v>6846563</v>
+        <v>6846284</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16389,19 +16384,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125035307</v>
+        <v>125046965</v>
       </c>
       <c r="B155" t="n">
         <v>78810</v>
@@ -16437,17 +16432,17 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>444643</v>
+        <v>444601</v>
       </c>
       <c r="R155" t="n">
-        <v>6846139</v>
+        <v>6846489</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16491,22 +16486,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125047056</v>
+        <v>125046737</v>
       </c>
       <c r="B156" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16515,38 +16510,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>444829</v>
+        <v>444759</v>
       </c>
       <c r="R156" t="n">
-        <v>6846284</v>
+        <v>6846476</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16605,10 +16605,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125046965</v>
+        <v>125046710</v>
       </c>
       <c r="B157" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16621,21 +16621,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>444601</v>
+        <v>444544</v>
       </c>
       <c r="R157" t="n">
-        <v>6846489</v>
+        <v>6846359</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18237,10 +18237,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125046742</v>
+        <v>125047063</v>
       </c>
       <c r="B173" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18253,21 +18253,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>444960</v>
+        <v>444866</v>
       </c>
       <c r="R173" t="n">
-        <v>6846416</v>
+        <v>6846312</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18339,10 +18339,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125046799</v>
+        <v>125037445</v>
       </c>
       <c r="B174" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18355,34 +18355,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>444487</v>
+        <v>444529</v>
       </c>
       <c r="R174" t="n">
-        <v>6846220</v>
+        <v>6846249</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18429,19 +18429,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125047045</v>
+        <v>125047066</v>
       </c>
       <c r="B175" t="n">
         <v>78810</v>
@@ -18481,10 +18481,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>444698</v>
+        <v>444930</v>
       </c>
       <c r="R175" t="n">
-        <v>6846210</v>
+        <v>6846308</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18543,7 +18543,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125047035</v>
+        <v>125034167</v>
       </c>
       <c r="B176" t="n">
         <v>78810</v>
@@ -18579,17 +18579,17 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>444612</v>
+        <v>444830</v>
       </c>
       <c r="R176" t="n">
-        <v>6846153</v>
+        <v>6846275</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18633,22 +18633,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>125046972</v>
+        <v>125046799</v>
       </c>
       <c r="B177" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18661,21 +18661,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18685,10 +18685,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>444542</v>
+        <v>444487</v>
       </c>
       <c r="R177" t="n">
-        <v>6846587</v>
+        <v>6846220</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18747,7 +18747,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>125034103</v>
+        <v>125047045</v>
       </c>
       <c r="B178" t="n">
         <v>78810</v>
@@ -18783,17 +18783,17 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>444850</v>
+        <v>444698</v>
       </c>
       <c r="R178" t="n">
-        <v>6846275</v>
+        <v>6846210</v>
       </c>
       <c r="S178" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18837,19 +18837,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>125047063</v>
+        <v>125047035</v>
       </c>
       <c r="B179" t="n">
         <v>78810</v>
@@ -18889,10 +18889,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>444866</v>
+        <v>444612</v>
       </c>
       <c r="R179" t="n">
-        <v>6846312</v>
+        <v>6846153</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18951,7 +18951,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125037445</v>
+        <v>125046972</v>
       </c>
       <c r="B180" t="n">
         <v>78810</v>
@@ -18987,14 +18987,14 @@
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>444529</v>
+        <v>444542</v>
       </c>
       <c r="R180" t="n">
-        <v>6846249</v>
+        <v>6846587</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19041,19 +19041,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125047066</v>
+        <v>125034103</v>
       </c>
       <c r="B181" t="n">
         <v>78810</v>
@@ -19089,17 +19089,17 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>444930</v>
+        <v>444850</v>
       </c>
       <c r="R181" t="n">
-        <v>6846308</v>
+        <v>6846275</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19143,22 +19143,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125034167</v>
+        <v>125046742</v>
       </c>
       <c r="B182" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19171,37 +19171,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>444830</v>
+        <v>444960</v>
       </c>
       <c r="R182" t="n">
-        <v>6846275</v>
+        <v>6846416</v>
       </c>
       <c r="S182" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19245,12 +19245,12 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
@@ -22438,10 +22438,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125047041</v>
+        <v>125046673</v>
       </c>
       <c r="B214" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22454,21 +22454,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22478,10 +22478,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>444642</v>
+        <v>444495</v>
       </c>
       <c r="R214" t="n">
-        <v>6846217</v>
+        <v>6846210</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22540,10 +22540,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>125046673</v>
+        <v>125046970</v>
       </c>
       <c r="B215" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22556,21 +22556,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22580,10 +22580,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>444495</v>
+        <v>444537</v>
       </c>
       <c r="R215" t="n">
-        <v>6846210</v>
+        <v>6846593</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22642,7 +22642,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>125046970</v>
+        <v>125047041</v>
       </c>
       <c r="B216" t="n">
         <v>78810</v>
@@ -22682,10 +22682,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>444537</v>
+        <v>444642</v>
       </c>
       <c r="R216" t="n">
-        <v>6846593</v>
+        <v>6846217</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -27687,10 +27687,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>125046944</v>
+        <v>125042127</v>
       </c>
       <c r="B265" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27703,37 +27703,37 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>445137</v>
+        <v>445538</v>
       </c>
       <c r="R265" t="n">
-        <v>6846572</v>
+        <v>6846416</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -27777,22 +27777,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>125047105</v>
+        <v>125046664</v>
       </c>
       <c r="B266" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27805,21 +27805,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27829,10 +27829,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>445276</v>
+        <v>445463</v>
       </c>
       <c r="R266" t="n">
-        <v>6846526</v>
+        <v>6846541</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27891,10 +27891,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>125046700</v>
+        <v>125046634</v>
       </c>
       <c r="B267" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -27907,21 +27907,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27931,10 +27931,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>445180</v>
+        <v>445653</v>
       </c>
       <c r="R267" t="n">
-        <v>6846446</v>
+        <v>6846540</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27993,10 +27993,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>125046611</v>
+        <v>125046900</v>
       </c>
       <c r="B268" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28009,21 +28009,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -28033,10 +28033,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>445200</v>
+        <v>445553</v>
       </c>
       <c r="R268" t="n">
-        <v>6846496</v>
+        <v>6846445</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28095,10 +28095,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>125042127</v>
+        <v>125046815</v>
       </c>
       <c r="B269" t="n">
-        <v>78842</v>
+        <v>91030</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28111,37 +28111,37 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>445538</v>
+        <v>445196</v>
       </c>
       <c r="R269" t="n">
-        <v>6846416</v>
+        <v>6846474</v>
       </c>
       <c r="S269" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28185,22 +28185,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>125046664</v>
+        <v>125046871</v>
       </c>
       <c r="B270" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28213,21 +28213,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28237,10 +28237,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>445463</v>
+        <v>445782</v>
       </c>
       <c r="R270" t="n">
-        <v>6846541</v>
+        <v>6846455</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28299,10 +28299,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>125046634</v>
+        <v>125046886</v>
       </c>
       <c r="B271" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28315,21 +28315,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28339,10 +28339,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>445653</v>
+        <v>445710</v>
       </c>
       <c r="R271" t="n">
-        <v>6846540</v>
+        <v>6846565</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28401,7 +28401,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>125046900</v>
+        <v>125046889</v>
       </c>
       <c r="B272" t="n">
         <v>78810</v>
@@ -28441,10 +28441,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>445553</v>
+        <v>445693</v>
       </c>
       <c r="R272" t="n">
-        <v>6846445</v>
+        <v>6846539</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28503,10 +28503,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>125046815</v>
+        <v>125046927</v>
       </c>
       <c r="B273" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28519,21 +28519,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28543,10 +28543,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>445196</v>
+        <v>445457</v>
       </c>
       <c r="R273" t="n">
-        <v>6846474</v>
+        <v>6846522</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28605,7 +28605,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>125046871</v>
+        <v>125042223</v>
       </c>
       <c r="B274" t="n">
         <v>78810</v>
@@ -28641,17 +28641,17 @@
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>445782</v>
+        <v>445542</v>
       </c>
       <c r="R274" t="n">
-        <v>6846455</v>
+        <v>6846457</v>
       </c>
       <c r="S274" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -28695,19 +28695,19 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>125046886</v>
+        <v>125046906</v>
       </c>
       <c r="B275" t="n">
         <v>78810</v>
@@ -28747,10 +28747,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>445710</v>
+        <v>445543</v>
       </c>
       <c r="R275" t="n">
-        <v>6846565</v>
+        <v>6846371</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28809,7 +28809,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>125046889</v>
+        <v>125046905</v>
       </c>
       <c r="B276" t="n">
         <v>78810</v>
@@ -28849,10 +28849,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>445693</v>
+        <v>445540</v>
       </c>
       <c r="R276" t="n">
-        <v>6846539</v>
+        <v>6846396</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28911,7 +28911,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>125046927</v>
+        <v>125047126</v>
       </c>
       <c r="B277" t="n">
         <v>78810</v>
@@ -28951,10 +28951,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>445457</v>
+        <v>445595</v>
       </c>
       <c r="R277" t="n">
-        <v>6846522</v>
+        <v>6846250</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -29013,10 +29013,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>125042223</v>
+        <v>125046705</v>
       </c>
       <c r="B278" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -29029,37 +29029,37 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>445542</v>
+        <v>445298</v>
       </c>
       <c r="R278" t="n">
-        <v>6846457</v>
+        <v>6846476</v>
       </c>
       <c r="S278" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -29103,19 +29103,19 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>125046906</v>
+        <v>125046944</v>
       </c>
       <c r="B279" t="n">
         <v>78810</v>
@@ -29155,10 +29155,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>445543</v>
+        <v>445137</v>
       </c>
       <c r="R279" t="n">
-        <v>6846371</v>
+        <v>6846572</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29217,7 +29217,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>125046905</v>
+        <v>125047105</v>
       </c>
       <c r="B280" t="n">
         <v>78810</v>
@@ -29257,10 +29257,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>445540</v>
+        <v>445276</v>
       </c>
       <c r="R280" t="n">
-        <v>6846396</v>
+        <v>6846526</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29319,10 +29319,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>125047126</v>
+        <v>125046700</v>
       </c>
       <c r="B281" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29335,21 +29335,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29359,10 +29359,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>445595</v>
+        <v>445180</v>
       </c>
       <c r="R281" t="n">
-        <v>6846250</v>
+        <v>6846446</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29421,10 +29421,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>125046705</v>
+        <v>125046611</v>
       </c>
       <c r="B282" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29437,21 +29437,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29461,10 +29461,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>445298</v>
+        <v>445200</v>
       </c>
       <c r="R282" t="n">
-        <v>6846476</v>
+        <v>6846496</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29523,10 +29523,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>125047089</v>
+        <v>125046620</v>
       </c>
       <c r="B283" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29539,21 +29539,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -29563,10 +29563,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>445130</v>
+        <v>445616</v>
       </c>
       <c r="R283" t="n">
-        <v>6846433</v>
+        <v>6846232</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29625,10 +29625,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>125040110</v>
+        <v>125046684</v>
       </c>
       <c r="B284" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29641,37 +29641,37 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>445183</v>
+        <v>445419</v>
       </c>
       <c r="R284" t="n">
-        <v>6846527</v>
+        <v>6846447</v>
       </c>
       <c r="S284" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -29715,22 +29715,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>125042608</v>
+        <v>125042629</v>
       </c>
       <c r="B285" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29743,21 +29743,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29767,10 +29767,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>445614</v>
+        <v>445619</v>
       </c>
       <c r="R285" t="n">
-        <v>6846422</v>
+        <v>6846434</v>
       </c>
       <c r="S285" t="n">
         <v>20</v>
@@ -30033,10 +30033,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>125046620</v>
+        <v>125047089</v>
       </c>
       <c r="B288" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -30049,21 +30049,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -30073,10 +30073,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>445616</v>
+        <v>445130</v>
       </c>
       <c r="R288" t="n">
-        <v>6846232</v>
+        <v>6846433</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -30135,10 +30135,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>125046684</v>
+        <v>125040110</v>
       </c>
       <c r="B289" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -30151,37 +30151,37 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>445419</v>
+        <v>445183</v>
       </c>
       <c r="R289" t="n">
-        <v>6846447</v>
+        <v>6846527</v>
       </c>
       <c r="S289" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -30225,22 +30225,22 @@
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>125042629</v>
+        <v>125042608</v>
       </c>
       <c r="B290" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -30253,21 +30253,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -30277,10 +30277,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>445619</v>
+        <v>445614</v>
       </c>
       <c r="R290" t="n">
-        <v>6846434</v>
+        <v>6846422</v>
       </c>
       <c r="S290" t="n">
         <v>20</v>
@@ -31364,10 +31364,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>125046627</v>
+        <v>125043231</v>
       </c>
       <c r="B301" t="n">
-        <v>78842</v>
+        <v>91012</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -31380,37 +31380,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>445760</v>
+        <v>445789</v>
       </c>
       <c r="R301" t="n">
-        <v>6846419</v>
+        <v>6846489</v>
       </c>
       <c r="S301" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -31454,22 +31454,22 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>125046636</v>
+        <v>125046723</v>
       </c>
       <c r="B302" t="n">
-        <v>78842</v>
+        <v>79399</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -31482,21 +31482,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -31506,10 +31506,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>445630</v>
+        <v>445416</v>
       </c>
       <c r="R302" t="n">
-        <v>6846498</v>
+        <v>6846385</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -31568,10 +31568,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>125046686</v>
+        <v>125046703</v>
       </c>
       <c r="B303" t="n">
-        <v>78842</v>
+        <v>79399</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -31584,21 +31584,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -31608,10 +31608,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>445410</v>
+        <v>445461</v>
       </c>
       <c r="R303" t="n">
-        <v>6846399</v>
+        <v>6846503</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -31670,7 +31670,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>125046655</v>
+        <v>125046627</v>
       </c>
       <c r="B304" t="n">
         <v>78842</v>
@@ -31710,10 +31710,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>445501</v>
+        <v>445760</v>
       </c>
       <c r="R304" t="n">
-        <v>6846448</v>
+        <v>6846419</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -31772,7 +31772,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>125046621</v>
+        <v>125046636</v>
       </c>
       <c r="B305" t="n">
         <v>78842</v>
@@ -31815,7 +31815,7 @@
         <v>445630</v>
       </c>
       <c r="R305" t="n">
-        <v>6846312</v>
+        <v>6846498</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -31874,7 +31874,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>125046630</v>
+        <v>125046686</v>
       </c>
       <c r="B306" t="n">
         <v>78842</v>
@@ -31914,10 +31914,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>445773</v>
+        <v>445410</v>
       </c>
       <c r="R306" t="n">
-        <v>6846524</v>
+        <v>6846399</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -31976,7 +31976,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>125046662</v>
+        <v>125046655</v>
       </c>
       <c r="B307" t="n">
         <v>78842</v>
@@ -32016,10 +32016,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>445499</v>
+        <v>445501</v>
       </c>
       <c r="R307" t="n">
-        <v>6846505</v>
+        <v>6846448</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -32078,10 +32078,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>125046861</v>
+        <v>125046621</v>
       </c>
       <c r="B308" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -32094,21 +32094,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -32118,10 +32118,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>445730</v>
+        <v>445630</v>
       </c>
       <c r="R308" t="n">
-        <v>6846366</v>
+        <v>6846312</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -32180,10 +32180,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>125047111</v>
+        <v>125046630</v>
       </c>
       <c r="B309" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -32196,21 +32196,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -32220,10 +32220,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>445392</v>
+        <v>445773</v>
       </c>
       <c r="R309" t="n">
-        <v>6846463</v>
+        <v>6846524</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32282,10 +32282,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>125044623</v>
+        <v>125046662</v>
       </c>
       <c r="B310" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -32298,37 +32298,37 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>445569</v>
+        <v>445499</v>
       </c>
       <c r="R310" t="n">
-        <v>6846111</v>
+        <v>6846505</v>
       </c>
       <c r="S310" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -32372,19 +32372,19 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>125047086</v>
+        <v>125046861</v>
       </c>
       <c r="B311" t="n">
         <v>78810</v>
@@ -32424,10 +32424,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>445120</v>
+        <v>445730</v>
       </c>
       <c r="R311" t="n">
-        <v>6846396</v>
+        <v>6846366</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -32486,7 +32486,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>125042481</v>
+        <v>125047111</v>
       </c>
       <c r="B312" t="n">
         <v>78810</v>
@@ -32522,17 +32522,17 @@
       <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>445595</v>
+        <v>445392</v>
       </c>
       <c r="R312" t="n">
-        <v>6846474</v>
+        <v>6846463</v>
       </c>
       <c r="S312" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -32576,19 +32576,19 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>125046935</v>
+        <v>125044623</v>
       </c>
       <c r="B313" t="n">
         <v>78810</v>
@@ -32624,17 +32624,17 @@
       <c r="I313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>445335</v>
+        <v>445569</v>
       </c>
       <c r="R313" t="n">
-        <v>6846449</v>
+        <v>6846111</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -32678,22 +32678,22 @@
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>125046699</v>
+        <v>125047086</v>
       </c>
       <c r="B314" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -32702,25 +32702,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -32730,10 +32730,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>445461</v>
+        <v>445120</v>
       </c>
       <c r="R314" t="n">
-        <v>6846541</v>
+        <v>6846396</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -32792,10 +32792,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>125046766</v>
+        <v>125042481</v>
       </c>
       <c r="B315" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -32804,41 +32804,41 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>445478</v>
+        <v>445595</v>
       </c>
       <c r="R315" t="n">
-        <v>6846122</v>
+        <v>6846474</v>
       </c>
       <c r="S315" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -32882,22 +32882,22 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>125046723</v>
+        <v>125046935</v>
       </c>
       <c r="B316" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -32910,21 +32910,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -32934,10 +32934,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>445416</v>
+        <v>445335</v>
       </c>
       <c r="R316" t="n">
-        <v>6846385</v>
+        <v>6846449</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -32996,10 +32996,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>125046703</v>
+        <v>125046699</v>
       </c>
       <c r="B317" t="n">
-        <v>79399</v>
+        <v>90977</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -33008,25 +33008,25 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -33039,7 +33039,7 @@
         <v>445461</v>
       </c>
       <c r="R317" t="n">
-        <v>6846503</v>
+        <v>6846541</v>
       </c>
       <c r="S317" t="n">
         <v>10</v>
@@ -33098,10 +33098,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>125043231</v>
+        <v>125046766</v>
       </c>
       <c r="B318" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -33110,41 +33110,41 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>445789</v>
+        <v>445478</v>
       </c>
       <c r="R318" t="n">
-        <v>6846489</v>
+        <v>6846122</v>
       </c>
       <c r="S318" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -33188,12 +33188,12 @@
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
@@ -34832,10 +34832,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>125046694</v>
+        <v>125047154</v>
       </c>
       <c r="B335" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -34848,34 +34848,39 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P335" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>445591</v>
+        <v>445783</v>
       </c>
       <c r="R335" t="n">
-        <v>6846253</v>
+        <v>6846451</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -34934,7 +34939,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125046638</v>
+        <v>125046694</v>
       </c>
       <c r="B336" t="n">
         <v>78842</v>
@@ -34974,10 +34979,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>445609</v>
+        <v>445591</v>
       </c>
       <c r="R336" t="n">
-        <v>6846474</v>
+        <v>6846253</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -35036,10 +35041,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125046845</v>
+        <v>125046638</v>
       </c>
       <c r="B337" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -35052,21 +35057,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -35076,10 +35081,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>445477</v>
+        <v>445609</v>
       </c>
       <c r="R337" t="n">
-        <v>6846122</v>
+        <v>6846474</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -35138,10 +35143,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125046846</v>
+        <v>125046743</v>
       </c>
       <c r="B338" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -35154,21 +35159,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -35178,10 +35183,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>445508</v>
+        <v>445427</v>
       </c>
       <c r="R338" t="n">
-        <v>6846149</v>
+        <v>6846297</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -35240,10 +35245,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125047172</v>
+        <v>125046731</v>
       </c>
       <c r="B339" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -35252,43 +35257,38 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>445593</v>
+        <v>445553</v>
       </c>
       <c r="R339" t="n">
-        <v>6846250</v>
+        <v>6846445</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -35347,10 +35347,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125046743</v>
+        <v>125046845</v>
       </c>
       <c r="B340" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -35363,21 +35363,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -35387,10 +35387,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>445427</v>
+        <v>445477</v>
       </c>
       <c r="R340" t="n">
-        <v>6846297</v>
+        <v>6846122</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -35449,10 +35449,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>125046731</v>
+        <v>125046846</v>
       </c>
       <c r="B341" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -35465,21 +35465,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -35489,10 +35489,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>445553</v>
+        <v>445508</v>
       </c>
       <c r="R341" t="n">
-        <v>6846445</v>
+        <v>6846149</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -35755,10 +35755,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>125047154</v>
+        <v>125047172</v>
       </c>
       <c r="B344" t="n">
-        <v>57513</v>
+        <v>5176</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -35767,31 +35767,31 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
       <c r="M344" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
@@ -35800,10 +35800,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>445783</v>
+        <v>445593</v>
       </c>
       <c r="R344" t="n">
-        <v>6846451</v>
+        <v>6846250</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -37295,7 +37295,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125046647</v>
+        <v>125043358</v>
       </c>
       <c r="B359" t="n">
         <v>78842</v>
@@ -37331,17 +37331,17 @@
       <c r="I359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>445561</v>
+        <v>445763</v>
       </c>
       <c r="R359" t="n">
-        <v>6846419</v>
+        <v>6846407</v>
       </c>
       <c r="S359" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -37385,19 +37385,19 @@
       <c r="AT359" t="inlineStr"/>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125043358</v>
+        <v>125046624</v>
       </c>
       <c r="B360" t="n">
         <v>78842</v>
@@ -37433,17 +37433,17 @@
       <c r="I360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>445763</v>
+        <v>445700</v>
       </c>
       <c r="R360" t="n">
-        <v>6846407</v>
+        <v>6846331</v>
       </c>
       <c r="S360" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -37487,19 +37487,19 @@
       <c r="AT360" t="inlineStr"/>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>125046624</v>
+        <v>125042970</v>
       </c>
       <c r="B361" t="n">
         <v>78842</v>
@@ -37535,17 +37535,17 @@
       <c r="I361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>445700</v>
+        <v>445734</v>
       </c>
       <c r="R361" t="n">
-        <v>6846331</v>
+        <v>6846477</v>
       </c>
       <c r="S361" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -37589,19 +37589,19 @@
       <c r="AT361" t="inlineStr"/>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>125042970</v>
+        <v>125046614</v>
       </c>
       <c r="B362" t="n">
         <v>78842</v>
@@ -37637,17 +37637,17 @@
       <c r="I362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>445734</v>
+        <v>445418</v>
       </c>
       <c r="R362" t="n">
-        <v>6846477</v>
+        <v>6846058</v>
       </c>
       <c r="S362" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -37691,22 +37691,22 @@
       <c r="AT362" t="inlineStr"/>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>125046614</v>
+        <v>125046854</v>
       </c>
       <c r="B363" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -37719,21 +37719,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
@@ -37743,10 +37743,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>445418</v>
+        <v>445654</v>
       </c>
       <c r="R363" t="n">
-        <v>6846058</v>
+        <v>6846310</v>
       </c>
       <c r="S363" t="n">
         <v>10</v>
@@ -37805,7 +37805,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>125046854</v>
+        <v>125046850</v>
       </c>
       <c r="B364" t="n">
         <v>78810</v>
@@ -37845,10 +37845,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>445654</v>
+        <v>445643</v>
       </c>
       <c r="R364" t="n">
-        <v>6846310</v>
+        <v>6846253</v>
       </c>
       <c r="S364" t="n">
         <v>10</v>
@@ -37907,7 +37907,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>125046850</v>
+        <v>125047079</v>
       </c>
       <c r="B365" t="n">
         <v>78810</v>
@@ -37947,10 +37947,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>445643</v>
+        <v>445117</v>
       </c>
       <c r="R365" t="n">
-        <v>6846253</v>
+        <v>6846339</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -38009,7 +38009,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>125047079</v>
+        <v>125046851</v>
       </c>
       <c r="B366" t="n">
         <v>78810</v>
@@ -38049,10 +38049,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>445117</v>
+        <v>445635</v>
       </c>
       <c r="R366" t="n">
-        <v>6846339</v>
+        <v>6846279</v>
       </c>
       <c r="S366" t="n">
         <v>10</v>
@@ -38111,7 +38111,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>125046851</v>
+        <v>125046839</v>
       </c>
       <c r="B367" t="n">
         <v>78810</v>
@@ -38151,10 +38151,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>445635</v>
+        <v>445488</v>
       </c>
       <c r="R367" t="n">
-        <v>6846279</v>
+        <v>6846039</v>
       </c>
       <c r="S367" t="n">
         <v>10</v>
@@ -38213,7 +38213,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>125046839</v>
+        <v>125046942</v>
       </c>
       <c r="B368" t="n">
         <v>78810</v>
@@ -38253,10 +38253,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>445488</v>
+        <v>445174</v>
       </c>
       <c r="R368" t="n">
-        <v>6846039</v>
+        <v>6846523</v>
       </c>
       <c r="S368" t="n">
         <v>10</v>
@@ -38315,7 +38315,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>125046942</v>
+        <v>125046891</v>
       </c>
       <c r="B369" t="n">
         <v>78810</v>
@@ -38355,10 +38355,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>445174</v>
+        <v>445648</v>
       </c>
       <c r="R369" t="n">
-        <v>6846523</v>
+        <v>6846524</v>
       </c>
       <c r="S369" t="n">
         <v>10</v>
@@ -38417,10 +38417,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>125046610</v>
+        <v>125047124</v>
       </c>
       <c r="B370" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -38433,21 +38433,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I370" t="inlineStr"/>
@@ -38457,10 +38457,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>445149</v>
+        <v>445517</v>
       </c>
       <c r="R370" t="n">
-        <v>6846429</v>
+        <v>6846232</v>
       </c>
       <c r="S370" t="n">
         <v>10</v>
@@ -38519,7 +38519,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>125046891</v>
+        <v>125047109</v>
       </c>
       <c r="B371" t="n">
         <v>78810</v>
@@ -38559,10 +38559,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>445648</v>
+        <v>445379</v>
       </c>
       <c r="R371" t="n">
-        <v>6846524</v>
+        <v>6846474</v>
       </c>
       <c r="S371" t="n">
         <v>10</v>
@@ -38621,7 +38621,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>125047124</v>
+        <v>125046869</v>
       </c>
       <c r="B372" t="n">
         <v>78810</v>
@@ -38661,10 +38661,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>445517</v>
+        <v>445765</v>
       </c>
       <c r="R372" t="n">
-        <v>6846232</v>
+        <v>6846447</v>
       </c>
       <c r="S372" t="n">
         <v>10</v>
@@ -38723,10 +38723,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>125047109</v>
+        <v>125041091</v>
       </c>
       <c r="B373" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -38735,41 +38735,41 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I373" t="inlineStr"/>
       <c r="P373" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>445379</v>
+        <v>445462</v>
       </c>
       <c r="R373" t="n">
-        <v>6846474</v>
+        <v>6846286</v>
       </c>
       <c r="S373" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -38799,6 +38799,11 @@
       <c r="AA373" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall.</t>
         </is>
       </c>
       <c r="AD373" t="b">
@@ -38813,22 +38818,22 @@
       <c r="AT373" t="inlineStr"/>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>125046869</v>
+        <v>125046789</v>
       </c>
       <c r="B374" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -38841,21 +38846,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I374" t="inlineStr"/>
@@ -38865,10 +38870,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>445765</v>
+        <v>445105</v>
       </c>
       <c r="R374" t="n">
-        <v>6846447</v>
+        <v>6846415</v>
       </c>
       <c r="S374" t="n">
         <v>10</v>
@@ -38927,10 +38932,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>125041091</v>
+        <v>125046790</v>
       </c>
       <c r="B375" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -38939,41 +38944,41 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
       <c r="P375" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>445462</v>
+        <v>445278</v>
       </c>
       <c r="R375" t="n">
-        <v>6846286</v>
+        <v>6846531</v>
       </c>
       <c r="S375" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T375" t="inlineStr">
         <is>
@@ -39003,11 +39008,6 @@
       <c r="AA375" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall.</t>
         </is>
       </c>
       <c r="AD375" t="b">
@@ -39022,22 +39022,22 @@
       <c r="AT375" t="inlineStr"/>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>125047151</v>
+        <v>125046783</v>
       </c>
       <c r="B376" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -39050,39 +39050,34 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I376" t="inlineStr"/>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P376" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>445414</v>
+        <v>445681</v>
       </c>
       <c r="R376" t="n">
-        <v>6846069</v>
+        <v>6846547</v>
       </c>
       <c r="S376" t="n">
         <v>10</v>
@@ -39141,10 +39136,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>125047176</v>
+        <v>125046701</v>
       </c>
       <c r="B377" t="n">
-        <v>57513</v>
+        <v>79399</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -39157,39 +39152,34 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I377" t="inlineStr"/>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P377" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>445645</v>
+        <v>445682</v>
       </c>
       <c r="R377" t="n">
-        <v>6846261</v>
+        <v>6846547</v>
       </c>
       <c r="S377" t="n">
         <v>10</v>
@@ -39248,10 +39238,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>125046789</v>
+        <v>125046647</v>
       </c>
       <c r="B378" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -39264,21 +39254,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I378" t="inlineStr"/>
@@ -39288,10 +39278,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>445105</v>
+        <v>445561</v>
       </c>
       <c r="R378" t="n">
-        <v>6846415</v>
+        <v>6846419</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -39350,10 +39340,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>125046790</v>
+        <v>125046610</v>
       </c>
       <c r="B379" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -39366,21 +39356,21 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
@@ -39390,10 +39380,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>445278</v>
+        <v>445149</v>
       </c>
       <c r="R379" t="n">
-        <v>6846531</v>
+        <v>6846429</v>
       </c>
       <c r="S379" t="n">
         <v>10</v>
@@ -39452,10 +39442,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>125046783</v>
+        <v>125047151</v>
       </c>
       <c r="B380" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -39468,34 +39458,39 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr"/>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P380" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>445681</v>
+        <v>445414</v>
       </c>
       <c r="R380" t="n">
-        <v>6846547</v>
+        <v>6846069</v>
       </c>
       <c r="S380" t="n">
         <v>10</v>
@@ -39554,10 +39549,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>125046701</v>
+        <v>125047176</v>
       </c>
       <c r="B381" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -39570,34 +39565,39 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P381" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>445682</v>
+        <v>445645</v>
       </c>
       <c r="R381" t="n">
-        <v>6846547</v>
+        <v>6846261</v>
       </c>
       <c r="S381" t="n">
         <v>10</v>
@@ -43129,10 +43129,10 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>125047107</v>
+        <v>125046625</v>
       </c>
       <c r="B416" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -43145,21 +43145,21 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I416" t="inlineStr"/>
@@ -43169,10 +43169,10 @@
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>445358</v>
+        <v>445730</v>
       </c>
       <c r="R416" t="n">
-        <v>6846488</v>
+        <v>6846366</v>
       </c>
       <c r="S416" t="n">
         <v>10</v>
@@ -43231,10 +43231,10 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>125047077</v>
+        <v>125046629</v>
       </c>
       <c r="B417" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -43247,21 +43247,21 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I417" t="inlineStr"/>
@@ -43271,10 +43271,10 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>445108</v>
+        <v>445792</v>
       </c>
       <c r="R417" t="n">
-        <v>6846332</v>
+        <v>6846513</v>
       </c>
       <c r="S417" t="n">
         <v>10</v>
@@ -43333,10 +43333,10 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>125043563</v>
+        <v>125046667</v>
       </c>
       <c r="B418" t="n">
-        <v>57513</v>
+        <v>78842</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -43349,37 +43349,37 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I418" t="inlineStr"/>
       <c r="P418" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>445716</v>
+        <v>445339</v>
       </c>
       <c r="R418" t="n">
-        <v>6846382</v>
+        <v>6846438</v>
       </c>
       <c r="S418" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -43409,11 +43409,6 @@
       <c r="AA418" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC418" t="inlineStr">
-        <is>
-          <t>Hackspår på granstam.</t>
         </is>
       </c>
       <c r="AD418" t="b">
@@ -43428,22 +43423,22 @@
       <c r="AT418" t="inlineStr"/>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>125046625</v>
+        <v>125033708</v>
       </c>
       <c r="B419" t="n">
-        <v>78842</v>
+        <v>78905</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -43456,37 +43451,37 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I419" t="inlineStr"/>
       <c r="P419" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>445730</v>
+        <v>445144</v>
       </c>
       <c r="R419" t="n">
-        <v>6846366</v>
+        <v>6846374</v>
       </c>
       <c r="S419" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -43530,22 +43525,22 @@
       <c r="AT419" t="inlineStr"/>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>125046629</v>
+        <v>125047107</v>
       </c>
       <c r="B420" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -43558,21 +43553,21 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I420" t="inlineStr"/>
@@ -43582,10 +43577,10 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>445792</v>
+        <v>445358</v>
       </c>
       <c r="R420" t="n">
-        <v>6846513</v>
+        <v>6846488</v>
       </c>
       <c r="S420" t="n">
         <v>10</v>
@@ -43644,10 +43639,10 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>125046667</v>
+        <v>125047077</v>
       </c>
       <c r="B421" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -43660,21 +43655,21 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I421" t="inlineStr"/>
@@ -43684,10 +43679,10 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>445339</v>
+        <v>445108</v>
       </c>
       <c r="R421" t="n">
-        <v>6846438</v>
+        <v>6846332</v>
       </c>
       <c r="S421" t="n">
         <v>10</v>
@@ -43746,10 +43741,10 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>125033708</v>
+        <v>125046665</v>
       </c>
       <c r="B422" t="n">
-        <v>78905</v>
+        <v>78842</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -43762,37 +43757,37 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I422" t="inlineStr"/>
       <c r="P422" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>445144</v>
+        <v>445375</v>
       </c>
       <c r="R422" t="n">
-        <v>6846374</v>
+        <v>6846474</v>
       </c>
       <c r="S422" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -43836,22 +43831,22 @@
       <c r="AT422" t="inlineStr"/>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>125046665</v>
+        <v>125042176</v>
       </c>
       <c r="B423" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -43864,37 +43859,37 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I423" t="inlineStr"/>
       <c r="P423" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>445375</v>
+        <v>445540</v>
       </c>
       <c r="R423" t="n">
-        <v>6846474</v>
+        <v>6846431</v>
       </c>
       <c r="S423" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -43938,19 +43933,19 @@
       <c r="AT423" t="inlineStr"/>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>125042176</v>
+        <v>125046940</v>
       </c>
       <c r="B424" t="n">
         <v>78810</v>
@@ -43986,17 +43981,17 @@
       <c r="I424" t="inlineStr"/>
       <c r="P424" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>445540</v>
+        <v>445218</v>
       </c>
       <c r="R424" t="n">
-        <v>6846431</v>
+        <v>6846526</v>
       </c>
       <c r="S424" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -44040,19 +44035,19 @@
       <c r="AT424" t="inlineStr"/>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>125046940</v>
+        <v>125047094</v>
       </c>
       <c r="B425" t="n">
         <v>78810</v>
@@ -44092,10 +44087,10 @@
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>445218</v>
+        <v>445172</v>
       </c>
       <c r="R425" t="n">
-        <v>6846526</v>
+        <v>6846437</v>
       </c>
       <c r="S425" t="n">
         <v>10</v>
@@ -44154,10 +44149,10 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>125047094</v>
+        <v>125046811</v>
       </c>
       <c r="B426" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -44170,21 +44165,21 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
@@ -44194,10 +44189,10 @@
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>445172</v>
+        <v>445791</v>
       </c>
       <c r="R426" t="n">
-        <v>6846437</v>
+        <v>6846476</v>
       </c>
       <c r="S426" t="n">
         <v>10</v>
@@ -44256,10 +44251,10 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>125046811</v>
+        <v>125046888</v>
       </c>
       <c r="B427" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -44272,21 +44267,21 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
@@ -44296,10 +44291,10 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>445791</v>
+        <v>445691</v>
       </c>
       <c r="R427" t="n">
-        <v>6846476</v>
+        <v>6846537</v>
       </c>
       <c r="S427" t="n">
         <v>10</v>
@@ -44358,7 +44353,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>125046888</v>
+        <v>125033575</v>
       </c>
       <c r="B428" t="n">
         <v>78810</v>
@@ -44394,14 +44389,14 @@
       <c r="I428" t="inlineStr"/>
       <c r="P428" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>445691</v>
+        <v>445136</v>
       </c>
       <c r="R428" t="n">
-        <v>6846537</v>
+        <v>6846374</v>
       </c>
       <c r="S428" t="n">
         <v>10</v>
@@ -44448,22 +44443,22 @@
       <c r="AT428" t="inlineStr"/>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>125033575</v>
+        <v>125042795</v>
       </c>
       <c r="B429" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -44472,25 +44467,25 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I429" t="inlineStr"/>
@@ -44500,13 +44495,13 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>445136</v>
+        <v>445688</v>
       </c>
       <c r="R429" t="n">
-        <v>6846374</v>
+        <v>6846464</v>
       </c>
       <c r="S429" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T429" t="inlineStr">
         <is>
@@ -44562,10 +44557,10 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>125042795</v>
+        <v>125046809</v>
       </c>
       <c r="B430" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -44574,41 +44569,41 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I430" t="inlineStr"/>
       <c r="P430" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>445688</v>
+        <v>445644</v>
       </c>
       <c r="R430" t="n">
-        <v>6846464</v>
+        <v>6846260</v>
       </c>
       <c r="S430" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T430" t="inlineStr">
         <is>
@@ -44652,22 +44647,22 @@
       <c r="AT430" t="inlineStr"/>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>125046809</v>
+        <v>125047096</v>
       </c>
       <c r="B431" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -44680,21 +44675,21 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I431" t="inlineStr"/>
@@ -44704,10 +44699,10 @@
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>445644</v>
+        <v>445181</v>
       </c>
       <c r="R431" t="n">
-        <v>6846260</v>
+        <v>6846450</v>
       </c>
       <c r="S431" t="n">
         <v>10</v>
@@ -44766,10 +44761,10 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>125047096</v>
+        <v>125046813</v>
       </c>
       <c r="B432" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -44782,21 +44777,21 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I432" t="inlineStr"/>
@@ -44806,10 +44801,10 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>445181</v>
+        <v>445597</v>
       </c>
       <c r="R432" t="n">
-        <v>6846450</v>
+        <v>6846492</v>
       </c>
       <c r="S432" t="n">
         <v>10</v>
@@ -44868,10 +44863,10 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>125046813</v>
+        <v>125043563</v>
       </c>
       <c r="B433" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -44884,37 +44879,37 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I433" t="inlineStr"/>
       <c r="P433" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>445597</v>
+        <v>445716</v>
       </c>
       <c r="R433" t="n">
-        <v>6846492</v>
+        <v>6846382</v>
       </c>
       <c r="S433" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -44944,6 +44939,11 @@
       <c r="AA433" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC433" t="inlineStr">
+        <is>
+          <t>Hackspår på granstam.</t>
         </is>
       </c>
       <c r="AD433" t="b">
@@ -44958,12 +44958,12 @@
       <c r="AT433" t="inlineStr"/>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
@@ -46709,10 +46709,10 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>125046690</v>
+        <v>125046585</v>
       </c>
       <c r="B451" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -46725,21 +46725,21 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I451" t="inlineStr"/>
@@ -46749,10 +46749,10 @@
         </is>
       </c>
       <c r="Q451" t="n">
-        <v>445424</v>
+        <v>445710</v>
       </c>
       <c r="R451" t="n">
-        <v>6846307</v>
+        <v>6846548</v>
       </c>
       <c r="S451" t="n">
         <v>10</v>
@@ -46811,10 +46811,10 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>125043851</v>
+        <v>125046605</v>
       </c>
       <c r="B452" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -46827,37 +46827,37 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I452" t="inlineStr"/>
       <c r="P452" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q452" t="n">
-        <v>445702</v>
+        <v>445117</v>
       </c>
       <c r="R452" t="n">
-        <v>6846338</v>
+        <v>6846341</v>
       </c>
       <c r="S452" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -46901,19 +46901,19 @@
       <c r="AT452" t="inlineStr"/>
       <c r="AW452" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX452" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>125046585</v>
+        <v>125046590</v>
       </c>
       <c r="B453" t="n">
         <v>79428</v>
@@ -46953,10 +46953,10 @@
         </is>
       </c>
       <c r="Q453" t="n">
-        <v>445710</v>
+        <v>445294</v>
       </c>
       <c r="R453" t="n">
-        <v>6846548</v>
+        <v>6846485</v>
       </c>
       <c r="S453" t="n">
         <v>10</v>
@@ -47015,10 +47015,10 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>125046605</v>
+        <v>125046920</v>
       </c>
       <c r="B454" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -47031,21 +47031,21 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I454" t="inlineStr"/>
@@ -47055,10 +47055,10 @@
         </is>
       </c>
       <c r="Q454" t="n">
-        <v>445117</v>
+        <v>445507</v>
       </c>
       <c r="R454" t="n">
-        <v>6846341</v>
+        <v>6846521</v>
       </c>
       <c r="S454" t="n">
         <v>10</v>
@@ -47117,10 +47117,10 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>125046590</v>
+        <v>125046937</v>
       </c>
       <c r="B455" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -47133,21 +47133,21 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I455" t="inlineStr"/>
@@ -47157,10 +47157,10 @@
         </is>
       </c>
       <c r="Q455" t="n">
-        <v>445294</v>
+        <v>445287</v>
       </c>
       <c r="R455" t="n">
-        <v>6846485</v>
+        <v>6846496</v>
       </c>
       <c r="S455" t="n">
         <v>10</v>
@@ -47219,10 +47219,10 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>125046808</v>
+        <v>125047097</v>
       </c>
       <c r="B456" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -47231,25 +47231,25 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I456" t="inlineStr"/>
@@ -47259,10 +47259,10 @@
         </is>
       </c>
       <c r="Q456" t="n">
-        <v>445463</v>
+        <v>445192</v>
       </c>
       <c r="R456" t="n">
-        <v>6846497</v>
+        <v>6846484</v>
       </c>
       <c r="S456" t="n">
         <v>10</v>
@@ -47321,7 +47321,7 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>125046920</v>
+        <v>125046887</v>
       </c>
       <c r="B457" t="n">
         <v>78810</v>
@@ -47361,10 +47361,10 @@
         </is>
       </c>
       <c r="Q457" t="n">
-        <v>445507</v>
+        <v>445718</v>
       </c>
       <c r="R457" t="n">
-        <v>6846521</v>
+        <v>6846552</v>
       </c>
       <c r="S457" t="n">
         <v>10</v>
@@ -47423,7 +47423,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>125046937</v>
+        <v>125046872</v>
       </c>
       <c r="B458" t="n">
         <v>78810</v>
@@ -47463,10 +47463,10 @@
         </is>
       </c>
       <c r="Q458" t="n">
-        <v>445287</v>
+        <v>445792</v>
       </c>
       <c r="R458" t="n">
-        <v>6846496</v>
+        <v>6846472</v>
       </c>
       <c r="S458" t="n">
         <v>10</v>
@@ -47525,10 +47525,10 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>125047097</v>
+        <v>125046808</v>
       </c>
       <c r="B459" t="n">
-        <v>78810</v>
+        <v>91172</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -47537,25 +47537,25 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I459" t="inlineStr"/>
@@ -47565,10 +47565,10 @@
         </is>
       </c>
       <c r="Q459" t="n">
-        <v>445192</v>
+        <v>445463</v>
       </c>
       <c r="R459" t="n">
-        <v>6846484</v>
+        <v>6846497</v>
       </c>
       <c r="S459" t="n">
         <v>10</v>
@@ -47627,10 +47627,10 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>125046887</v>
+        <v>125046690</v>
       </c>
       <c r="B460" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -47643,21 +47643,21 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I460" t="inlineStr"/>
@@ -47667,10 +47667,10 @@
         </is>
       </c>
       <c r="Q460" t="n">
-        <v>445718</v>
+        <v>445424</v>
       </c>
       <c r="R460" t="n">
-        <v>6846552</v>
+        <v>6846307</v>
       </c>
       <c r="S460" t="n">
         <v>10</v>
@@ -47729,10 +47729,10 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>125046872</v>
+        <v>125043851</v>
       </c>
       <c r="B461" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -47745,37 +47745,37 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I461" t="inlineStr"/>
       <c r="P461" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q461" t="n">
-        <v>445792</v>
+        <v>445702</v>
       </c>
       <c r="R461" t="n">
-        <v>6846472</v>
+        <v>6846338</v>
       </c>
       <c r="S461" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T461" t="inlineStr">
         <is>
@@ -47819,12 +47819,12 @@
       <c r="AT461" t="inlineStr"/>
       <c r="AW461" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX461" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY461" t="inlineStr"/>
@@ -52018,10 +52018,10 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>125046795</v>
+        <v>125046727</v>
       </c>
       <c r="B503" t="n">
-        <v>80763</v>
+        <v>78905</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -52034,21 +52034,21 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>1049</v>
+        <v>967</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I503" t="inlineStr"/>
@@ -52058,10 +52058,10 @@
         </is>
       </c>
       <c r="Q503" t="n">
-        <v>445335</v>
+        <v>445106</v>
       </c>
       <c r="R503" t="n">
-        <v>6846442</v>
+        <v>6846414</v>
       </c>
       <c r="S503" t="n">
         <v>10</v>
@@ -52120,10 +52120,10 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>125046727</v>
+        <v>125046795</v>
       </c>
       <c r="B504" t="n">
-        <v>78905</v>
+        <v>80763</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -52136,21 +52136,21 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>967</v>
+        <v>1049</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I504" t="inlineStr"/>
@@ -52160,10 +52160,10 @@
         </is>
       </c>
       <c r="Q504" t="n">
-        <v>445106</v>
+        <v>445335</v>
       </c>
       <c r="R504" t="n">
-        <v>6846414</v>
+        <v>6846442</v>
       </c>
       <c r="S504" t="n">
         <v>10</v>
@@ -52737,10 +52737,10 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>125046848</v>
+        <v>125046794</v>
       </c>
       <c r="B510" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -52753,21 +52753,21 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I510" t="inlineStr"/>
@@ -52777,10 +52777,10 @@
         </is>
       </c>
       <c r="Q510" t="n">
-        <v>445555</v>
+        <v>445622</v>
       </c>
       <c r="R510" t="n">
-        <v>6846181</v>
+        <v>6846518</v>
       </c>
       <c r="S510" t="n">
         <v>10</v>
@@ -52839,10 +52839,10 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>125046794</v>
+        <v>125046623</v>
       </c>
       <c r="B511" t="n">
-        <v>80763</v>
+        <v>78842</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -52855,21 +52855,21 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I511" t="inlineStr"/>
@@ -52879,10 +52879,10 @@
         </is>
       </c>
       <c r="Q511" t="n">
-        <v>445622</v>
+        <v>445684</v>
       </c>
       <c r="R511" t="n">
-        <v>6846518</v>
+        <v>6846335</v>
       </c>
       <c r="S511" t="n">
         <v>10</v>
@@ -52941,7 +52941,7 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>125046623</v>
+        <v>125040082</v>
       </c>
       <c r="B512" t="n">
         <v>78842</v>
@@ -52977,17 +52977,17 @@
       <c r="I512" t="inlineStr"/>
       <c r="P512" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q512" t="n">
-        <v>445684</v>
+        <v>445167</v>
       </c>
       <c r="R512" t="n">
-        <v>6846335</v>
+        <v>6846498</v>
       </c>
       <c r="S512" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -53031,19 +53031,19 @@
       <c r="AT512" t="inlineStr"/>
       <c r="AW512" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX512" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>125040082</v>
+        <v>125046682</v>
       </c>
       <c r="B513" t="n">
         <v>78842</v>
@@ -53079,17 +53079,17 @@
       <c r="I513" t="inlineStr"/>
       <c r="P513" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q513" t="n">
-        <v>445167</v>
+        <v>445276</v>
       </c>
       <c r="R513" t="n">
-        <v>6846498</v>
+        <v>6846526</v>
       </c>
       <c r="S513" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
@@ -53133,22 +53133,22 @@
       <c r="AT513" t="inlineStr"/>
       <c r="AW513" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX513" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>125046682</v>
+        <v>125042845</v>
       </c>
       <c r="B514" t="n">
-        <v>78842</v>
+        <v>88359</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -53161,37 +53161,37 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I514" t="inlineStr"/>
       <c r="P514" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q514" t="n">
-        <v>445276</v>
+        <v>445688</v>
       </c>
       <c r="R514" t="n">
-        <v>6846526</v>
+        <v>6846464</v>
       </c>
       <c r="S514" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
@@ -53235,22 +53235,22 @@
       <c r="AT514" t="inlineStr"/>
       <c r="AW514" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX514" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>125042845</v>
+        <v>125046652</v>
       </c>
       <c r="B515" t="n">
-        <v>88359</v>
+        <v>78842</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -53263,37 +53263,37 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I515" t="inlineStr"/>
       <c r="P515" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q515" t="n">
-        <v>445688</v>
+        <v>445509</v>
       </c>
       <c r="R515" t="n">
-        <v>6846464</v>
+        <v>6846409</v>
       </c>
       <c r="S515" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T515" t="inlineStr">
         <is>
@@ -53337,22 +53337,22 @@
       <c r="AT515" t="inlineStr"/>
       <c r="AW515" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX515" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>125046652</v>
+        <v>125046848</v>
       </c>
       <c r="B516" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -53365,21 +53365,21 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I516" t="inlineStr"/>
@@ -53389,10 +53389,10 @@
         </is>
       </c>
       <c r="Q516" t="n">
-        <v>445509</v>
+        <v>445555</v>
       </c>
       <c r="R516" t="n">
-        <v>6846409</v>
+        <v>6846181</v>
       </c>
       <c r="S516" t="n">
         <v>10</v>

--- a/artfynd/A 18557-2025 artfynd.xlsx
+++ b/artfynd/A 18557-2025 artfynd.xlsx
@@ -5569,10 +5569,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125046949</v>
+        <v>125046797</v>
       </c>
       <c r="B49" t="n">
-        <v>78947</v>
+        <v>80900</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5585,21 +5585,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445036</v>
+        <v>444830</v>
       </c>
       <c r="R49" t="n">
-        <v>6846538</v>
+        <v>6846275</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5671,7 +5671,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125047004</v>
+        <v>125046949</v>
       </c>
       <c r="B50" t="n">
         <v>78947</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444496</v>
+        <v>445036</v>
       </c>
       <c r="R50" t="n">
-        <v>6846293</v>
+        <v>6846538</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125047036</v>
+        <v>125047004</v>
       </c>
       <c r="B51" t="n">
         <v>78947</v>
@@ -5813,10 +5813,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444614</v>
+        <v>444496</v>
       </c>
       <c r="R51" t="n">
-        <v>6846159</v>
+        <v>6846293</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5875,7 +5875,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125047027</v>
+        <v>125047036</v>
       </c>
       <c r="B52" t="n">
         <v>78947</v>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444529</v>
+        <v>444614</v>
       </c>
       <c r="R52" t="n">
-        <v>6846143</v>
+        <v>6846159</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,10 +5977,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125046599</v>
+        <v>125047027</v>
       </c>
       <c r="B53" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5993,21 +5993,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444520</v>
+        <v>444529</v>
       </c>
       <c r="R53" t="n">
-        <v>6846480</v>
+        <v>6846143</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125046797</v>
+        <v>125046599</v>
       </c>
       <c r="B54" t="n">
-        <v>80900</v>
+        <v>79565</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6095,21 +6095,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6119,10 +6119,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444830</v>
+        <v>444520</v>
       </c>
       <c r="R54" t="n">
-        <v>6846275</v>
+        <v>6846480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6487,10 +6487,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125046709</v>
+        <v>125039726</v>
       </c>
       <c r="B58" t="n">
-        <v>79536</v>
+        <v>79565</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6503,37 +6503,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444531</v>
+        <v>445081</v>
       </c>
       <c r="R58" t="n">
-        <v>6846461</v>
+        <v>6846466</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6577,19 +6577,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125039726</v>
+        <v>125046602</v>
       </c>
       <c r="B59" t="n">
         <v>79565</v>
@@ -6625,17 +6625,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445081</v>
+        <v>444748</v>
       </c>
       <c r="R59" t="n">
-        <v>6846466</v>
+        <v>6846223</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6679,22 +6679,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125034167</v>
+        <v>125046607</v>
       </c>
       <c r="B60" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6707,37 +6707,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444830</v>
+        <v>445086</v>
       </c>
       <c r="R60" t="n">
-        <v>6846275</v>
+        <v>6846378</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6781,19 +6781,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125047039</v>
+        <v>125034167</v>
       </c>
       <c r="B61" t="n">
         <v>78947</v>
@@ -6829,17 +6829,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444637</v>
+        <v>444830</v>
       </c>
       <c r="R61" t="n">
-        <v>6846186</v>
+        <v>6846275</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6883,19 +6883,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125046957</v>
+        <v>125047039</v>
       </c>
       <c r="B62" t="n">
         <v>78947</v>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444839</v>
+        <v>444637</v>
       </c>
       <c r="R62" t="n">
-        <v>6846390</v>
+        <v>6846186</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6997,7 +6997,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125046992</v>
+        <v>125046957</v>
       </c>
       <c r="B63" t="n">
         <v>78947</v>
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444523</v>
+        <v>444839</v>
       </c>
       <c r="R63" t="n">
-        <v>6846404</v>
+        <v>6846390</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7099,7 +7099,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125047022</v>
+        <v>125046992</v>
       </c>
       <c r="B64" t="n">
         <v>78947</v>
@@ -7139,10 +7139,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444485</v>
+        <v>444523</v>
       </c>
       <c r="R64" t="n">
-        <v>6846146</v>
+        <v>6846404</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7201,10 +7201,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125046602</v>
+        <v>125047022</v>
       </c>
       <c r="B65" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7217,21 +7217,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444748</v>
+        <v>444485</v>
       </c>
       <c r="R65" t="n">
-        <v>6846223</v>
+        <v>6846146</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125046607</v>
+        <v>125046709</v>
       </c>
       <c r="B66" t="n">
-        <v>79565</v>
+        <v>79536</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7319,21 +7319,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445086</v>
+        <v>444531</v>
       </c>
       <c r="R66" t="n">
-        <v>6846378</v>
+        <v>6846461</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125046680</v>
+        <v>125046672</v>
       </c>
       <c r="B68" t="n">
         <v>78979</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444854</v>
+        <v>444514</v>
       </c>
       <c r="R68" t="n">
-        <v>6846304</v>
+        <v>6846296</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7609,10 +7609,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125046959</v>
+        <v>125033738</v>
       </c>
       <c r="B69" t="n">
-        <v>78947</v>
+        <v>79026</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7625,37 +7625,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444778</v>
+        <v>445053</v>
       </c>
       <c r="R69" t="n">
-        <v>6846468</v>
+        <v>6846325</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7699,19 +7699,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125046987</v>
+        <v>125047037</v>
       </c>
       <c r="B70" t="n">
         <v>78947</v>
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444532</v>
+        <v>444636</v>
       </c>
       <c r="R70" t="n">
-        <v>6846448</v>
+        <v>6846147</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7813,7 +7813,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125037581</v>
+        <v>125038496</v>
       </c>
       <c r="B71" t="n">
         <v>78947</v>
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444606</v>
+        <v>444774</v>
       </c>
       <c r="R71" t="n">
-        <v>6846358</v>
+        <v>6846574</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125047011</v>
+        <v>125047059</v>
       </c>
       <c r="B72" t="n">
         <v>78947</v>
@@ -7955,10 +7955,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444500</v>
+        <v>444841</v>
       </c>
       <c r="R72" t="n">
-        <v>6846235</v>
+        <v>6846295</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,10 +8017,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125046785</v>
+        <v>125046593</v>
       </c>
       <c r="B73" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8033,21 +8033,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445050</v>
+        <v>444840</v>
       </c>
       <c r="R73" t="n">
-        <v>6846540</v>
+        <v>6846397</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8119,10 +8119,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125034812</v>
+        <v>125046680</v>
       </c>
       <c r="B74" t="n">
-        <v>79536</v>
+        <v>78979</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8135,37 +8135,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444712</v>
+        <v>444854</v>
       </c>
       <c r="R74" t="n">
-        <v>6846142</v>
+        <v>6846304</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8209,22 +8209,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125046672</v>
+        <v>125046959</v>
       </c>
       <c r="B75" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8237,21 +8237,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444514</v>
+        <v>444778</v>
       </c>
       <c r="R75" t="n">
-        <v>6846296</v>
+        <v>6846468</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8323,10 +8323,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125033738</v>
+        <v>125046987</v>
       </c>
       <c r="B76" t="n">
-        <v>79026</v>
+        <v>78947</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8339,37 +8339,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445053</v>
+        <v>444532</v>
       </c>
       <c r="R76" t="n">
-        <v>6846325</v>
+        <v>6846448</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8413,19 +8413,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125038496</v>
+        <v>125037581</v>
       </c>
       <c r="B77" t="n">
         <v>78947</v>
@@ -8465,13 +8465,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444774</v>
+        <v>444606</v>
       </c>
       <c r="R77" t="n">
-        <v>6846574</v>
+        <v>6846358</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125047037</v>
+        <v>125047011</v>
       </c>
       <c r="B78" t="n">
         <v>78947</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444636</v>
+        <v>444500</v>
       </c>
       <c r="R78" t="n">
-        <v>6846147</v>
+        <v>6846235</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125047059</v>
+        <v>125046785</v>
       </c>
       <c r="B79" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8645,21 +8645,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444841</v>
+        <v>445050</v>
       </c>
       <c r="R79" t="n">
-        <v>6846295</v>
+        <v>6846540</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125046593</v>
+        <v>125034812</v>
       </c>
       <c r="B80" t="n">
-        <v>79565</v>
+        <v>79536</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8747,37 +8747,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444840</v>
+        <v>444712</v>
       </c>
       <c r="R80" t="n">
-        <v>6846397</v>
+        <v>6846142</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8821,12 +8821,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -11198,10 +11198,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125046804</v>
+        <v>125037692</v>
       </c>
       <c r="B104" t="n">
-        <v>78683</v>
+        <v>78331</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11214,37 +11214,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444616</v>
+        <v>444696</v>
       </c>
       <c r="R104" t="n">
-        <v>6846465</v>
+        <v>6846398</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125034871</v>
+        <v>125046804</v>
       </c>
       <c r="B105" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11316,37 +11316,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444678</v>
+        <v>444616</v>
       </c>
       <c r="R105" t="n">
-        <v>6846146</v>
+        <v>6846465</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11390,22 +11390,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125046744</v>
+        <v>125034871</v>
       </c>
       <c r="B106" t="n">
-        <v>91186</v>
+        <v>78947</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11418,37 +11418,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445022</v>
+        <v>444678</v>
       </c>
       <c r="R106" t="n">
-        <v>6846541</v>
+        <v>6846146</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11492,22 +11492,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125037692</v>
+        <v>125046744</v>
       </c>
       <c r="B107" t="n">
-        <v>78331</v>
+        <v>91186</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11520,37 +11520,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6437</v>
+        <v>5442</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444696</v>
+        <v>445022</v>
       </c>
       <c r="R107" t="n">
-        <v>6846398</v>
+        <v>6846541</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11594,12 +11594,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -28483,7 +28483,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>125042600</v>
+        <v>125046636</v>
       </c>
       <c r="B273" t="n">
         <v>78979</v>
@@ -28519,17 +28519,17 @@
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>445618</v>
+        <v>445630</v>
       </c>
       <c r="R273" t="n">
-        <v>6846407</v>
+        <v>6846498</v>
       </c>
       <c r="S273" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -28573,22 +28573,22 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>125046813</v>
+        <v>125046668</v>
       </c>
       <c r="B274" t="n">
-        <v>91184</v>
+        <v>78979</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28601,21 +28601,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28625,10 +28625,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>445597</v>
+        <v>445340</v>
       </c>
       <c r="R274" t="n">
-        <v>6846492</v>
+        <v>6846449</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -29406,10 +29406,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>125047106</v>
+        <v>125042845</v>
       </c>
       <c r="B282" t="n">
-        <v>78947</v>
+        <v>88512</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29422,37 +29422,37 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>445294</v>
+        <v>445688</v>
       </c>
       <c r="R282" t="n">
-        <v>6846511</v>
+        <v>6846464</v>
       </c>
       <c r="S282" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -29496,22 +29496,22 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>125042845</v>
+        <v>125047106</v>
       </c>
       <c r="B283" t="n">
-        <v>88512</v>
+        <v>78947</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29524,37 +29524,37 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>445688</v>
+        <v>445294</v>
       </c>
       <c r="R283" t="n">
-        <v>6846464</v>
+        <v>6846511</v>
       </c>
       <c r="S283" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -29598,19 +29598,19 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>125046636</v>
+        <v>125042600</v>
       </c>
       <c r="B284" t="n">
         <v>78979</v>
@@ -29646,17 +29646,17 @@
       <c r="I284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>445630</v>
+        <v>445618</v>
       </c>
       <c r="R284" t="n">
-        <v>6846498</v>
+        <v>6846407</v>
       </c>
       <c r="S284" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -29700,22 +29700,22 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>125046668</v>
+        <v>125046813</v>
       </c>
       <c r="B285" t="n">
-        <v>78979</v>
+        <v>91184</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29728,21 +29728,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29752,10 +29752,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>445340</v>
+        <v>445597</v>
       </c>
       <c r="R285" t="n">
-        <v>6846449</v>
+        <v>6846492</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29814,10 +29814,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>125046704</v>
+        <v>125047152</v>
       </c>
       <c r="B286" t="n">
-        <v>79536</v>
+        <v>57635</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -29830,34 +29830,39 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P286" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>445482</v>
+        <v>445630</v>
       </c>
       <c r="R286" t="n">
-        <v>6846539</v>
+        <v>6846272</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -30324,10 +30329,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>125042520</v>
+        <v>125046908</v>
       </c>
       <c r="B291" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -30340,37 +30345,37 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>445599</v>
+        <v>445514</v>
       </c>
       <c r="R291" t="n">
-        <v>6846427</v>
+        <v>6846439</v>
       </c>
       <c r="S291" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -30414,22 +30419,22 @@
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>125046614</v>
+        <v>125042795</v>
       </c>
       <c r="B292" t="n">
-        <v>78979</v>
+        <v>91131</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30438,41 +30443,41 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>445418</v>
+        <v>445688</v>
       </c>
       <c r="R292" t="n">
-        <v>6846058</v>
+        <v>6846464</v>
       </c>
       <c r="S292" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -30516,22 +30521,22 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>125042795</v>
+        <v>125046809</v>
       </c>
       <c r="B293" t="n">
-        <v>91131</v>
+        <v>91184</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -30540,41 +30545,41 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>445688</v>
+        <v>445644</v>
       </c>
       <c r="R293" t="n">
-        <v>6846464</v>
+        <v>6846260</v>
       </c>
       <c r="S293" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -30618,22 +30623,22 @@
       <c r="AT293" t="inlineStr"/>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>125046809</v>
+        <v>125046843</v>
       </c>
       <c r="B294" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30646,21 +30651,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -30670,10 +30675,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>445644</v>
+        <v>445436</v>
       </c>
       <c r="R294" t="n">
-        <v>6846260</v>
+        <v>6846091</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30732,7 +30737,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>125046843</v>
+        <v>125046861</v>
       </c>
       <c r="B295" t="n">
         <v>78947</v>
@@ -30772,10 +30777,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>445436</v>
+        <v>445730</v>
       </c>
       <c r="R295" t="n">
-        <v>6846091</v>
+        <v>6846366</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30834,7 +30839,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>125046861</v>
+        <v>125046845</v>
       </c>
       <c r="B296" t="n">
         <v>78947</v>
@@ -30874,10 +30879,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>445730</v>
+        <v>445477</v>
       </c>
       <c r="R296" t="n">
-        <v>6846366</v>
+        <v>6846122</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30936,7 +30941,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>125046845</v>
+        <v>125047133</v>
       </c>
       <c r="B297" t="n">
         <v>78947</v>
@@ -30976,10 +30981,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>445477</v>
+        <v>445672</v>
       </c>
       <c r="R297" t="n">
-        <v>6846122</v>
+        <v>6846269</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -31038,7 +31043,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>125047133</v>
+        <v>125046916</v>
       </c>
       <c r="B298" t="n">
         <v>78947</v>
@@ -31078,10 +31083,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>445672</v>
+        <v>445474</v>
       </c>
       <c r="R298" t="n">
-        <v>6846269</v>
+        <v>6846496</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -31140,10 +31145,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>125046916</v>
+        <v>125042520</v>
       </c>
       <c r="B299" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -31156,37 +31161,37 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>445474</v>
+        <v>445599</v>
       </c>
       <c r="R299" t="n">
-        <v>6846496</v>
+        <v>6846427</v>
       </c>
       <c r="S299" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -31230,22 +31235,22 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>125047152</v>
+        <v>125046614</v>
       </c>
       <c r="B300" t="n">
-        <v>57635</v>
+        <v>78979</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -31258,39 +31263,34 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P300" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>445630</v>
+        <v>445418</v>
       </c>
       <c r="R300" t="n">
-        <v>6846272</v>
+        <v>6846058</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -31349,10 +31349,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>125041091</v>
+        <v>125046766</v>
       </c>
       <c r="B301" t="n">
-        <v>56836</v>
+        <v>97147</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -31365,37 +31365,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>445462</v>
+        <v>445478</v>
       </c>
       <c r="R301" t="n">
-        <v>6846286</v>
+        <v>6846122</v>
       </c>
       <c r="S301" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -31425,11 +31425,6 @@
       <c r="AA301" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall.</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -31444,22 +31439,22 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>125046766</v>
+        <v>125046784</v>
       </c>
       <c r="B302" t="n">
-        <v>97147</v>
+        <v>78684</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -31468,25 +31463,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -31496,10 +31491,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>445478</v>
+        <v>445501</v>
       </c>
       <c r="R302" t="n">
-        <v>6846122</v>
+        <v>6846560</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -31558,10 +31553,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>125046908</v>
+        <v>125046704</v>
       </c>
       <c r="B303" t="n">
-        <v>78947</v>
+        <v>79536</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -31574,21 +31569,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -31598,10 +31593,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>445514</v>
+        <v>445482</v>
       </c>
       <c r="R303" t="n">
-        <v>6846439</v>
+        <v>6846539</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -31660,10 +31655,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>125046784</v>
+        <v>125041091</v>
       </c>
       <c r="B304" t="n">
-        <v>78684</v>
+        <v>56836</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -31672,41 +31667,41 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>445501</v>
+        <v>445462</v>
       </c>
       <c r="R304" t="n">
-        <v>6846560</v>
+        <v>6846286</v>
       </c>
       <c r="S304" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -31736,6 +31731,11 @@
       <c r="AA304" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall.</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -31750,19 +31750,19 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>125046651</v>
+        <v>125046623</v>
       </c>
       <c r="B305" t="n">
         <v>78979</v>
@@ -31802,10 +31802,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>445539</v>
+        <v>445684</v>
       </c>
       <c r="R305" t="n">
-        <v>6846375</v>
+        <v>6846335</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -31864,10 +31864,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>125046811</v>
+        <v>125046659</v>
       </c>
       <c r="B306" t="n">
-        <v>91184</v>
+        <v>78979</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -31880,21 +31880,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -31904,10 +31904,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>445791</v>
+        <v>445463</v>
       </c>
       <c r="R306" t="n">
-        <v>6846476</v>
+        <v>6846495</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -31966,10 +31966,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>125046885</v>
+        <v>125046663</v>
       </c>
       <c r="B307" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -31982,21 +31982,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -32006,10 +32006,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>445732</v>
+        <v>445512</v>
       </c>
       <c r="R307" t="n">
-        <v>6846592</v>
+        <v>6846523</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -32068,10 +32068,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>125046898</v>
+        <v>125042160</v>
       </c>
       <c r="B308" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -32084,37 +32084,37 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>445556</v>
+        <v>445543</v>
       </c>
       <c r="R308" t="n">
-        <v>6846502</v>
+        <v>6846425</v>
       </c>
       <c r="S308" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -32158,19 +32158,19 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>125046930</v>
+        <v>125047099</v>
       </c>
       <c r="B309" t="n">
         <v>78947</v>
@@ -32210,10 +32210,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>445392</v>
+        <v>445199</v>
       </c>
       <c r="R309" t="n">
-        <v>6846479</v>
+        <v>6846494</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -32272,7 +32272,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>125046878</v>
+        <v>125039902</v>
       </c>
       <c r="B310" t="n">
         <v>78947</v>
@@ -32308,17 +32308,17 @@
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>445773</v>
+        <v>445109</v>
       </c>
       <c r="R310" t="n">
-        <v>6846542</v>
+        <v>6846460</v>
       </c>
       <c r="S310" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -32362,22 +32362,22 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>125042370</v>
+        <v>125046651</v>
       </c>
       <c r="B311" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -32390,37 +32390,37 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>445558</v>
+        <v>445539</v>
       </c>
       <c r="R311" t="n">
-        <v>6846476</v>
+        <v>6846375</v>
       </c>
       <c r="S311" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -32464,22 +32464,22 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>125033498</v>
+        <v>125046811</v>
       </c>
       <c r="B312" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -32492,34 +32492,34 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>445171</v>
+        <v>445791</v>
       </c>
       <c r="R312" t="n">
-        <v>6846401</v>
+        <v>6846476</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -32566,19 +32566,19 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>125047121</v>
+        <v>125046885</v>
       </c>
       <c r="B313" t="n">
         <v>78947</v>
@@ -32618,10 +32618,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>445426</v>
+        <v>445732</v>
       </c>
       <c r="R313" t="n">
-        <v>6846303</v>
+        <v>6846592</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -32680,10 +32680,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>125046741</v>
+        <v>125046898</v>
       </c>
       <c r="B314" t="n">
-        <v>57793</v>
+        <v>78947</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -32696,21 +32696,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -32720,10 +32720,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>445465</v>
+        <v>445556</v>
       </c>
       <c r="R314" t="n">
-        <v>6846123</v>
+        <v>6846502</v>
       </c>
       <c r="S314" t="n">
         <v>10</v>
@@ -32782,10 +32782,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>125046623</v>
+        <v>125046930</v>
       </c>
       <c r="B315" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -32798,21 +32798,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -32822,10 +32822,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>445684</v>
+        <v>445392</v>
       </c>
       <c r="R315" t="n">
-        <v>6846335</v>
+        <v>6846479</v>
       </c>
       <c r="S315" t="n">
         <v>10</v>
@@ -32884,10 +32884,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>125046659</v>
+        <v>125046878</v>
       </c>
       <c r="B316" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -32900,21 +32900,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -32924,10 +32924,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>445463</v>
+        <v>445773</v>
       </c>
       <c r="R316" t="n">
-        <v>6846495</v>
+        <v>6846542</v>
       </c>
       <c r="S316" t="n">
         <v>10</v>
@@ -32986,10 +32986,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>125046663</v>
+        <v>125042370</v>
       </c>
       <c r="B317" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -33002,37 +33002,37 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>445512</v>
+        <v>445558</v>
       </c>
       <c r="R317" t="n">
-        <v>6846523</v>
+        <v>6846476</v>
       </c>
       <c r="S317" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -33076,22 +33076,22 @@
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>125042160</v>
+        <v>125033498</v>
       </c>
       <c r="B318" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -33104,37 +33104,37 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>445543</v>
+        <v>445171</v>
       </c>
       <c r="R318" t="n">
-        <v>6846425</v>
+        <v>6846401</v>
       </c>
       <c r="S318" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>125047099</v>
+        <v>125047121</v>
       </c>
       <c r="B319" t="n">
         <v>78947</v>
@@ -33230,10 +33230,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>445199</v>
+        <v>445426</v>
       </c>
       <c r="R319" t="n">
-        <v>6846494</v>
+        <v>6846303</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -33292,10 +33292,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>125039902</v>
+        <v>125046741</v>
       </c>
       <c r="B320" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -33308,37 +33308,37 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>445109</v>
+        <v>445465</v>
       </c>
       <c r="R320" t="n">
-        <v>6846460</v>
+        <v>6846123</v>
       </c>
       <c r="S320" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -33382,12 +33382,12 @@
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
@@ -36046,10 +36046,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125046722</v>
+        <v>125033708</v>
       </c>
       <c r="B347" t="n">
-        <v>79536</v>
+        <v>79042</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -36062,37 +36062,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>445331</v>
+        <v>445144</v>
       </c>
       <c r="R347" t="n">
-        <v>6846511</v>
+        <v>6846374</v>
       </c>
       <c r="S347" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -36136,22 +36136,22 @@
       <c r="AT347" t="inlineStr"/>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125046699</v>
+        <v>125043041</v>
       </c>
       <c r="B348" t="n">
-        <v>91131</v>
+        <v>91338</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -36160,41 +36160,41 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>5447</v>
+        <v>1588</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>445461</v>
+        <v>445711</v>
       </c>
       <c r="R348" t="n">
-        <v>6846541</v>
+        <v>6846458</v>
       </c>
       <c r="S348" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -36238,22 +36238,22 @@
       <c r="AT348" t="inlineStr"/>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>125047176</v>
+        <v>125046635</v>
       </c>
       <c r="B349" t="n">
-        <v>57635</v>
+        <v>78979</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -36266,39 +36266,34 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P349" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>445645</v>
+        <v>445624</v>
       </c>
       <c r="R349" t="n">
-        <v>6846261</v>
+        <v>6846513</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -36357,10 +36352,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>125033708</v>
+        <v>125046699</v>
       </c>
       <c r="B350" t="n">
-        <v>79042</v>
+        <v>91131</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -36369,41 +36364,41 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>967</v>
+        <v>5447</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>445144</v>
+        <v>445461</v>
       </c>
       <c r="R350" t="n">
-        <v>6846374</v>
+        <v>6846541</v>
       </c>
       <c r="S350" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -36447,22 +36442,22 @@
       <c r="AT350" t="inlineStr"/>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>125043041</v>
+        <v>125046722</v>
       </c>
       <c r="B351" t="n">
-        <v>91338</v>
+        <v>79536</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -36475,37 +36470,37 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1588</v>
+        <v>229821</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>445711</v>
+        <v>445331</v>
       </c>
       <c r="R351" t="n">
-        <v>6846458</v>
+        <v>6846511</v>
       </c>
       <c r="S351" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -36549,22 +36544,22 @@
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125046635</v>
+        <v>125047089</v>
       </c>
       <c r="B352" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -36577,21 +36572,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
@@ -36601,10 +36596,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>445624</v>
+        <v>445130</v>
       </c>
       <c r="R352" t="n">
-        <v>6846513</v>
+        <v>6846433</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -36663,7 +36658,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125047089</v>
+        <v>125046886</v>
       </c>
       <c r="B353" t="n">
         <v>78947</v>
@@ -36703,10 +36698,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>445130</v>
+        <v>445710</v>
       </c>
       <c r="R353" t="n">
-        <v>6846433</v>
+        <v>6846565</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -36765,7 +36760,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125046886</v>
+        <v>125046889</v>
       </c>
       <c r="B354" t="n">
         <v>78947</v>
@@ -36805,10 +36800,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>445710</v>
+        <v>445693</v>
       </c>
       <c r="R354" t="n">
-        <v>6846565</v>
+        <v>6846539</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -36867,7 +36862,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125046889</v>
+        <v>125046882</v>
       </c>
       <c r="B355" t="n">
         <v>78947</v>
@@ -36907,10 +36902,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>445693</v>
+        <v>445747</v>
       </c>
       <c r="R355" t="n">
-        <v>6846539</v>
+        <v>6846595</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -36969,7 +36964,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125046882</v>
+        <v>125046926</v>
       </c>
       <c r="B356" t="n">
         <v>78947</v>
@@ -37009,10 +37004,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>445747</v>
+        <v>445458</v>
       </c>
       <c r="R356" t="n">
-        <v>6846595</v>
+        <v>6846537</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -37071,7 +37066,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>125046926</v>
+        <v>125046856</v>
       </c>
       <c r="B357" t="n">
         <v>78947</v>
@@ -37111,10 +37106,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>445458</v>
+        <v>445684</v>
       </c>
       <c r="R357" t="n">
-        <v>6846537</v>
+        <v>6846335</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -37173,7 +37168,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>125046856</v>
+        <v>125047096</v>
       </c>
       <c r="B358" t="n">
         <v>78947</v>
@@ -37213,10 +37208,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>445684</v>
+        <v>445181</v>
       </c>
       <c r="R358" t="n">
-        <v>6846335</v>
+        <v>6846450</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -37275,7 +37270,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125047096</v>
+        <v>125046872</v>
       </c>
       <c r="B359" t="n">
         <v>78947</v>
@@ -37315,10 +37310,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>445181</v>
+        <v>445792</v>
       </c>
       <c r="R359" t="n">
-        <v>6846450</v>
+        <v>6846472</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -37377,10 +37372,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125046872</v>
+        <v>125047176</v>
       </c>
       <c r="B360" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -37393,34 +37388,39 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P360" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>445792</v>
+        <v>445645</v>
       </c>
       <c r="R360" t="n">
-        <v>6846472</v>
+        <v>6846261</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>

--- a/artfynd/A 18557-2025 artfynd.xlsx
+++ b/artfynd/A 18557-2025 artfynd.xlsx
@@ -3422,7 +3422,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125035654</v>
+        <v>125035937</v>
       </c>
       <c r="B28" t="n">
         <v>78947</v>
@@ -3458,14 +3458,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444640</v>
+        <v>444514</v>
       </c>
       <c r="R28" t="n">
-        <v>6846141</v>
+        <v>6846145</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125047002</v>
+        <v>125034086</v>
       </c>
       <c r="B29" t="n">
         <v>78947</v>
@@ -3560,17 +3560,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444513</v>
+        <v>444847</v>
       </c>
       <c r="R29" t="n">
-        <v>6846284</v>
+        <v>6846241</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,19 +3614,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125047026</v>
+        <v>125046977</v>
       </c>
       <c r="B30" t="n">
         <v>78947</v>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444519</v>
+        <v>444540</v>
       </c>
       <c r="R30" t="n">
-        <v>6846154</v>
+        <v>6846553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125035937</v>
+        <v>125047062</v>
       </c>
       <c r="B31" t="n">
         <v>78947</v>
@@ -3764,17 +3764,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444514</v>
+        <v>444855</v>
       </c>
       <c r="R31" t="n">
-        <v>6846145</v>
+        <v>6846310</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3818,19 +3818,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125034086</v>
+        <v>125035654</v>
       </c>
       <c r="B32" t="n">
         <v>78947</v>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444847</v>
+        <v>444640</v>
       </c>
       <c r="R32" t="n">
-        <v>6846241</v>
+        <v>6846141</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125046977</v>
+        <v>125047002</v>
       </c>
       <c r="B33" t="n">
         <v>78947</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444540</v>
+        <v>444513</v>
       </c>
       <c r="R33" t="n">
-        <v>6846553</v>
+        <v>6846284</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125047062</v>
+        <v>125047026</v>
       </c>
       <c r="B34" t="n">
         <v>78947</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444855</v>
+        <v>444519</v>
       </c>
       <c r="R34" t="n">
-        <v>6846310</v>
+        <v>6846154</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -8833,10 +8833,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125046716</v>
+        <v>125047009</v>
       </c>
       <c r="B81" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444784</v>
+        <v>444501</v>
       </c>
       <c r="R81" t="n">
-        <v>6846153</v>
+        <v>6846240</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125046708</v>
+        <v>125047052</v>
       </c>
       <c r="B82" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8951,21 +8951,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444671</v>
+        <v>444778</v>
       </c>
       <c r="R82" t="n">
-        <v>6846500</v>
+        <v>6846129</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9037,10 +9037,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125046581</v>
+        <v>125047012</v>
       </c>
       <c r="B83" t="n">
-        <v>5196</v>
+        <v>78947</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9049,43 +9049,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444829</v>
+        <v>444491</v>
       </c>
       <c r="R83" t="n">
-        <v>6846284</v>
+        <v>6846224</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9144,7 +9139,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125047009</v>
+        <v>125046981</v>
       </c>
       <c r="B84" t="n">
         <v>78947</v>
@@ -9184,10 +9179,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444501</v>
+        <v>444537</v>
       </c>
       <c r="R84" t="n">
-        <v>6846240</v>
+        <v>6846522</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9246,10 +9241,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125047052</v>
+        <v>125046581</v>
       </c>
       <c r="B85" t="n">
-        <v>78947</v>
+        <v>5196</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9258,38 +9253,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444778</v>
+        <v>444829</v>
       </c>
       <c r="R85" t="n">
-        <v>6846129</v>
+        <v>6846284</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9348,10 +9348,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125047012</v>
+        <v>125046716</v>
       </c>
       <c r="B86" t="n">
-        <v>78947</v>
+        <v>79536</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444491</v>
+        <v>444784</v>
       </c>
       <c r="R86" t="n">
-        <v>6846224</v>
+        <v>6846153</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125046981</v>
+        <v>125046708</v>
       </c>
       <c r="B87" t="n">
-        <v>78947</v>
+        <v>79536</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9466,21 +9466,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444537</v>
+        <v>444671</v>
       </c>
       <c r="R87" t="n">
-        <v>6846522</v>
+        <v>6846500</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125047159</v>
+        <v>125047014</v>
       </c>
       <c r="B88" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9568,39 +9568,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444551</v>
+        <v>444494</v>
       </c>
       <c r="R88" t="n">
-        <v>6846127</v>
+        <v>6846208</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9659,10 +9654,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125046737</v>
+        <v>125046990</v>
       </c>
       <c r="B89" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9671,43 +9666,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444759</v>
+        <v>444512</v>
       </c>
       <c r="R89" t="n">
-        <v>6846476</v>
+        <v>6846426</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9766,10 +9756,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125046736</v>
+        <v>125046954</v>
       </c>
       <c r="B90" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9778,42 +9768,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444593</v>
+        <v>444910</v>
       </c>
       <c r="R90" t="n">
-        <v>6846129</v>
+        <v>6846390</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9872,10 +9858,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125046800</v>
+        <v>125046993</v>
       </c>
       <c r="B91" t="n">
-        <v>79026</v>
+        <v>78947</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9888,21 +9874,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9912,10 +9898,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444499</v>
+        <v>444504</v>
       </c>
       <c r="R91" t="n">
-        <v>6846245</v>
+        <v>6846395</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9974,10 +9960,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125046802</v>
+        <v>125047043</v>
       </c>
       <c r="B92" t="n">
-        <v>79026</v>
+        <v>78947</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9990,21 +9976,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10014,10 +10000,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444487</v>
+        <v>444684</v>
       </c>
       <c r="R92" t="n">
-        <v>6846177</v>
+        <v>6846221</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10076,10 +10062,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125046762</v>
+        <v>125047159</v>
       </c>
       <c r="B93" t="n">
-        <v>79033</v>
+        <v>57635</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10088,38 +10074,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444529</v>
+        <v>444551</v>
       </c>
       <c r="R93" t="n">
-        <v>6846448</v>
+        <v>6846127</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10178,10 +10169,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125038887</v>
+        <v>125046737</v>
       </c>
       <c r="B94" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10190,38 +10181,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444847</v>
+        <v>444759</v>
       </c>
       <c r="R94" t="n">
-        <v>6846563</v>
+        <v>6846476</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10268,22 +10264,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125046958</v>
+        <v>125046736</v>
       </c>
       <c r="B95" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10292,38 +10288,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444818</v>
+        <v>444593</v>
       </c>
       <c r="R95" t="n">
-        <v>6846440</v>
+        <v>6846129</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10382,10 +10382,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125047170</v>
+        <v>125046671</v>
       </c>
       <c r="B96" t="n">
-        <v>78331</v>
+        <v>78979</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10398,21 +10398,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444963</v>
+        <v>444533</v>
       </c>
       <c r="R96" t="n">
-        <v>6846302</v>
+        <v>6846410</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10484,10 +10484,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125046677</v>
+        <v>125046800</v>
       </c>
       <c r="B97" t="n">
-        <v>78979</v>
+        <v>79026</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10500,21 +10500,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444494</v>
+        <v>444499</v>
       </c>
       <c r="R97" t="n">
-        <v>6846208</v>
+        <v>6846245</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10586,10 +10586,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125046671</v>
+        <v>125046802</v>
       </c>
       <c r="B98" t="n">
-        <v>78979</v>
+        <v>79026</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10602,21 +10602,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444533</v>
+        <v>444487</v>
       </c>
       <c r="R98" t="n">
-        <v>6846410</v>
+        <v>6846177</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10688,10 +10688,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125047014</v>
+        <v>125046762</v>
       </c>
       <c r="B99" t="n">
-        <v>78947</v>
+        <v>79033</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10700,25 +10700,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444494</v>
+        <v>444529</v>
       </c>
       <c r="R99" t="n">
-        <v>6846208</v>
+        <v>6846448</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125046990</v>
+        <v>125038887</v>
       </c>
       <c r="B100" t="n">
         <v>78947</v>
@@ -10826,14 +10826,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444512</v>
+        <v>444847</v>
       </c>
       <c r="R100" t="n">
-        <v>6846426</v>
+        <v>6846563</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10880,19 +10880,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125046954</v>
+        <v>125046958</v>
       </c>
       <c r="B101" t="n">
         <v>78947</v>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444910</v>
+        <v>444818</v>
       </c>
       <c r="R101" t="n">
-        <v>6846390</v>
+        <v>6846440</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10994,10 +10994,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125046993</v>
+        <v>125047170</v>
       </c>
       <c r="B102" t="n">
-        <v>78947</v>
+        <v>78331</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11010,21 +11010,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11034,10 +11034,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444504</v>
+        <v>444963</v>
       </c>
       <c r="R102" t="n">
-        <v>6846395</v>
+        <v>6846302</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11096,10 +11096,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125047043</v>
+        <v>125046677</v>
       </c>
       <c r="B103" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11112,21 +11112,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11136,10 +11136,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444684</v>
+        <v>444494</v>
       </c>
       <c r="R103" t="n">
-        <v>6846221</v>
+        <v>6846208</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11198,10 +11198,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125037692</v>
+        <v>125046804</v>
       </c>
       <c r="B104" t="n">
-        <v>78331</v>
+        <v>78683</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11214,37 +11214,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444696</v>
+        <v>444616</v>
       </c>
       <c r="R104" t="n">
-        <v>6846398</v>
+        <v>6846465</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125046804</v>
+        <v>125034871</v>
       </c>
       <c r="B105" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11316,37 +11316,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444616</v>
+        <v>444678</v>
       </c>
       <c r="R105" t="n">
-        <v>6846465</v>
+        <v>6846146</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11390,22 +11390,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125034871</v>
+        <v>125046744</v>
       </c>
       <c r="B106" t="n">
-        <v>78947</v>
+        <v>91186</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11418,37 +11418,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444678</v>
+        <v>445022</v>
       </c>
       <c r="R106" t="n">
-        <v>6846146</v>
+        <v>6846541</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11492,22 +11492,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125046744</v>
+        <v>125037692</v>
       </c>
       <c r="B107" t="n">
-        <v>91186</v>
+        <v>78331</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11520,37 +11520,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5442</v>
+        <v>6437</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445022</v>
+        <v>444696</v>
       </c>
       <c r="R107" t="n">
-        <v>6846541</v>
+        <v>6846398</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11594,12 +11594,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13340,7 +13340,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125036045</v>
+        <v>125047064</v>
       </c>
       <c r="B125" t="n">
         <v>78947</v>
@@ -13376,17 +13376,17 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444513</v>
+        <v>444890</v>
       </c>
       <c r="R125" t="n">
-        <v>6846156</v>
+        <v>6846336</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13430,19 +13430,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125047025</v>
+        <v>125034509</v>
       </c>
       <c r="B126" t="n">
         <v>78947</v>
@@ -13478,17 +13478,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>444502</v>
+        <v>444763</v>
       </c>
       <c r="R126" t="n">
-        <v>6846158</v>
+        <v>6846122</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13532,19 +13532,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125047061</v>
+        <v>125047034</v>
       </c>
       <c r="B127" t="n">
         <v>78947</v>
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444853</v>
+        <v>444612</v>
       </c>
       <c r="R127" t="n">
-        <v>6846304</v>
+        <v>6846142</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13646,10 +13646,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125046604</v>
+        <v>125046997</v>
       </c>
       <c r="B128" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13662,21 +13662,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13686,10 +13686,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444838</v>
+        <v>444540</v>
       </c>
       <c r="R128" t="n">
-        <v>6846288</v>
+        <v>6846347</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13748,7 +13748,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125038198</v>
+        <v>125046998</v>
       </c>
       <c r="B129" t="n">
         <v>78947</v>
@@ -13784,17 +13784,17 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>444753</v>
+        <v>444547</v>
       </c>
       <c r="R129" t="n">
-        <v>6846467</v>
+        <v>6846345</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13838,19 +13838,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125037824</v>
+        <v>125047045</v>
       </c>
       <c r="B130" t="n">
         <v>78947</v>
@@ -13886,17 +13886,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>444709</v>
+        <v>444698</v>
       </c>
       <c r="R130" t="n">
-        <v>6846425</v>
+        <v>6846210</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13940,22 +13940,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125046674</v>
+        <v>125035599</v>
       </c>
       <c r="B131" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13968,37 +13968,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>444501</v>
+        <v>444609</v>
       </c>
       <c r="R131" t="n">
-        <v>6846240</v>
+        <v>6846136</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14042,19 +14042,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125047064</v>
+        <v>125036045</v>
       </c>
       <c r="B132" t="n">
         <v>78947</v>
@@ -14090,17 +14090,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>444890</v>
+        <v>444513</v>
       </c>
       <c r="R132" t="n">
-        <v>6846336</v>
+        <v>6846156</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14144,19 +14144,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125034509</v>
+        <v>125047025</v>
       </c>
       <c r="B133" t="n">
         <v>78947</v>
@@ -14192,17 +14192,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>444763</v>
+        <v>444502</v>
       </c>
       <c r="R133" t="n">
-        <v>6846122</v>
+        <v>6846158</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14246,19 +14246,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125047034</v>
+        <v>125047061</v>
       </c>
       <c r="B134" t="n">
         <v>78947</v>
@@ -14298,10 +14298,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>444612</v>
+        <v>444853</v>
       </c>
       <c r="R134" t="n">
-        <v>6846142</v>
+        <v>6846304</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14360,10 +14360,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125046997</v>
+        <v>125046604</v>
       </c>
       <c r="B135" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14376,21 +14376,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>444540</v>
+        <v>444838</v>
       </c>
       <c r="R135" t="n">
-        <v>6846347</v>
+        <v>6846288</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14462,7 +14462,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125046998</v>
+        <v>125038198</v>
       </c>
       <c r="B136" t="n">
         <v>78947</v>
@@ -14498,17 +14498,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>444547</v>
+        <v>444753</v>
       </c>
       <c r="R136" t="n">
-        <v>6846345</v>
+        <v>6846467</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14552,19 +14552,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125047045</v>
+        <v>125037824</v>
       </c>
       <c r="B137" t="n">
         <v>78947</v>
@@ -14600,17 +14600,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444698</v>
+        <v>444709</v>
       </c>
       <c r="R137" t="n">
-        <v>6846210</v>
+        <v>6846425</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14654,22 +14654,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125035599</v>
+        <v>125046674</v>
       </c>
       <c r="B138" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14682,37 +14682,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444609</v>
+        <v>444501</v>
       </c>
       <c r="R138" t="n">
-        <v>6846136</v>
+        <v>6846240</v>
       </c>
       <c r="S138" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14756,12 +14756,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -18965,10 +18965,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>125046730</v>
+        <v>125046712</v>
       </c>
       <c r="B180" t="n">
-        <v>79042</v>
+        <v>79536</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18981,21 +18981,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19005,10 +19005,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445092</v>
+        <v>444508</v>
       </c>
       <c r="R180" t="n">
-        <v>6846328</v>
+        <v>6846303</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19067,10 +19067,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125047084</v>
+        <v>125046711</v>
       </c>
       <c r="B181" t="n">
-        <v>78947</v>
+        <v>79536</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19083,21 +19083,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19107,10 +19107,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445085</v>
+        <v>444558</v>
       </c>
       <c r="R181" t="n">
-        <v>6846391</v>
+        <v>6846340</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19169,10 +19169,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125047063</v>
+        <v>125046730</v>
       </c>
       <c r="B182" t="n">
-        <v>78947</v>
+        <v>79042</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19185,21 +19185,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19209,10 +19209,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>444866</v>
+        <v>445092</v>
       </c>
       <c r="R182" t="n">
-        <v>6846312</v>
+        <v>6846328</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19271,7 +19271,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125046980</v>
+        <v>125047049</v>
       </c>
       <c r="B183" t="n">
         <v>78947</v>
@@ -19311,10 +19311,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>444528</v>
+        <v>444730</v>
       </c>
       <c r="R183" t="n">
-        <v>6846547</v>
+        <v>6846168</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19373,7 +19373,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125033819</v>
+        <v>125047066</v>
       </c>
       <c r="B184" t="n">
         <v>78947</v>
@@ -19409,17 +19409,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>444990</v>
+        <v>444930</v>
       </c>
       <c r="R184" t="n">
-        <v>6846293</v>
+        <v>6846308</v>
       </c>
       <c r="S184" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19463,19 +19463,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125047003</v>
+        <v>125039886</v>
       </c>
       <c r="B185" t="n">
         <v>78947</v>
@@ -19511,17 +19511,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>444514</v>
+        <v>445091</v>
       </c>
       <c r="R185" t="n">
-        <v>6846274</v>
+        <v>6846446</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19565,19 +19565,19 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125047033</v>
+        <v>125047042</v>
       </c>
       <c r="B186" t="n">
         <v>78947</v>
@@ -19617,10 +19617,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>444600</v>
+        <v>444654</v>
       </c>
       <c r="R186" t="n">
-        <v>6846124</v>
+        <v>6846208</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19679,7 +19679,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125039020</v>
+        <v>125047084</v>
       </c>
       <c r="B187" t="n">
         <v>78947</v>
@@ -19715,17 +19715,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>444897</v>
+        <v>445085</v>
       </c>
       <c r="R187" t="n">
-        <v>6846564</v>
+        <v>6846391</v>
       </c>
       <c r="S187" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19769,19 +19769,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125046983</v>
+        <v>125047063</v>
       </c>
       <c r="B188" t="n">
         <v>78947</v>
@@ -19821,10 +19821,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>444525</v>
+        <v>444866</v>
       </c>
       <c r="R188" t="n">
-        <v>6846510</v>
+        <v>6846312</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19883,7 +19883,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125047035</v>
+        <v>125046980</v>
       </c>
       <c r="B189" t="n">
         <v>78947</v>
@@ -19923,10 +19923,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>444612</v>
+        <v>444528</v>
       </c>
       <c r="R189" t="n">
-        <v>6846153</v>
+        <v>6846547</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19985,7 +19985,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125047047</v>
+        <v>125033819</v>
       </c>
       <c r="B190" t="n">
         <v>78947</v>
@@ -20021,17 +20021,17 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>444740</v>
+        <v>444990</v>
       </c>
       <c r="R190" t="n">
-        <v>6846228</v>
+        <v>6846293</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20075,19 +20075,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125047016</v>
+        <v>125047003</v>
       </c>
       <c r="B191" t="n">
         <v>78947</v>
@@ -20127,10 +20127,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>444490</v>
+        <v>444514</v>
       </c>
       <c r="R191" t="n">
-        <v>6846202</v>
+        <v>6846274</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20189,7 +20189,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125047049</v>
+        <v>125047033</v>
       </c>
       <c r="B192" t="n">
         <v>78947</v>
@@ -20229,10 +20229,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>444730</v>
+        <v>444600</v>
       </c>
       <c r="R192" t="n">
-        <v>6846168</v>
+        <v>6846124</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20291,7 +20291,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125047066</v>
+        <v>125039020</v>
       </c>
       <c r="B193" t="n">
         <v>78947</v>
@@ -20327,17 +20327,17 @@
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>444930</v>
+        <v>444897</v>
       </c>
       <c r="R193" t="n">
-        <v>6846308</v>
+        <v>6846564</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20381,19 +20381,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125039886</v>
+        <v>125046983</v>
       </c>
       <c r="B194" t="n">
         <v>78947</v>
@@ -20429,17 +20429,17 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445091</v>
+        <v>444525</v>
       </c>
       <c r="R194" t="n">
-        <v>6846446</v>
+        <v>6846510</v>
       </c>
       <c r="S194" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20483,19 +20483,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125047042</v>
+        <v>125047035</v>
       </c>
       <c r="B195" t="n">
         <v>78947</v>
@@ -20535,10 +20535,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>444654</v>
+        <v>444612</v>
       </c>
       <c r="R195" t="n">
-        <v>6846208</v>
+        <v>6846153</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20597,10 +20597,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125046712</v>
+        <v>125047047</v>
       </c>
       <c r="B196" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20613,21 +20613,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20637,10 +20637,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>444508</v>
+        <v>444740</v>
       </c>
       <c r="R196" t="n">
-        <v>6846303</v>
+        <v>6846228</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20699,10 +20699,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125046711</v>
+        <v>125047016</v>
       </c>
       <c r="B197" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20715,21 +20715,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20739,10 +20739,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>444558</v>
+        <v>444490</v>
       </c>
       <c r="R197" t="n">
-        <v>6846340</v>
+        <v>6846202</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -27361,10 +27361,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>125046617</v>
+        <v>125046727</v>
       </c>
       <c r="B262" t="n">
-        <v>78979</v>
+        <v>79042</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27377,21 +27377,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27401,10 +27401,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>445436</v>
+        <v>445106</v>
       </c>
       <c r="R262" t="n">
-        <v>6846091</v>
+        <v>6846414</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27463,7 +27463,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>125046684</v>
+        <v>125042743</v>
       </c>
       <c r="B263" t="n">
         <v>78979</v>
@@ -27499,17 +27499,17 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>445419</v>
+        <v>445674</v>
       </c>
       <c r="R263" t="n">
-        <v>6846447</v>
+        <v>6846451</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27553,22 +27553,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>125046644</v>
+        <v>125044882</v>
       </c>
       <c r="B264" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27581,37 +27581,37 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>445553</v>
+        <v>445503</v>
       </c>
       <c r="R264" t="n">
-        <v>6846445</v>
+        <v>6846055</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27655,22 +27655,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>125046727</v>
+        <v>125046928</v>
       </c>
       <c r="B265" t="n">
-        <v>79042</v>
+        <v>78947</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27683,21 +27683,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27707,10 +27707,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>445106</v>
+        <v>445428</v>
       </c>
       <c r="R265" t="n">
-        <v>6846414</v>
+        <v>6846496</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27769,7 +27769,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>125046844</v>
+        <v>125047092</v>
       </c>
       <c r="B266" t="n">
         <v>78947</v>
@@ -27809,10 +27809,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>445468</v>
+        <v>445141</v>
       </c>
       <c r="R266" t="n">
-        <v>6846114</v>
+        <v>6846434</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27871,10 +27871,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>125042743</v>
+        <v>125046863</v>
       </c>
       <c r="B267" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -27887,37 +27887,37 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>445674</v>
+        <v>445707</v>
       </c>
       <c r="R267" t="n">
-        <v>6846451</v>
+        <v>6846395</v>
       </c>
       <c r="S267" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -27961,19 +27961,19 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>125044882</v>
+        <v>125046842</v>
       </c>
       <c r="B268" t="n">
         <v>78947</v>
@@ -28009,17 +28009,17 @@
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>445503</v>
+        <v>445413</v>
       </c>
       <c r="R268" t="n">
-        <v>6846055</v>
+        <v>6846058</v>
       </c>
       <c r="S268" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28063,22 +28063,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>125046928</v>
+        <v>125046617</v>
       </c>
       <c r="B269" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28091,21 +28091,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28115,10 +28115,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>445428</v>
+        <v>445436</v>
       </c>
       <c r="R269" t="n">
-        <v>6846496</v>
+        <v>6846091</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28177,10 +28177,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>125047092</v>
+        <v>125046684</v>
       </c>
       <c r="B270" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28193,21 +28193,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28217,10 +28217,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>445141</v>
+        <v>445419</v>
       </c>
       <c r="R270" t="n">
-        <v>6846434</v>
+        <v>6846447</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28279,10 +28279,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>125046863</v>
+        <v>125046644</v>
       </c>
       <c r="B271" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28295,21 +28295,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28319,10 +28319,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>445707</v>
+        <v>445553</v>
       </c>
       <c r="R271" t="n">
-        <v>6846395</v>
+        <v>6846445</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28381,7 +28381,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>125046842</v>
+        <v>125046844</v>
       </c>
       <c r="B272" t="n">
         <v>78947</v>
@@ -28421,10 +28421,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>445413</v>
+        <v>445468</v>
       </c>
       <c r="R272" t="n">
-        <v>6846058</v>
+        <v>6846114</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -33496,10 +33496,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>125043114</v>
+        <v>125047114</v>
       </c>
       <c r="B322" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -33512,34 +33512,34 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>445786</v>
+        <v>445415</v>
       </c>
       <c r="R322" t="n">
-        <v>6846495</v>
+        <v>6846427</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -33586,19 +33586,19 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>125047114</v>
+        <v>125044794</v>
       </c>
       <c r="B323" t="n">
         <v>78947</v>
@@ -33634,14 +33634,14 @@
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>445415</v>
+        <v>445525</v>
       </c>
       <c r="R323" t="n">
-        <v>6846427</v>
+        <v>6846116</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -33688,19 +33688,19 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>125044794</v>
+        <v>125046859</v>
       </c>
       <c r="B324" t="n">
         <v>78947</v>
@@ -33736,14 +33736,14 @@
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>445525</v>
+        <v>445700</v>
       </c>
       <c r="R324" t="n">
-        <v>6846116</v>
+        <v>6846331</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -33790,19 +33790,19 @@
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>125046859</v>
+        <v>125047093</v>
       </c>
       <c r="B325" t="n">
         <v>78947</v>
@@ -33842,10 +33842,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>445700</v>
+        <v>445167</v>
       </c>
       <c r="R325" t="n">
-        <v>6846331</v>
+        <v>6846434</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -33904,7 +33904,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125047093</v>
+        <v>125042608</v>
       </c>
       <c r="B326" t="n">
         <v>78947</v>
@@ -33940,17 +33940,17 @@
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>445167</v>
+        <v>445614</v>
       </c>
       <c r="R326" t="n">
-        <v>6846434</v>
+        <v>6846422</v>
       </c>
       <c r="S326" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -33994,22 +33994,22 @@
       <c r="AT326" t="inlineStr"/>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>125042608</v>
+        <v>125043114</v>
       </c>
       <c r="B327" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -34022,21 +34022,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -34046,13 +34046,13 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>445614</v>
+        <v>445786</v>
       </c>
       <c r="R327" t="n">
-        <v>6846422</v>
+        <v>6846495</v>
       </c>
       <c r="S327" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -34924,10 +34924,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>125046808</v>
+        <v>125044415</v>
       </c>
       <c r="B336" t="n">
-        <v>91326</v>
+        <v>79536</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -34936,41 +34936,41 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>445463</v>
+        <v>445625</v>
       </c>
       <c r="R336" t="n">
-        <v>6846497</v>
+        <v>6846206</v>
       </c>
       <c r="S336" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -35014,22 +35014,22 @@
       <c r="AT336" t="inlineStr"/>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>125047167</v>
+        <v>125046939</v>
       </c>
       <c r="B337" t="n">
-        <v>88512</v>
+        <v>78947</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -35042,21 +35042,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -35066,10 +35066,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>445451</v>
+        <v>445245</v>
       </c>
       <c r="R337" t="n">
-        <v>6846542</v>
+        <v>6846523</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -35128,10 +35128,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>125046700</v>
+        <v>125046865</v>
       </c>
       <c r="B338" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -35144,21 +35144,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -35168,10 +35168,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>445180</v>
+        <v>445731</v>
       </c>
       <c r="R338" t="n">
-        <v>6846446</v>
+        <v>6846384</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -35230,10 +35230,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>125046686</v>
+        <v>125046923</v>
       </c>
       <c r="B339" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -35246,21 +35246,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -35270,10 +35270,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>445410</v>
+        <v>445506</v>
       </c>
       <c r="R339" t="n">
-        <v>6846399</v>
+        <v>6846550</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -35332,10 +35332,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>125040082</v>
+        <v>125046915</v>
       </c>
       <c r="B340" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -35348,37 +35348,37 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>445167</v>
+        <v>445463</v>
       </c>
       <c r="R340" t="n">
-        <v>6846498</v>
+        <v>6846495</v>
       </c>
       <c r="S340" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -35422,12 +35422,12 @@
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
@@ -35536,10 +35536,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>125046939</v>
+        <v>125046808</v>
       </c>
       <c r="B342" t="n">
-        <v>78947</v>
+        <v>91326</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -35548,25 +35548,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -35576,10 +35576,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>445245</v>
+        <v>445463</v>
       </c>
       <c r="R342" t="n">
-        <v>6846523</v>
+        <v>6846497</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -35638,10 +35638,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>125046865</v>
+        <v>125047167</v>
       </c>
       <c r="B343" t="n">
-        <v>78947</v>
+        <v>88512</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -35654,21 +35654,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -35678,10 +35678,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>445731</v>
+        <v>445451</v>
       </c>
       <c r="R343" t="n">
-        <v>6846384</v>
+        <v>6846542</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -35740,10 +35740,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>125046923</v>
+        <v>125046700</v>
       </c>
       <c r="B344" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -35756,21 +35756,21 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
@@ -35780,10 +35780,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>445506</v>
+        <v>445180</v>
       </c>
       <c r="R344" t="n">
-        <v>6846550</v>
+        <v>6846446</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -35842,10 +35842,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>125046915</v>
+        <v>125046686</v>
       </c>
       <c r="B345" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -35858,21 +35858,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -35882,10 +35882,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>445463</v>
+        <v>445410</v>
       </c>
       <c r="R345" t="n">
-        <v>6846495</v>
+        <v>6846399</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -35944,10 +35944,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>125044415</v>
+        <v>125040082</v>
       </c>
       <c r="B346" t="n">
-        <v>79536</v>
+        <v>78979</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -35960,34 +35960,34 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>445625</v>
+        <v>445167</v>
       </c>
       <c r="R346" t="n">
-        <v>6846206</v>
+        <v>6846498</v>
       </c>
       <c r="S346" t="n">
         <v>20</v>
@@ -36046,10 +36046,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>125033708</v>
+        <v>125046722</v>
       </c>
       <c r="B347" t="n">
-        <v>79042</v>
+        <v>79536</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -36062,37 +36062,37 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>445144</v>
+        <v>445331</v>
       </c>
       <c r="R347" t="n">
-        <v>6846374</v>
+        <v>6846511</v>
       </c>
       <c r="S347" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -36136,22 +36136,22 @@
       <c r="AT347" t="inlineStr"/>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>125043041</v>
+        <v>125046699</v>
       </c>
       <c r="B348" t="n">
-        <v>91338</v>
+        <v>91131</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -36160,41 +36160,41 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>445711</v>
+        <v>445461</v>
       </c>
       <c r="R348" t="n">
-        <v>6846458</v>
+        <v>6846541</v>
       </c>
       <c r="S348" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -36238,22 +36238,22 @@
       <c r="AT348" t="inlineStr"/>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>125046635</v>
+        <v>125047176</v>
       </c>
       <c r="B349" t="n">
-        <v>78979</v>
+        <v>57635</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -36266,34 +36266,39 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P349" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>445624</v>
+        <v>445645</v>
       </c>
       <c r="R349" t="n">
-        <v>6846513</v>
+        <v>6846261</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -36352,10 +36357,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>125046699</v>
+        <v>125033708</v>
       </c>
       <c r="B350" t="n">
-        <v>91131</v>
+        <v>79042</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -36364,41 +36369,41 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>5447</v>
+        <v>967</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>445461</v>
+        <v>445144</v>
       </c>
       <c r="R350" t="n">
-        <v>6846541</v>
+        <v>6846374</v>
       </c>
       <c r="S350" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -36442,22 +36447,22 @@
       <c r="AT350" t="inlineStr"/>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>125046722</v>
+        <v>125043041</v>
       </c>
       <c r="B351" t="n">
-        <v>79536</v>
+        <v>91338</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -36470,37 +36475,37 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>229821</v>
+        <v>1588</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>445331</v>
+        <v>445711</v>
       </c>
       <c r="R351" t="n">
-        <v>6846511</v>
+        <v>6846458</v>
       </c>
       <c r="S351" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -36544,22 +36549,22 @@
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>125047089</v>
+        <v>125046635</v>
       </c>
       <c r="B352" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -36572,21 +36577,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
@@ -36596,10 +36601,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>445130</v>
+        <v>445624</v>
       </c>
       <c r="R352" t="n">
-        <v>6846433</v>
+        <v>6846513</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -36658,7 +36663,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>125046886</v>
+        <v>125047089</v>
       </c>
       <c r="B353" t="n">
         <v>78947</v>
@@ -36698,10 +36703,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>445710</v>
+        <v>445130</v>
       </c>
       <c r="R353" t="n">
-        <v>6846565</v>
+        <v>6846433</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -36760,7 +36765,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>125046889</v>
+        <v>125046886</v>
       </c>
       <c r="B354" t="n">
         <v>78947</v>
@@ -36800,10 +36805,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>445693</v>
+        <v>445710</v>
       </c>
       <c r="R354" t="n">
-        <v>6846539</v>
+        <v>6846565</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -36862,7 +36867,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>125046882</v>
+        <v>125046889</v>
       </c>
       <c r="B355" t="n">
         <v>78947</v>
@@ -36902,10 +36907,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>445747</v>
+        <v>445693</v>
       </c>
       <c r="R355" t="n">
-        <v>6846595</v>
+        <v>6846539</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -36964,7 +36969,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>125046926</v>
+        <v>125046882</v>
       </c>
       <c r="B356" t="n">
         <v>78947</v>
@@ -37004,10 +37009,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>445458</v>
+        <v>445747</v>
       </c>
       <c r="R356" t="n">
-        <v>6846537</v>
+        <v>6846595</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -37066,7 +37071,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>125046856</v>
+        <v>125046926</v>
       </c>
       <c r="B357" t="n">
         <v>78947</v>
@@ -37106,10 +37111,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>445684</v>
+        <v>445458</v>
       </c>
       <c r="R357" t="n">
-        <v>6846335</v>
+        <v>6846537</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -37168,7 +37173,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>125047096</v>
+        <v>125046856</v>
       </c>
       <c r="B358" t="n">
         <v>78947</v>
@@ -37208,10 +37213,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>445181</v>
+        <v>445684</v>
       </c>
       <c r="R358" t="n">
-        <v>6846450</v>
+        <v>6846335</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -37270,7 +37275,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>125046872</v>
+        <v>125047096</v>
       </c>
       <c r="B359" t="n">
         <v>78947</v>
@@ -37310,10 +37315,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>445792</v>
+        <v>445181</v>
       </c>
       <c r="R359" t="n">
-        <v>6846472</v>
+        <v>6846450</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -37372,10 +37377,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>125047176</v>
+        <v>125046872</v>
       </c>
       <c r="B360" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -37388,39 +37393,34 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P360" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>445645</v>
+        <v>445792</v>
       </c>
       <c r="R360" t="n">
-        <v>6846261</v>
+        <v>6846472</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -39218,10 +39218,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>125046795</v>
+        <v>125046891</v>
       </c>
       <c r="B378" t="n">
-        <v>80900</v>
+        <v>78947</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -39234,21 +39234,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I378" t="inlineStr"/>
@@ -39258,10 +39258,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>445335</v>
+        <v>445648</v>
       </c>
       <c r="R378" t="n">
-        <v>6846442</v>
+        <v>6846524</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -39320,7 +39320,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>125046921</v>
+        <v>125047131</v>
       </c>
       <c r="B379" t="n">
         <v>78947</v>
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>445512</v>
+        <v>445633</v>
       </c>
       <c r="R379" t="n">
-        <v>6846523</v>
+        <v>6846266</v>
       </c>
       <c r="S379" t="n">
         <v>10</v>
@@ -39422,10 +39422,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>125046586</v>
+        <v>125046927</v>
       </c>
       <c r="B380" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -39438,21 +39438,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I380" t="inlineStr"/>
@@ -39462,10 +39462,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>445461</v>
+        <v>445457</v>
       </c>
       <c r="R380" t="n">
-        <v>6846503</v>
+        <v>6846522</v>
       </c>
       <c r="S380" t="n">
         <v>10</v>
@@ -39524,7 +39524,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>125033638</v>
+        <v>125047086</v>
       </c>
       <c r="B381" t="n">
         <v>78947</v>
@@ -39560,17 +39560,17 @@
       <c r="I381" t="inlineStr"/>
       <c r="P381" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>445149</v>
+        <v>445120</v>
       </c>
       <c r="R381" t="n">
-        <v>6846386</v>
+        <v>6846396</v>
       </c>
       <c r="S381" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -39614,22 +39614,22 @@
       <c r="AT381" t="inlineStr"/>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>125046630</v>
+        <v>125047160</v>
       </c>
       <c r="B382" t="n">
-        <v>78979</v>
+        <v>57635</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -39642,34 +39642,39 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P382" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>445773</v>
+        <v>445108</v>
       </c>
       <c r="R382" t="n">
-        <v>6846524</v>
+        <v>6846332</v>
       </c>
       <c r="S382" t="n">
         <v>10</v>
@@ -39728,10 +39733,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>125046698</v>
+        <v>125046795</v>
       </c>
       <c r="B383" t="n">
-        <v>91131</v>
+        <v>80900</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -39740,25 +39745,25 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
@@ -39768,10 +39773,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>445716</v>
+        <v>445335</v>
       </c>
       <c r="R383" t="n">
-        <v>6846584</v>
+        <v>6846442</v>
       </c>
       <c r="S383" t="n">
         <v>10</v>
@@ -39830,7 +39835,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>125046891</v>
+        <v>125046921</v>
       </c>
       <c r="B384" t="n">
         <v>78947</v>
@@ -39870,10 +39875,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>445648</v>
+        <v>445512</v>
       </c>
       <c r="R384" t="n">
-        <v>6846524</v>
+        <v>6846523</v>
       </c>
       <c r="S384" t="n">
         <v>10</v>
@@ -39932,10 +39937,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>125047131</v>
+        <v>125046586</v>
       </c>
       <c r="B385" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -39948,21 +39953,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
@@ -39972,10 +39977,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>445633</v>
+        <v>445461</v>
       </c>
       <c r="R385" t="n">
-        <v>6846266</v>
+        <v>6846503</v>
       </c>
       <c r="S385" t="n">
         <v>10</v>
@@ -40034,7 +40039,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>125046927</v>
+        <v>125033638</v>
       </c>
       <c r="B386" t="n">
         <v>78947</v>
@@ -40070,17 +40075,17 @@
       <c r="I386" t="inlineStr"/>
       <c r="P386" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>445457</v>
+        <v>445149</v>
       </c>
       <c r="R386" t="n">
-        <v>6846522</v>
+        <v>6846386</v>
       </c>
       <c r="S386" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -40124,22 +40129,22 @@
       <c r="AT386" t="inlineStr"/>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>125047086</v>
+        <v>125046630</v>
       </c>
       <c r="B387" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -40152,21 +40157,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
@@ -40176,10 +40181,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>445120</v>
+        <v>445773</v>
       </c>
       <c r="R387" t="n">
-        <v>6846396</v>
+        <v>6846524</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -40238,10 +40243,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>125047160</v>
+        <v>125046698</v>
       </c>
       <c r="B388" t="n">
-        <v>57635</v>
+        <v>91131</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -40250,43 +40255,38 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P388" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>445108</v>
+        <v>445716</v>
       </c>
       <c r="R388" t="n">
-        <v>6846332</v>
+        <v>6846584</v>
       </c>
       <c r="S388" t="n">
         <v>10</v>
@@ -43303,7 +43303,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>125046929</v>
+        <v>125046868</v>
       </c>
       <c r="B418" t="n">
         <v>78947</v>
@@ -43343,10 +43343,10 @@
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>445400</v>
+        <v>445755</v>
       </c>
       <c r="R418" t="n">
-        <v>6846484</v>
+        <v>6846425</v>
       </c>
       <c r="S418" t="n">
         <v>10</v>
@@ -43405,7 +43405,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>125047113</v>
+        <v>125040110</v>
       </c>
       <c r="B419" t="n">
         <v>78947</v>
@@ -43441,17 +43441,17 @@
       <c r="I419" t="inlineStr"/>
       <c r="P419" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>445420</v>
+        <v>445183</v>
       </c>
       <c r="R419" t="n">
-        <v>6846444</v>
+        <v>6846527</v>
       </c>
       <c r="S419" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -43495,19 +43495,19 @@
       <c r="AT419" t="inlineStr"/>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>125046932</v>
+        <v>125046911</v>
       </c>
       <c r="B420" t="n">
         <v>78947</v>
@@ -43547,10 +43547,10 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>445374</v>
+        <v>445466</v>
       </c>
       <c r="R420" t="n">
-        <v>6846475</v>
+        <v>6846487</v>
       </c>
       <c r="S420" t="n">
         <v>10</v>
@@ -43609,7 +43609,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>125047109</v>
+        <v>125046873</v>
       </c>
       <c r="B421" t="n">
         <v>78947</v>
@@ -43649,10 +43649,10 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>445379</v>
+        <v>445796</v>
       </c>
       <c r="R421" t="n">
-        <v>6846474</v>
+        <v>6846481</v>
       </c>
       <c r="S421" t="n">
         <v>10</v>
@@ -43711,10 +43711,10 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>125046605</v>
+        <v>125046627</v>
       </c>
       <c r="B422" t="n">
-        <v>79565</v>
+        <v>78979</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -43727,21 +43727,21 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I422" t="inlineStr"/>
@@ -43751,10 +43751,10 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>445117</v>
+        <v>445760</v>
       </c>
       <c r="R422" t="n">
-        <v>6846341</v>
+        <v>6846419</v>
       </c>
       <c r="S422" t="n">
         <v>10</v>
@@ -43813,10 +43813,10 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>125046868</v>
+        <v>125046633</v>
       </c>
       <c r="B423" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -43829,21 +43829,21 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I423" t="inlineStr"/>
@@ -43853,10 +43853,10 @@
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>445755</v>
+        <v>445732</v>
       </c>
       <c r="R423" t="n">
-        <v>6846425</v>
+        <v>6846593</v>
       </c>
       <c r="S423" t="n">
         <v>10</v>
@@ -43915,10 +43915,10 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>125040110</v>
+        <v>125046724</v>
       </c>
       <c r="B424" t="n">
-        <v>78947</v>
+        <v>79042</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -43931,37 +43931,37 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I424" t="inlineStr"/>
       <c r="P424" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>445183</v>
+        <v>445715</v>
       </c>
       <c r="R424" t="n">
-        <v>6846527</v>
+        <v>6846550</v>
       </c>
       <c r="S424" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -44005,19 +44005,19 @@
       <c r="AT424" t="inlineStr"/>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>125046911</v>
+        <v>125046929</v>
       </c>
       <c r="B425" t="n">
         <v>78947</v>
@@ -44057,10 +44057,10 @@
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>445466</v>
+        <v>445400</v>
       </c>
       <c r="R425" t="n">
-        <v>6846487</v>
+        <v>6846484</v>
       </c>
       <c r="S425" t="n">
         <v>10</v>
@@ -44119,7 +44119,7 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>125046873</v>
+        <v>125047113</v>
       </c>
       <c r="B426" t="n">
         <v>78947</v>
@@ -44159,10 +44159,10 @@
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>445796</v>
+        <v>445420</v>
       </c>
       <c r="R426" t="n">
-        <v>6846481</v>
+        <v>6846444</v>
       </c>
       <c r="S426" t="n">
         <v>10</v>
@@ -44221,10 +44221,10 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>125046627</v>
+        <v>125046932</v>
       </c>
       <c r="B427" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -44237,21 +44237,21 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
@@ -44261,10 +44261,10 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>445760</v>
+        <v>445374</v>
       </c>
       <c r="R427" t="n">
-        <v>6846419</v>
+        <v>6846475</v>
       </c>
       <c r="S427" t="n">
         <v>10</v>
@@ -44323,10 +44323,10 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>125046633</v>
+        <v>125047109</v>
       </c>
       <c r="B428" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -44339,21 +44339,21 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I428" t="inlineStr"/>
@@ -44363,10 +44363,10 @@
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>445732</v>
+        <v>445379</v>
       </c>
       <c r="R428" t="n">
-        <v>6846593</v>
+        <v>6846474</v>
       </c>
       <c r="S428" t="n">
         <v>10</v>
@@ -44425,10 +44425,10 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>125046724</v>
+        <v>125046605</v>
       </c>
       <c r="B429" t="n">
-        <v>79042</v>
+        <v>79565</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -44441,21 +44441,21 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I429" t="inlineStr"/>
@@ -44465,10 +44465,10 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>445715</v>
+        <v>445117</v>
       </c>
       <c r="R429" t="n">
-        <v>6846550</v>
+        <v>6846341</v>
       </c>
       <c r="S429" t="n">
         <v>10</v>
@@ -47801,10 +47801,10 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>125047162</v>
+        <v>125042661</v>
       </c>
       <c r="B462" t="n">
-        <v>57635</v>
+        <v>78979</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
@@ -47817,39 +47817,34 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I462" t="inlineStr"/>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P462" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q462" t="n">
-        <v>445592</v>
+        <v>445648</v>
       </c>
       <c r="R462" t="n">
-        <v>6846251</v>
+        <v>6846428</v>
       </c>
       <c r="S462" t="n">
         <v>10</v>
@@ -47896,22 +47891,22 @@
       <c r="AT462" t="inlineStr"/>
       <c r="AW462" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX462" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>125047171</v>
+        <v>125046638</v>
       </c>
       <c r="B463" t="n">
-        <v>5176</v>
+        <v>78979</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -47920,43 +47915,38 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I463" t="inlineStr"/>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P463" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q463" t="n">
-        <v>445621</v>
+        <v>445609</v>
       </c>
       <c r="R463" t="n">
-        <v>6846481</v>
+        <v>6846474</v>
       </c>
       <c r="S463" t="n">
         <v>10</v>
@@ -48015,10 +48005,10 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>125046743</v>
+        <v>125046794</v>
       </c>
       <c r="B464" t="n">
-        <v>57793</v>
+        <v>80900</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -48031,21 +48021,21 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I464" t="inlineStr"/>
@@ -48055,10 +48045,10 @@
         </is>
       </c>
       <c r="Q464" t="n">
-        <v>445427</v>
+        <v>445622</v>
       </c>
       <c r="R464" t="n">
-        <v>6846297</v>
+        <v>6846518</v>
       </c>
       <c r="S464" t="n">
         <v>10</v>
@@ -48117,10 +48107,10 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>125042661</v>
+        <v>125046895</v>
       </c>
       <c r="B465" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -48133,34 +48123,34 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I465" t="inlineStr"/>
       <c r="P465" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q465" t="n">
-        <v>445648</v>
+        <v>445603</v>
       </c>
       <c r="R465" t="n">
-        <v>6846428</v>
+        <v>6846478</v>
       </c>
       <c r="S465" t="n">
         <v>10</v>
@@ -48207,22 +48197,22 @@
       <c r="AT465" t="inlineStr"/>
       <c r="AW465" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX465" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>125046638</v>
+        <v>125043770</v>
       </c>
       <c r="B466" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -48235,37 +48225,37 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I466" t="inlineStr"/>
       <c r="P466" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q466" t="n">
-        <v>445609</v>
+        <v>445700</v>
       </c>
       <c r="R466" t="n">
-        <v>6846474</v>
+        <v>6846353</v>
       </c>
       <c r="S466" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T466" t="inlineStr">
         <is>
@@ -48309,22 +48299,22 @@
       <c r="AT466" t="inlineStr"/>
       <c r="AW466" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX466" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>125046794</v>
+        <v>125033462</v>
       </c>
       <c r="B467" t="n">
-        <v>80900</v>
+        <v>79565</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -48337,34 +48327,34 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I467" t="inlineStr"/>
       <c r="P467" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q467" t="n">
-        <v>445622</v>
+        <v>445182</v>
       </c>
       <c r="R467" t="n">
-        <v>6846518</v>
+        <v>6846445</v>
       </c>
       <c r="S467" t="n">
         <v>10</v>
@@ -48411,22 +48401,22 @@
       <c r="AT467" t="inlineStr"/>
       <c r="AW467" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX467" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>125042127</v>
+        <v>125046761</v>
       </c>
       <c r="B468" t="n">
-        <v>78979</v>
+        <v>79033</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -48435,41 +48425,41 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I468" t="inlineStr"/>
       <c r="P468" t="inlineStr">
         <is>
-          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q468" t="n">
-        <v>445538</v>
+        <v>445101</v>
       </c>
       <c r="R468" t="n">
-        <v>6846416</v>
+        <v>6846542</v>
       </c>
       <c r="S468" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T468" t="inlineStr">
         <is>
@@ -48513,22 +48503,22 @@
       <c r="AT468" t="inlineStr"/>
       <c r="AW468" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX468" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>125046693</v>
+        <v>125033588</v>
       </c>
       <c r="B469" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -48541,34 +48531,34 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I469" t="inlineStr"/>
       <c r="P469" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
         </is>
       </c>
       <c r="Q469" t="n">
-        <v>445542</v>
+        <v>445139</v>
       </c>
       <c r="R469" t="n">
-        <v>6846225</v>
+        <v>6846361</v>
       </c>
       <c r="S469" t="n">
         <v>10</v>
@@ -48615,22 +48605,22 @@
       <c r="AT469" t="inlineStr"/>
       <c r="AW469" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX469" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>125047111</v>
+        <v>125042127</v>
       </c>
       <c r="B470" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -48643,37 +48633,37 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I470" t="inlineStr"/>
       <c r="P470" t="inlineStr">
         <is>
-          <t>Stor Åndberg, Hjd</t>
+          <t>Åndbergskölen, Åndbergskölen, Hjd</t>
         </is>
       </c>
       <c r="Q470" t="n">
-        <v>445392</v>
+        <v>445538</v>
       </c>
       <c r="R470" t="n">
-        <v>6846463</v>
+        <v>6846416</v>
       </c>
       <c r="S470" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T470" t="inlineStr">
         <is>
@@ -48717,22 +48707,22 @@
       <c r="AT470" t="inlineStr"/>
       <c r="AW470" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX470" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>125046860</v>
+        <v>125046634</v>
       </c>
       <c r="B471" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -48745,21 +48735,21 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I471" t="inlineStr"/>
@@ -48769,10 +48759,10 @@
         </is>
       </c>
       <c r="Q471" t="n">
-        <v>445719</v>
+        <v>445653</v>
       </c>
       <c r="R471" t="n">
-        <v>6846343</v>
+        <v>6846540</v>
       </c>
       <c r="S471" t="n">
         <v>10</v>
@@ -48831,10 +48821,10 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>125047079</v>
+        <v>125046815</v>
       </c>
       <c r="B472" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -48847,21 +48837,21 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I472" t="inlineStr"/>
@@ -48871,10 +48861,10 @@
         </is>
       </c>
       <c r="Q472" t="n">
-        <v>445117</v>
+        <v>445196</v>
       </c>
       <c r="R472" t="n">
-        <v>6846339</v>
+        <v>6846474</v>
       </c>
       <c r="S472" t="n">
         <v>10</v>
@@ -48933,10 +48923,10 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>125046840</v>
+        <v>125046812</v>
       </c>
       <c r="B473" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -48949,21 +48939,21 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I473" t="inlineStr"/>
@@ -48973,10 +48963,10 @@
         </is>
       </c>
       <c r="Q473" t="n">
-        <v>445468</v>
+        <v>445677</v>
       </c>
       <c r="R473" t="n">
-        <v>6846075</v>
+        <v>6846563</v>
       </c>
       <c r="S473" t="n">
         <v>10</v>
@@ -49035,10 +49025,10 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>125047127</v>
+        <v>125046693</v>
       </c>
       <c r="B474" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
@@ -49051,21 +49041,21 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I474" t="inlineStr"/>
@@ -49075,10 +49065,10 @@
         </is>
       </c>
       <c r="Q474" t="n">
-        <v>445599</v>
+        <v>445542</v>
       </c>
       <c r="R474" t="n">
-        <v>6846247</v>
+        <v>6846225</v>
       </c>
       <c r="S474" t="n">
         <v>10</v>
@@ -49137,7 +49127,7 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>125047103</v>
+        <v>125047111</v>
       </c>
       <c r="B475" t="n">
         <v>78947</v>
@@ -49177,10 +49167,10 @@
         </is>
       </c>
       <c r="Q475" t="n">
-        <v>445267</v>
+        <v>445392</v>
       </c>
       <c r="R475" t="n">
-        <v>6846508</v>
+        <v>6846463</v>
       </c>
       <c r="S475" t="n">
         <v>10</v>
@@ -49239,7 +49229,7 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>125046895</v>
+        <v>125046860</v>
       </c>
       <c r="B476" t="n">
         <v>78947</v>
@@ -49279,10 +49269,10 @@
         </is>
       </c>
       <c r="Q476" t="n">
-        <v>445603</v>
+        <v>445719</v>
       </c>
       <c r="R476" t="n">
-        <v>6846478</v>
+        <v>6846343</v>
       </c>
       <c r="S476" t="n">
         <v>10</v>
@@ -49341,7 +49331,7 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>125043770</v>
+        <v>125047079</v>
       </c>
       <c r="B477" t="n">
         <v>78947</v>
@@ -49377,17 +49367,17 @@
       <c r="I477" t="inlineStr"/>
       <c r="P477" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q477" t="n">
-        <v>445700</v>
+        <v>445117</v>
       </c>
       <c r="R477" t="n">
-        <v>6846353</v>
+        <v>6846339</v>
       </c>
       <c r="S477" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T477" t="inlineStr">
         <is>
@@ -49431,22 +49421,22 @@
       <c r="AT477" t="inlineStr"/>
       <c r="AW477" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX477" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>125033462</v>
+        <v>125046840</v>
       </c>
       <c r="B478" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -49459,34 +49449,34 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I478" t="inlineStr"/>
       <c r="P478" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q478" t="n">
-        <v>445182</v>
+        <v>445468</v>
       </c>
       <c r="R478" t="n">
-        <v>6846445</v>
+        <v>6846075</v>
       </c>
       <c r="S478" t="n">
         <v>10</v>
@@ -49533,22 +49523,22 @@
       <c r="AT478" t="inlineStr"/>
       <c r="AW478" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX478" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>125046761</v>
+        <v>125047127</v>
       </c>
       <c r="B479" t="n">
-        <v>79033</v>
+        <v>78947</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -49557,25 +49547,25 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I479" t="inlineStr"/>
@@ -49585,10 +49575,10 @@
         </is>
       </c>
       <c r="Q479" t="n">
-        <v>445101</v>
+        <v>445599</v>
       </c>
       <c r="R479" t="n">
-        <v>6846542</v>
+        <v>6846247</v>
       </c>
       <c r="S479" t="n">
         <v>10</v>
@@ -49647,7 +49637,7 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>125033588</v>
+        <v>125047103</v>
       </c>
       <c r="B480" t="n">
         <v>78947</v>
@@ -49683,14 +49673,14 @@
       <c r="I480" t="inlineStr"/>
       <c r="P480" t="inlineStr">
         <is>
-          <t>Stor-Åndberget, Stor-Åndberget, Hjd</t>
+          <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q480" t="n">
-        <v>445139</v>
+        <v>445267</v>
       </c>
       <c r="R480" t="n">
-        <v>6846361</v>
+        <v>6846508</v>
       </c>
       <c r="S480" t="n">
         <v>10</v>
@@ -49737,22 +49727,22 @@
       <c r="AT480" t="inlineStr"/>
       <c r="AW480" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX480" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson</t>
         </is>
       </c>
       <c r="AY480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>125046634</v>
+        <v>125046743</v>
       </c>
       <c r="B481" t="n">
-        <v>78979</v>
+        <v>57793</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -49765,21 +49755,21 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I481" t="inlineStr"/>
@@ -49789,10 +49779,10 @@
         </is>
       </c>
       <c r="Q481" t="n">
-        <v>445653</v>
+        <v>445427</v>
       </c>
       <c r="R481" t="n">
-        <v>6846540</v>
+        <v>6846297</v>
       </c>
       <c r="S481" t="n">
         <v>10</v>
@@ -49851,10 +49841,10 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>125046815</v>
+        <v>125047162</v>
       </c>
       <c r="B482" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -49867,34 +49857,39 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P482" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q482" t="n">
-        <v>445196</v>
+        <v>445592</v>
       </c>
       <c r="R482" t="n">
-        <v>6846474</v>
+        <v>6846251</v>
       </c>
       <c r="S482" t="n">
         <v>10</v>
@@ -49953,10 +49948,10 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>125046812</v>
+        <v>125047171</v>
       </c>
       <c r="B483" t="n">
-        <v>91184</v>
+        <v>5176</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -49965,38 +49960,43 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P483" t="inlineStr">
         <is>
           <t>Stor Åndberg, Hjd</t>
         </is>
       </c>
       <c r="Q483" t="n">
-        <v>445677</v>
+        <v>445621</v>
       </c>
       <c r="R483" t="n">
-        <v>6846563</v>
+        <v>6846481</v>
       </c>
       <c r="S483" t="n">
         <v>10</v>
